--- a/JSTQB_Foundation.xlsx
+++ b/JSTQB_Foundation.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27932"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29530"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ドキュメント\勉強\資格(取得)\JSTQB\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ドキュメント\その他\eラーニング\JSTQB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F183FA1E-4C86-4B72-901C-8ED457AA3172}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C4F3AE8-E2F3-49D4-A487-66CCB4C79AB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,15 +33,12 @@
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="15">
   <si>
     <t>典型的なテストの目的として、誤っているものはどれか。次の選択肢の中から1つ選びなさい。</t>
     <phoneticPr fontId="1"/>
@@ -430,7 +427,7 @@
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="2" max="2" width="4.5" customWidth="1"/>
-    <col min="3" max="3" width="4.796875" customWidth="1"/>
+    <col min="3" max="3" width="4.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:4">
@@ -496,7 +493,7 @@
   <dimension ref="B2:F107"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
-    <col min="6" max="6" width="10.19921875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:6">
@@ -1351,93 +1348,108 @@
       <c r="C78">
         <v>11</v>
       </c>
+      <c r="E78" t="s">
+        <v>10</v>
+      </c>
+      <c r="F78" s="1">
+        <v>46090</v>
+      </c>
     </row>
     <row r="79" spans="2:6">
       <c r="C79">
         <v>12</v>
       </c>
+      <c r="E79" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="80" spans="2:6">
       <c r="C80">
         <v>13</v>
       </c>
-    </row>
-    <row r="81" spans="3:3">
+      <c r="E80" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="81" spans="3:5">
       <c r="C81">
         <v>14</v>
       </c>
-    </row>
-    <row r="82" spans="3:3">
+      <c r="E81" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="82" spans="3:5">
       <c r="C82">
         <v>15</v>
       </c>
     </row>
-    <row r="83" spans="3:3">
+    <row r="83" spans="3:5">
       <c r="C83">
         <v>16</v>
       </c>
     </row>
-    <row r="84" spans="3:3">
+    <row r="84" spans="3:5">
       <c r="C84">
         <v>17</v>
       </c>
     </row>
-    <row r="85" spans="3:3">
+    <row r="85" spans="3:5">
       <c r="C85">
         <v>18</v>
       </c>
     </row>
-    <row r="86" spans="3:3">
+    <row r="86" spans="3:5">
       <c r="C86">
         <v>19</v>
       </c>
     </row>
-    <row r="87" spans="3:3">
+    <row r="87" spans="3:5">
       <c r="C87">
         <v>20</v>
       </c>
     </row>
-    <row r="88" spans="3:3">
+    <row r="88" spans="3:5">
       <c r="C88">
         <v>21</v>
       </c>
     </row>
-    <row r="89" spans="3:3">
+    <row r="89" spans="3:5">
       <c r="C89">
         <v>22</v>
       </c>
     </row>
-    <row r="90" spans="3:3">
+    <row r="90" spans="3:5">
       <c r="C90">
         <v>23</v>
       </c>
     </row>
-    <row r="91" spans="3:3">
+    <row r="91" spans="3:5">
       <c r="C91">
         <v>24</v>
       </c>
     </row>
-    <row r="92" spans="3:3">
+    <row r="92" spans="3:5">
       <c r="C92">
         <v>25</v>
       </c>
     </row>
-    <row r="93" spans="3:3">
+    <row r="93" spans="3:5">
       <c r="C93">
         <v>26</v>
       </c>
     </row>
-    <row r="94" spans="3:3">
+    <row r="94" spans="3:5">
       <c r="C94">
         <v>27</v>
       </c>
     </row>
-    <row r="95" spans="3:3">
+    <row r="95" spans="3:5">
       <c r="C95">
         <v>28</v>
       </c>
     </row>
-    <row r="96" spans="3:3">
+    <row r="96" spans="3:5">
       <c r="C96">
         <v>29</v>
       </c>
@@ -1500,5 +1512,6 @@
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/JSTQB_Foundation.xlsx
+++ b/JSTQB_Foundation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ドキュメント\その他\eラーニング\JSTQB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C4F3AE8-E2F3-49D4-A487-66CCB4C79AB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75917D3F-1190-4A51-8FDD-74789A59605D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="15">
   <si>
     <t>典型的なテストの目的として、誤っているものはどれか。次の選択肢の中から1つ選びなさい。</t>
     <phoneticPr fontId="1"/>
@@ -1371,7 +1371,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="81" spans="3:5">
+    <row r="81" spans="3:6">
       <c r="C81">
         <v>14</v>
       </c>
@@ -1379,77 +1379,110 @@
         <v>12</v>
       </c>
     </row>
-    <row r="82" spans="3:5">
+    <row r="82" spans="3:6">
       <c r="C82">
         <v>15</v>
       </c>
-    </row>
-    <row r="83" spans="3:5">
+      <c r="E82" t="s">
+        <v>11</v>
+      </c>
+      <c r="F82" s="1">
+        <v>46091</v>
+      </c>
+    </row>
+    <row r="83" spans="3:6">
       <c r="C83">
         <v>16</v>
       </c>
-    </row>
-    <row r="84" spans="3:5">
+      <c r="E83" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="84" spans="3:6">
       <c r="C84">
         <v>17</v>
       </c>
-    </row>
-    <row r="85" spans="3:5">
+      <c r="E84" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="85" spans="3:6">
       <c r="C85">
         <v>18</v>
       </c>
-    </row>
-    <row r="86" spans="3:5">
+      <c r="E85" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="86" spans="3:6">
       <c r="C86">
         <v>19</v>
       </c>
-    </row>
-    <row r="87" spans="3:5">
+      <c r="E86" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="87" spans="3:6">
       <c r="C87">
         <v>20</v>
       </c>
-    </row>
-    <row r="88" spans="3:5">
+      <c r="E87" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="88" spans="3:6">
       <c r="C88">
         <v>21</v>
       </c>
-    </row>
-    <row r="89" spans="3:5">
+      <c r="E88" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="89" spans="3:6">
       <c r="C89">
         <v>22</v>
       </c>
-    </row>
-    <row r="90" spans="3:5">
+      <c r="E89" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="90" spans="3:6">
       <c r="C90">
         <v>23</v>
       </c>
-    </row>
-    <row r="91" spans="3:5">
+      <c r="E90" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="91" spans="3:6">
       <c r="C91">
         <v>24</v>
       </c>
-    </row>
-    <row r="92" spans="3:5">
+      <c r="E91" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="92" spans="3:6">
       <c r="C92">
         <v>25</v>
       </c>
     </row>
-    <row r="93" spans="3:5">
+    <row r="93" spans="3:6">
       <c r="C93">
         <v>26</v>
       </c>
     </row>
-    <row r="94" spans="3:5">
+    <row r="94" spans="3:6">
       <c r="C94">
         <v>27</v>
       </c>
     </row>
-    <row r="95" spans="3:5">
+    <row r="95" spans="3:6">
       <c r="C95">
         <v>28</v>
       </c>
     </row>
-    <row r="96" spans="3:5">
+    <row r="96" spans="3:6">
       <c r="C96">
         <v>29</v>
       </c>

--- a/JSTQB_Foundation.xlsx
+++ b/JSTQB_Foundation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ドキュメント\その他\eラーニング\JSTQB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75917D3F-1190-4A51-8FDD-74789A59605D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FC13ED8-4729-4ED3-AD8B-8683ED6055B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="15">
   <si>
     <t>典型的なテストの目的として、誤っているものはどれか。次の選択肢の中から1つ選びなさい。</t>
     <phoneticPr fontId="1"/>
@@ -96,7 +96,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -117,6 +117,13 @@
       <name val="Segoe UI Symbol"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Yu Gothic"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -135,15 +142,20 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="パーセント" xfId="1" builtinId="5"/>
     <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -490,7 +502,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CFBD2AC0-38EC-4B9C-A0BF-1559C25A244C}">
   <sheetPr codeName="Sheet3"/>
-  <dimension ref="B2:F107"/>
+  <dimension ref="B2:F108"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="6" max="6" width="10.1640625" bestFit="1" customWidth="1"/>
@@ -1265,6 +1277,9 @@
       <c r="C68">
         <v>1</v>
       </c>
+      <c r="D68" t="s">
+        <v>9</v>
+      </c>
       <c r="E68" t="s">
         <v>12</v>
       </c>
@@ -1276,6 +1291,9 @@
       <c r="C69">
         <v>2</v>
       </c>
+      <c r="D69" t="s">
+        <v>9</v>
+      </c>
       <c r="E69" t="s">
         <v>12</v>
       </c>
@@ -1284,6 +1302,9 @@
       <c r="C70">
         <v>3</v>
       </c>
+      <c r="D70" t="s">
+        <v>9</v>
+      </c>
       <c r="E70" t="s">
         <v>13</v>
       </c>
@@ -1292,6 +1313,9 @@
       <c r="C71">
         <v>4</v>
       </c>
+      <c r="D71" t="s">
+        <v>9</v>
+      </c>
       <c r="E71" t="s">
         <v>12</v>
       </c>
@@ -1300,6 +1324,9 @@
       <c r="C72">
         <v>5</v>
       </c>
+      <c r="D72" t="s">
+        <v>9</v>
+      </c>
       <c r="E72" t="s">
         <v>13</v>
       </c>
@@ -1308,6 +1335,9 @@
       <c r="C73">
         <v>6</v>
       </c>
+      <c r="D73" t="s">
+        <v>9</v>
+      </c>
       <c r="E73" t="s">
         <v>13</v>
       </c>
@@ -1316,6 +1346,9 @@
       <c r="C74">
         <v>7</v>
       </c>
+      <c r="D74" t="s">
+        <v>9</v>
+      </c>
       <c r="E74" t="s">
         <v>12</v>
       </c>
@@ -1324,6 +1357,9 @@
       <c r="C75">
         <v>8</v>
       </c>
+      <c r="D75" t="s">
+        <v>9</v>
+      </c>
       <c r="E75" t="s">
         <v>10</v>
       </c>
@@ -1332,6 +1368,9 @@
       <c r="C76">
         <v>9</v>
       </c>
+      <c r="D76" t="s">
+        <v>9</v>
+      </c>
       <c r="E76" t="s">
         <v>10</v>
       </c>
@@ -1340,6 +1379,9 @@
       <c r="C77">
         <v>10</v>
       </c>
+      <c r="D77" s="2" t="s">
+        <v>14</v>
+      </c>
       <c r="E77" t="s">
         <v>11</v>
       </c>
@@ -1348,6 +1390,9 @@
       <c r="C78">
         <v>11</v>
       </c>
+      <c r="D78" t="s">
+        <v>9</v>
+      </c>
       <c r="E78" t="s">
         <v>10</v>
       </c>
@@ -1359,6 +1404,9 @@
       <c r="C79">
         <v>12</v>
       </c>
+      <c r="D79" t="s">
+        <v>9</v>
+      </c>
       <c r="E79" t="s">
         <v>13</v>
       </c>
@@ -1367,6 +1415,9 @@
       <c r="C80">
         <v>13</v>
       </c>
+      <c r="D80" s="2" t="s">
+        <v>14</v>
+      </c>
       <c r="E80" t="s">
         <v>13</v>
       </c>
@@ -1374,6 +1425,9 @@
     <row r="81" spans="3:6">
       <c r="C81">
         <v>14</v>
+      </c>
+      <c r="D81" t="s">
+        <v>9</v>
       </c>
       <c r="E81" t="s">
         <v>12</v>
@@ -1383,6 +1437,9 @@
       <c r="C82">
         <v>15</v>
       </c>
+      <c r="D82" s="2" t="s">
+        <v>14</v>
+      </c>
       <c r="E82" t="s">
         <v>11</v>
       </c>
@@ -1394,6 +1451,9 @@
       <c r="C83">
         <v>16</v>
       </c>
+      <c r="D83" t="s">
+        <v>9</v>
+      </c>
       <c r="E83" t="s">
         <v>13</v>
       </c>
@@ -1402,6 +1462,9 @@
       <c r="C84">
         <v>17</v>
       </c>
+      <c r="D84" s="2" t="s">
+        <v>14</v>
+      </c>
       <c r="E84" t="s">
         <v>10</v>
       </c>
@@ -1410,6 +1473,9 @@
       <c r="C85">
         <v>18</v>
       </c>
+      <c r="D85" t="s">
+        <v>9</v>
+      </c>
       <c r="E85" t="s">
         <v>11</v>
       </c>
@@ -1418,6 +1484,9 @@
       <c r="C86">
         <v>19</v>
       </c>
+      <c r="D86" t="s">
+        <v>9</v>
+      </c>
       <c r="E86" t="s">
         <v>12</v>
       </c>
@@ -1426,6 +1495,9 @@
       <c r="C87">
         <v>20</v>
       </c>
+      <c r="D87" t="s">
+        <v>9</v>
+      </c>
       <c r="E87" t="s">
         <v>13</v>
       </c>
@@ -1434,6 +1506,9 @@
       <c r="C88">
         <v>21</v>
       </c>
+      <c r="D88" t="s">
+        <v>9</v>
+      </c>
       <c r="E88" t="s">
         <v>12</v>
       </c>
@@ -1442,6 +1517,9 @@
       <c r="C89">
         <v>22</v>
       </c>
+      <c r="D89" t="s">
+        <v>9</v>
+      </c>
       <c r="E89" t="s">
         <v>13</v>
       </c>
@@ -1450,6 +1528,9 @@
       <c r="C90">
         <v>23</v>
       </c>
+      <c r="D90" t="s">
+        <v>9</v>
+      </c>
       <c r="E90" t="s">
         <v>10</v>
       </c>
@@ -1458,6 +1539,9 @@
       <c r="C91">
         <v>24</v>
       </c>
+      <c r="D91" s="2" t="s">
+        <v>14</v>
+      </c>
       <c r="E91" t="s">
         <v>12</v>
       </c>
@@ -1466,80 +1550,186 @@
       <c r="C92">
         <v>25</v>
       </c>
+      <c r="D92" t="s">
+        <v>9</v>
+      </c>
+      <c r="E92" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="93" spans="3:6">
       <c r="C93">
         <v>26</v>
       </c>
+      <c r="D93" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E93" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="94" spans="3:6">
       <c r="C94">
         <v>27</v>
       </c>
+      <c r="D94" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E94" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="95" spans="3:6">
       <c r="C95">
         <v>28</v>
       </c>
+      <c r="D95" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E95" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="96" spans="3:6">
       <c r="C96">
         <v>29</v>
       </c>
-    </row>
-    <row r="97" spans="3:3">
+      <c r="D96" t="s">
+        <v>9</v>
+      </c>
+      <c r="E96" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="97" spans="3:5">
       <c r="C97">
         <v>30</v>
       </c>
-    </row>
-    <row r="98" spans="3:3">
+      <c r="D97" t="s">
+        <v>9</v>
+      </c>
+      <c r="E97" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="98" spans="3:5">
       <c r="C98">
         <v>31</v>
       </c>
-    </row>
-    <row r="99" spans="3:3">
+      <c r="D98" t="s">
+        <v>9</v>
+      </c>
+      <c r="E98" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="99" spans="3:5">
       <c r="C99">
         <v>32</v>
       </c>
-    </row>
-    <row r="100" spans="3:3">
+      <c r="D99" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E99" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="100" spans="3:5">
       <c r="C100">
         <v>33</v>
       </c>
-    </row>
-    <row r="101" spans="3:3">
+      <c r="D100" t="s">
+        <v>9</v>
+      </c>
+      <c r="E100" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="101" spans="3:5">
       <c r="C101">
         <v>34</v>
       </c>
-    </row>
-    <row r="102" spans="3:3">
+      <c r="D101" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E101" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="102" spans="3:5">
       <c r="C102">
         <v>35</v>
       </c>
-    </row>
-    <row r="103" spans="3:3">
+      <c r="D102" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E102" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="103" spans="3:5">
       <c r="C103">
         <v>36</v>
       </c>
-    </row>
-    <row r="104" spans="3:3">
+      <c r="D103" t="s">
+        <v>9</v>
+      </c>
+      <c r="E103" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="104" spans="3:5">
       <c r="C104">
         <v>37</v>
       </c>
-    </row>
-    <row r="105" spans="3:3">
+      <c r="D104" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E104" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="105" spans="3:5">
       <c r="C105">
         <v>38</v>
       </c>
-    </row>
-    <row r="106" spans="3:3">
+      <c r="D105" t="s">
+        <v>9</v>
+      </c>
+      <c r="E105" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="106" spans="3:5">
       <c r="C106">
         <v>39</v>
       </c>
-    </row>
-    <row r="107" spans="3:3">
+      <c r="D106" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E106" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="107" spans="3:5">
       <c r="C107">
         <v>40</v>
+      </c>
+      <c r="D107" t="s">
+        <v>9</v>
+      </c>
+      <c r="E107" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="108" spans="3:5">
+      <c r="D108" s="3">
+        <f>COUNTIF(D2:D107,"○")/COUNTA(D2:D107)</f>
+        <v>0.59433962264150941</v>
+      </c>
+      <c r="E108" s="3">
+        <f>COUNTIF(D68:D107,"○")/COUNTA(D68:D107)</f>
+        <v>0.67500000000000004</v>
       </c>
     </row>
   </sheetData>

--- a/JSTQB_Foundation.xlsx
+++ b/JSTQB_Foundation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ドキュメント\その他\eラーニング\JSTQB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FC13ED8-4729-4ED3-AD8B-8683ED6055B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F9B050C-0EF9-4E9F-877A-8FD98F7CC6C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="15">
   <si>
     <t>典型的なテストの目的として、誤っているものはどれか。次の選択肢の中から1つ選びなさい。</t>
     <phoneticPr fontId="1"/>
@@ -502,13 +502,16 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CFBD2AC0-38EC-4B9C-A0BF-1559C25A244C}">
   <sheetPr codeName="Sheet3"/>
-  <dimension ref="B2:F108"/>
+  <dimension ref="B2:I108"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
-    <col min="6" max="6" width="10.1640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.6640625" hidden="1" customWidth="1"/>
+    <col min="6" max="6" width="10.1640625" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="8.6640625" customWidth="1"/>
+    <col min="9" max="9" width="10.25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:6">
+    <row r="2" spans="2:9">
       <c r="B2">
         <v>1</v>
       </c>
@@ -525,7 +528,7 @@
         <v>46075</v>
       </c>
     </row>
-    <row r="3" spans="2:6">
+    <row r="3" spans="2:9">
       <c r="C3">
         <v>2</v>
       </c>
@@ -536,7 +539,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="2:6">
+    <row r="4" spans="2:9">
       <c r="C4">
         <v>3</v>
       </c>
@@ -547,7 +550,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="2:6">
+    <row r="5" spans="2:9">
       <c r="C5">
         <v>4</v>
       </c>
@@ -557,8 +560,17 @@
       <c r="E5" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="6" spans="2:6">
+      <c r="G5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H5" t="s">
+        <v>10</v>
+      </c>
+      <c r="I5" s="1">
+        <v>46092</v>
+      </c>
+    </row>
+    <row r="6" spans="2:9">
       <c r="C6">
         <v>5</v>
       </c>
@@ -569,7 +581,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="2:6">
+    <row r="7" spans="2:9">
       <c r="C7">
         <v>6</v>
       </c>
@@ -579,8 +591,17 @@
       <c r="E7" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="8" spans="2:6">
+      <c r="G7" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H7" t="s">
+        <v>11</v>
+      </c>
+      <c r="I7" s="1">
+        <v>46092</v>
+      </c>
+    </row>
+    <row r="8" spans="2:9">
       <c r="C8">
         <v>7</v>
       </c>
@@ -590,8 +611,17 @@
       <c r="E8" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="9" spans="2:6">
+      <c r="G8" t="s">
+        <v>9</v>
+      </c>
+      <c r="H8" t="s">
+        <v>12</v>
+      </c>
+      <c r="I8" s="1">
+        <v>46092</v>
+      </c>
+    </row>
+    <row r="9" spans="2:9">
       <c r="C9">
         <v>8</v>
       </c>
@@ -602,7 +632,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="2:6">
+    <row r="10" spans="2:9">
       <c r="C10">
         <v>9</v>
       </c>
@@ -612,8 +642,17 @@
       <c r="E10" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="11" spans="2:6">
+      <c r="G10" t="s">
+        <v>9</v>
+      </c>
+      <c r="H10" t="s">
+        <v>11</v>
+      </c>
+      <c r="I10" s="1">
+        <v>46092</v>
+      </c>
+    </row>
+    <row r="11" spans="2:9">
       <c r="C11">
         <v>10</v>
       </c>
@@ -623,8 +662,17 @@
       <c r="E11" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="12" spans="2:6">
+      <c r="G11" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H11" t="s">
+        <v>10</v>
+      </c>
+      <c r="I11" s="1">
+        <v>46092</v>
+      </c>
+    </row>
+    <row r="12" spans="2:9">
       <c r="C12">
         <v>11</v>
       </c>
@@ -634,8 +682,17 @@
       <c r="E12" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="13" spans="2:6">
+      <c r="G12" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H12" t="s">
+        <v>10</v>
+      </c>
+      <c r="I12" s="1">
+        <v>46092</v>
+      </c>
+    </row>
+    <row r="13" spans="2:9">
       <c r="C13">
         <v>12</v>
       </c>
@@ -645,8 +702,17 @@
       <c r="E13" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="14" spans="2:6">
+      <c r="G13" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H13" t="s">
+        <v>10</v>
+      </c>
+      <c r="I13" s="1">
+        <v>46092</v>
+      </c>
+    </row>
+    <row r="14" spans="2:9">
       <c r="C14">
         <v>13</v>
       </c>
@@ -656,8 +722,17 @@
       <c r="E14" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="15" spans="2:6">
+      <c r="G14" t="s">
+        <v>9</v>
+      </c>
+      <c r="H14" t="s">
+        <v>12</v>
+      </c>
+      <c r="I14" s="1">
+        <v>46092</v>
+      </c>
+    </row>
+    <row r="15" spans="2:9">
       <c r="C15">
         <v>14</v>
       </c>
@@ -668,7 +743,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="16" spans="2:6">
+    <row r="16" spans="2:9">
       <c r="C16">
         <v>15</v>
       </c>
@@ -679,7 +754,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="17" spans="2:6">
+    <row r="17" spans="2:9">
       <c r="C17">
         <v>16</v>
       </c>
@@ -690,7 +765,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="18" spans="2:6">
+    <row r="18" spans="2:9">
       <c r="B18">
         <v>2</v>
       </c>
@@ -706,8 +781,17 @@
       <c r="F18" s="1">
         <v>46076</v>
       </c>
-    </row>
-    <row r="19" spans="2:6">
+      <c r="G18" t="s">
+        <v>9</v>
+      </c>
+      <c r="H18" t="s">
+        <v>13</v>
+      </c>
+      <c r="I18" s="1">
+        <v>46092</v>
+      </c>
+    </row>
+    <row r="19" spans="2:9">
       <c r="C19">
         <v>2</v>
       </c>
@@ -718,7 +802,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="20" spans="2:6">
+    <row r="20" spans="2:9">
       <c r="C20">
         <v>3</v>
       </c>
@@ -729,7 +813,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="21" spans="2:6">
+    <row r="21" spans="2:9">
       <c r="C21">
         <v>4</v>
       </c>
@@ -740,7 +824,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="22" spans="2:6">
+    <row r="22" spans="2:9">
       <c r="C22">
         <v>5</v>
       </c>
@@ -751,7 +835,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="23" spans="2:6">
+    <row r="23" spans="2:9">
       <c r="C23">
         <v>6</v>
       </c>
@@ -761,8 +845,17 @@
       <c r="E23" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="24" spans="2:6">
+      <c r="G23" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H23" t="s">
+        <v>12</v>
+      </c>
+      <c r="I23" s="1">
+        <v>46093</v>
+      </c>
+    </row>
+    <row r="24" spans="2:9">
       <c r="C24">
         <v>7</v>
       </c>
@@ -773,7 +866,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="25" spans="2:6">
+    <row r="25" spans="2:9">
       <c r="C25">
         <v>8</v>
       </c>
@@ -783,8 +876,17 @@
       <c r="E25" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="26" spans="2:6">
+      <c r="G25" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H25" t="s">
+        <v>12</v>
+      </c>
+      <c r="I25" s="1">
+        <v>46093</v>
+      </c>
+    </row>
+    <row r="26" spans="2:9">
       <c r="C26">
         <v>9</v>
       </c>
@@ -795,7 +897,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="27" spans="2:6">
+    <row r="27" spans="2:9">
       <c r="C27">
         <v>10</v>
       </c>
@@ -806,7 +908,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="28" spans="2:6">
+    <row r="28" spans="2:9">
       <c r="C28">
         <v>11</v>
       </c>
@@ -816,8 +918,17 @@
       <c r="E28" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="29" spans="2:6">
+      <c r="G28" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H28" t="s">
+        <v>10</v>
+      </c>
+      <c r="I28" s="1">
+        <v>46093</v>
+      </c>
+    </row>
+    <row r="29" spans="2:9">
       <c r="C29">
         <v>12</v>
       </c>
@@ -827,8 +938,17 @@
       <c r="E29" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="30" spans="2:6">
+      <c r="G29" t="s">
+        <v>9</v>
+      </c>
+      <c r="H29" t="s">
+        <v>11</v>
+      </c>
+      <c r="I29" s="1">
+        <v>46093</v>
+      </c>
+    </row>
+    <row r="30" spans="2:9">
       <c r="C30">
         <v>13</v>
       </c>
@@ -839,7 +959,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="31" spans="2:6">
+    <row r="31" spans="2:9">
       <c r="C31">
         <v>14</v>
       </c>
@@ -849,8 +969,17 @@
       <c r="E31" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="32" spans="2:6">
+      <c r="G31" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H31" t="s">
+        <v>11</v>
+      </c>
+      <c r="I31" s="1">
+        <v>46093</v>
+      </c>
+    </row>
+    <row r="32" spans="2:9">
       <c r="C32">
         <v>15</v>
       </c>
@@ -861,7 +990,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="33" spans="2:6">
+    <row r="33" spans="2:9">
       <c r="C33">
         <v>16</v>
       </c>
@@ -872,7 +1001,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="34" spans="2:6">
+    <row r="34" spans="2:9">
       <c r="B34">
         <v>3</v>
       </c>
@@ -888,8 +1017,17 @@
       <c r="F34" s="1">
         <v>46081</v>
       </c>
-    </row>
-    <row r="35" spans="2:6">
+      <c r="G34" t="s">
+        <v>9</v>
+      </c>
+      <c r="H34" t="s">
+        <v>12</v>
+      </c>
+      <c r="I34" s="1">
+        <v>46094</v>
+      </c>
+    </row>
+    <row r="35" spans="2:9">
       <c r="C35">
         <v>2</v>
       </c>
@@ -899,8 +1037,17 @@
       <c r="E35" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="36" spans="2:6">
+      <c r="G35" t="s">
+        <v>9</v>
+      </c>
+      <c r="H35" t="s">
+        <v>12</v>
+      </c>
+      <c r="I35" s="1">
+        <v>46094</v>
+      </c>
+    </row>
+    <row r="36" spans="2:9">
       <c r="C36">
         <v>3</v>
       </c>
@@ -911,7 +1058,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="37" spans="2:6">
+    <row r="37" spans="2:9">
       <c r="C37">
         <v>4</v>
       </c>
@@ -922,7 +1069,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="38" spans="2:6">
+    <row r="38" spans="2:9">
       <c r="C38">
         <v>5</v>
       </c>
@@ -933,7 +1080,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="39" spans="2:6">
+    <row r="39" spans="2:9">
       <c r="C39">
         <v>6</v>
       </c>
@@ -943,8 +1090,17 @@
       <c r="E39" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="40" spans="2:6">
+      <c r="G39" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H39" t="s">
+        <v>13</v>
+      </c>
+      <c r="I39" s="1">
+        <v>46094</v>
+      </c>
+    </row>
+    <row r="40" spans="2:9">
       <c r="C40">
         <v>7</v>
       </c>
@@ -954,8 +1110,17 @@
       <c r="E40" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="41" spans="2:6">
+      <c r="G40" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H40" t="s">
+        <v>13</v>
+      </c>
+      <c r="I40" s="1">
+        <v>46094</v>
+      </c>
+    </row>
+    <row r="41" spans="2:9">
       <c r="C41">
         <v>8</v>
       </c>
@@ -966,7 +1131,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="42" spans="2:6">
+    <row r="42" spans="2:9">
       <c r="B42">
         <v>4</v>
       </c>
@@ -982,8 +1147,17 @@
       <c r="F42" s="1">
         <v>46088</v>
       </c>
-    </row>
-    <row r="43" spans="2:6">
+      <c r="G42" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H42" t="s">
+        <v>11</v>
+      </c>
+      <c r="I42" s="1">
+        <v>46094</v>
+      </c>
+    </row>
+    <row r="43" spans="2:9">
       <c r="C43">
         <v>2</v>
       </c>
@@ -994,7 +1168,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="44" spans="2:6">
+    <row r="44" spans="2:9">
       <c r="C44">
         <v>3</v>
       </c>
@@ -1004,8 +1178,17 @@
       <c r="E44" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="45" spans="2:6">
+      <c r="G44" t="s">
+        <v>9</v>
+      </c>
+      <c r="H44" t="s">
+        <v>12</v>
+      </c>
+      <c r="I44" s="1">
+        <v>46094</v>
+      </c>
+    </row>
+    <row r="45" spans="2:9">
       <c r="C45">
         <v>4</v>
       </c>
@@ -1015,8 +1198,17 @@
       <c r="E45" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="46" spans="2:6">
+      <c r="G45" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H45" t="s">
+        <v>10</v>
+      </c>
+      <c r="I45" s="1">
+        <v>46094</v>
+      </c>
+    </row>
+    <row r="46" spans="2:9">
       <c r="C46">
         <v>5</v>
       </c>
@@ -1027,7 +1219,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="47" spans="2:6">
+    <row r="47" spans="2:9">
       <c r="C47">
         <v>6</v>
       </c>
@@ -1038,7 +1230,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="48" spans="2:6">
+    <row r="48" spans="2:9">
       <c r="C48">
         <v>7</v>
       </c>
@@ -1601,7 +1793,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="97" spans="3:5">
+    <row r="97" spans="3:8">
       <c r="C97">
         <v>30</v>
       </c>
@@ -1612,7 +1804,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="98" spans="3:5">
+    <row r="98" spans="3:8">
       <c r="C98">
         <v>31</v>
       </c>
@@ -1623,7 +1815,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="99" spans="3:5">
+    <row r="99" spans="3:8">
       <c r="C99">
         <v>32</v>
       </c>
@@ -1634,7 +1826,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="100" spans="3:5">
+    <row r="100" spans="3:8">
       <c r="C100">
         <v>33</v>
       </c>
@@ -1645,7 +1837,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="101" spans="3:5">
+    <row r="101" spans="3:8">
       <c r="C101">
         <v>34</v>
       </c>
@@ -1656,7 +1848,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="102" spans="3:5">
+    <row r="102" spans="3:8">
       <c r="C102">
         <v>35</v>
       </c>
@@ -1667,7 +1859,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="103" spans="3:5">
+    <row r="103" spans="3:8">
       <c r="C103">
         <v>36</v>
       </c>
@@ -1678,7 +1870,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="104" spans="3:5">
+    <row r="104" spans="3:8">
       <c r="C104">
         <v>37</v>
       </c>
@@ -1689,7 +1881,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="105" spans="3:5">
+    <row r="105" spans="3:8">
       <c r="C105">
         <v>38</v>
       </c>
@@ -1700,7 +1892,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="106" spans="3:5">
+    <row r="106" spans="3:8">
       <c r="C106">
         <v>39</v>
       </c>
@@ -1711,7 +1903,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="107" spans="3:5">
+    <row r="107" spans="3:8">
       <c r="C107">
         <v>40</v>
       </c>
@@ -1722,7 +1914,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="108" spans="3:5">
+    <row r="108" spans="3:8">
       <c r="D108" s="3">
         <f>COUNTIF(D2:D107,"○")/COUNTA(D2:D107)</f>
         <v>0.59433962264150941</v>
@@ -1730,6 +1922,14 @@
       <c r="E108" s="3">
         <f>COUNTIF(D68:D107,"○")/COUNTA(D68:D107)</f>
         <v>0.67500000000000004</v>
+      </c>
+      <c r="G108" s="3">
+        <f>COUNTIF(G2:G107,"○")/COUNTA(G2:G107)</f>
+        <v>0.42857142857142855</v>
+      </c>
+      <c r="H108" s="3" t="e">
+        <f>COUNTIF(G68:G107,"○")/COUNTA(G68:G107)</f>
+        <v>#DIV/0!</v>
       </c>
     </row>
   </sheetData>

--- a/JSTQB_Foundation.xlsx
+++ b/JSTQB_Foundation.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27932"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ドキュメント\その他\eラーニング\JSTQB\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ドキュメント\勉強\資格(取得)\JSTQB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F9B050C-0EF9-4E9F-877A-8FD98F7CC6C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0700C502-3573-4E50-9527-36D8CFB4D9EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="テス友" sheetId="1" r:id="rId1"/>
@@ -33,12 +33,15 @@
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="736" uniqueCount="254">
   <si>
     <t>典型的なテストの目的として、誤っているものはどれか。次の選択肢の中から1つ選びなさい。</t>
     <phoneticPr fontId="1"/>
@@ -56,39 +59,893 @@
     <t>求められるテスト対象のカバレッジを確保する</t>
   </si>
   <si>
+    <t>B</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>D</t>
+  </si>
+  <si>
+    <t>○</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>B</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
     <t>A</t>
-  </si>
-  <si>
-    <t>B</t>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>C</t>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>D</t>
-  </si>
-  <si>
-    <t>○</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>B</t>
-    <phoneticPr fontId="1"/>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>✕</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>テストの原則として、誤っているものはどれか。次の選択肢の中から1つ選びなさい。</t>
   </si>
   <si>
     <t>A</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>C</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>D</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>✕</t>
+    <t>全数テストは不可能</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>欠陥の偏在</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>テストはコンテキスト次第</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>コンポーネント統合テストの主な目的はどれか。次の選択肢の中から1つ選びなさい。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>コンポーネント間のインターフェースと相互処理をテストすること</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ユーザーのビジネスニーズを満たすことを確認すること</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>DevOpsのテストに関する利点や課題について、誤っているものはどれか。次の選択肢の中から1つ選びなさい。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>CI/CDツールの導入と保守をしなければならない</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>テスト自動化は、追加のリソースを必要とし、確立と保守が困難な場合がある</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>メンテナンステストのきっかけとして、最も適切ではないものはどれか。次の選択肢の中から1つ選びなさい。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>迅速なフィードバックを得ることができない</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>非機能品質特性（性能、信頼性など）に対する観点が増える</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>システム全体の振る舞いや能力をテストすること</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>コンポーネントの単独でのテストを行うこと</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>テストは欠陥がないことを示す</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>データのバックアップの実施</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>計画的な機能拡張（リリースベース）</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>システムの修正を伴う変更</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>運用環境の更新や移行</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>レビュープロセスにおける役割と責務について、最も不適切なものはどれか。次の選択肢の中から1つ選びなさい。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>マネージャーは、レビューのためのリソースを提供する責任がある</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>モデレーターは、レビューミーティングを運営し、安全な環境を提供する責任がある</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>書記は、レビューアの役割を果たす責任がある</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>レビューリーダーは、レビューの全体的な責任を負い、参加者を決定する</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>テクニカルレビューの目的として、最も不適切なものはどれか。次の選択肢の中から1つ選びなさい。</t>
+  </si>
+  <si>
+    <t>新しいアイデアの創出</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>不正の検出と品質評価</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>作成者のモチベーションの向上と改善</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>レビューアの教育</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>インスペクションの目的として、最も不適切なものはどれか。次の選択肢の中から1つ選びなさい。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>品質評価や作業成果物に対する信頼の積み上げ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>不正を最大数発見すること</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ウォークスループロセスの改善</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>オンラインショッピングサイトの支払い機能をテストする際に、有効なクレジットカードを使用する場合と、無効なカードを使用する場合でテストする。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>その際に使用されるテスト技法で最も適切なものはどれか。次の選択肢の中から1つ選びなさい。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>状態遷移テスト</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>境界値分析</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>デシジョンテーブルテスト</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>同値分割法</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>経験ベースのテスト技法に該当しないものとして、最も適切なものはどれか。次の選択肢の中から1つ選びなさい。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>エラー推測</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>チェックリストベースドテスト</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>探索的テスト</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t xml:space="preserve">	ユーザビリティテスト</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>エラー推測におけるフォールト攻撃のアプローチとして、最も適切なものはどれか。次の選択肢の中から1つ選びなさい。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>モデルベースのテスト</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ランダムなテスト</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ユーザーインタビュー</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>系統的なアプローチ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>探索的テストにおけるセッションベースドテストの特徴で、最も適切なものはどれか。次の選択肢の中から1つ選びなさい。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>テスト結果の文書化が不要</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>テスト担当者の経験が不要</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>テスト目的が事前に決められる</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>予め決められた時間枠内で行われる</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>受け入れテスト駆動開発（ATDD）の最初のステップについて、最も適切なものはどれか。次の選択肢の中から1つ選びなさい。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ユーザーストーリーの実装</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>テストケースの実行</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ユーザーストーリーの評価</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>仕様化のワークショップ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>外挿に関する説明の中で、最も適切なものはどれか。次の選択肢の中から1つ選びなさい。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>外挿では、データ収集をするために、プロジェクトの早い段階で測定が行われる</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>外挿では、３つの推定値を使って見積もる</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>外挿では、専門家による手法を使用して見積もる</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>外挿では、組織内のプロジェクトの比率を使用して見積もる</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>テストケースの優先順位付けに関する説明の中で、リスクに基づく優先順位付けの特徴はどれか。次の選択肢の中から1つ選びなさい。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>テストケースの実行順序はリスクの対処方法に基づいている</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>テストケースの実行順序はリスクの特定範囲に基づいている</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>テストケースの実行順序はリスク分析の結果に基づいている</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>テストケースの実行順序はリスク検討の結果に基づいている</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>リスクの特徴の説明として、最も適切なものはどれか。次の選択肢の中から1つ選びなさい。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>リスクの可能性は、リスクがもたらす悪影響を示し、影響は顕在化する確率を示す</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>リスクの可能性、影響ともリスクの顕在化がもたらす結果を示す</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>リスクの可能性、影響ともリスクが顕在化する確率を示す</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>リスクの可能性は、顕在化する確率を示し、影響はリスクがもたらす結果を示す</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>テスト計画におけるテストアプローチに含まれるものとして、最も不適切なものはどれか。次の選択肢の中から1つ選びなさい。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>テストの独立性</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>収集すべきメトリック</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>テストスケジュール</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>テスト成果物</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>イテレーション計画に関わるテスト担当者の役割について、正しいものはどれか。次の選択肢の中から1つ選びなさい。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ユーザーストーリーの試験性を判断する</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ユーザーストーリーの詳細な欠陥分析に参加する</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ユーザーストーリーの詳細な自動化分析に参加する</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>すべての欠陥の工数を見積る</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>静的テストツールがサポートする主な活動として、最も適切なものはどれか。次の選択肢の中から1つ選びなさい。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>レビューを行うテスト担当者をサポートする</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ステークホルダー間のコミュニケーションをサポートする</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>マネジメントを行うテストマネージャーをサポートする</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>テストケース、テストデータ、テストプロシジャーの作成を促進する</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>テスト実行とカバレッジツールについて、最も不適切なものはどれか。次の選択肢の中から1つ選びなさい。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>テストスクリプトの実行結果を収集し、テストのカバレッジを評価する</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>静的テストに特化したツールであり、テストケースの設計や実行をサポートする</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>テスト実行及びカバレッジ計測を容易にする</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>テストの自動化を支援し、テスト実行時のデータを収集してカバレッジを評価する</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>テスト自動化の潜在的なリスクについて、(A)(B)に当てはまる、正しい語句の組み合わせはどれか。次の選択肢の中から1つ選びなさい。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ツールの(A)、テストスクリプトの(B)、既存の手動テストプロセスの変更に必要な時間、コスト、労力の見積りが正確でない。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>(A)実行  (B)保守</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>(A)導入  (B)作成</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>(A)導入  (B)保守</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>(A)実行  (B)作成</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>DevOpsツールが提供する機能について、最も不適切なものはどれか。次の選択肢の中から1つ選びなさい。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>マネジメントツールの統合</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>テストの実行とその結果の分析</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ビルドプロセスの自動化</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ワークフロー追跡</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>下記の語群のうち、マネジメントツールの使用によりマネジメントが容易になる、正しい組み合わせはどれか。次の選択肢の中から1つ選びなさい。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>(A)SDLC (B)要件 (C)人員 (D)故障 (E)構成</t>
+  </si>
+  <si>
+    <t>(B)と(D)</t>
+  </si>
+  <si>
+    <t>(D)と(E)</t>
+  </si>
+  <si>
+    <t>(A)と(B)</t>
+  </si>
+  <si>
+    <t>(A)と(C)</t>
+  </si>
+  <si>
+    <t>同値分割法において、カバレッジアイテムとして扱われる同値パーティションの範囲について、最も適切なものはどれか。次の選択肢の中から1つ選びなさい。</t>
+  </si>
+  <si>
+    <t>無限のパーティション</t>
+  </si>
+  <si>
+    <t>有効パーティションのみ</t>
+  </si>
+  <si>
+    <t>すべての同値パーティション</t>
+  </si>
+  <si>
+    <t>無効パーティションのみ</t>
+  </si>
+  <si>
+    <t>イテレーティブ開発モデルやインクリメンタル開発モデルにおいて、各イテレーションに関連するテスト活動はどれか。次の選択肢の中から1つ選びなさい。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>静的テストのみの実施</t>
+  </si>
+  <si>
+    <t>動的テストのみの実施</t>
+  </si>
+  <si>
+    <t>静的テストと動的テストの両方を実施することがある</t>
+  </si>
+  <si>
+    <t>要件レビューの実施</t>
+  </si>
+  <si>
+    <t>探索的テストを他のテスト技法と併用する場合、最も一般的なものはどれか。次の選択肢の中から1つ選びなさい。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>エラー推測と併用する</t>
+  </si>
+  <si>
+    <t>チェックリストベースドテストと併用する</t>
+  </si>
+  <si>
+    <t>同値分割法と併用する</t>
+  </si>
+  <si>
+    <t>ステートメントテストと併用する</t>
+  </si>
+  <si>
+    <t>ユーザーストーリーにおいて、重要な側面はどれか。次の選択肢の中から1つ選びなさい。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>会話</t>
+  </si>
+  <si>
+    <t>全て正しい</t>
+  </si>
+  <si>
+    <t>確認</t>
+  </si>
+  <si>
+    <t>カード</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>テスト分析の作業成果物として、最も適切なものはどれか。次の選択肢の中から1つ選びなさい。</t>
+  </si>
+  <si>
+    <t>ユーザーストーリー</t>
+  </si>
+  <si>
+    <t>テストスクリプト</t>
+  </si>
+  <si>
+    <t>テスト条件</t>
+  </si>
+  <si>
+    <t>リグレッションテストのログ</t>
+  </si>
+  <si>
+    <t>ウォークスルーの目的として、最も不適切なものはどれか。次の選択肢の中から1つ選びなさい。</t>
+  </si>
+  <si>
+    <t>不正の検出</t>
+  </si>
+  <si>
+    <t>メトリクスの収集</t>
+  </si>
+  <si>
+    <t>作成者のモチベーションの向上と改善</t>
+  </si>
+  <si>
+    <t>新しいアイデアの創出</t>
+  </si>
+  <si>
+    <t>プロダクトリスク分析の目的はどれか。次の選択肢の中から適切なものを1つ選びなさい。</t>
+  </si>
+  <si>
+    <t>プロダクトリスクを最大化する方法を見つけること</t>
+  </si>
+  <si>
+    <t>プロダクトリスクのレベルを変更すること</t>
+  </si>
+  <si>
+    <t>プロダクトリスクの残存レベルを最小化する方法を見つけること</t>
+  </si>
+  <si>
+    <t>プロダクトリスクを無視すること</t>
+  </si>
+  <si>
+    <t>メンテナンステストのきっかけとなるものはどれか。次の選択肢の中から1つ選びなさい。</t>
+  </si>
+  <si>
+    <t>計画的な機能拡張や修正を伴う変更</t>
+  </si>
+  <si>
+    <t>システムの停止</t>
+  </si>
+  <si>
+    <t>予期せぬハードウェア故障</t>
+  </si>
+  <si>
+    <t>プロジェクトの開始</t>
+  </si>
+  <si>
+    <t>ふりかえりの結果は通常、どのようなレポートの一部となることが多いか。次の選択肢の中から1つ選びなさい。</t>
+  </si>
+  <si>
+    <t>デザインドキュメント</t>
+  </si>
+  <si>
+    <t>リスク分析レポート</t>
+  </si>
+  <si>
+    <t>テスト完了レポート</t>
+  </si>
+  <si>
+    <t>開発進捗レポート</t>
+  </si>
+  <si>
+    <t>ホワイトボックステストについて、正しい記述はどれか。次の選択肢の中から1つ選びなさい。</t>
+  </si>
+  <si>
+    <t>ホワイトボックステストは、ユーザーがシステムをどのように使用するかを評価するテスト手法です</t>
+  </si>
+  <si>
+    <t>ホワイトボックステストは、システムの外部にあるドキュメントからテストを導き出すテスト手法です</t>
+  </si>
+  <si>
+    <t>ホワイトボックステストは、システムの内部構造や実装に基づいてテストを導き出すテスト手法です</t>
+  </si>
+  <si>
+    <t>ホワイトボックステストは、主にシステムの動作速度やリソース使用量などを評価するテスト手法です</t>
+  </si>
+  <si>
+    <t>シフトレフトアプローチにおける自動化プロセスとして、最も適切なものはどれか。次の選択肢の中から1つ選びなさい</t>
+  </si>
+  <si>
+    <t>動的テストをすべて手動で行う</t>
+  </si>
+  <si>
+    <t>コード実装後にテストケースを作成する</t>
+  </si>
+  <si>
+    <t>ソースコードの静的解析を手動で行う</t>
+  </si>
+  <si>
+    <t>ソースコードをリポジトリにサブミットする際に自動コンポーネントテストを実行する</t>
+  </si>
+  <si>
+    <t>アジャイルプロジェクトにおいて、手動テストで主に使用されるテスト技法はどれか。次の選択肢の中から1つ選びなさい。</t>
+  </si>
+  <si>
+    <t>テスト自動化の技法</t>
+  </si>
+  <si>
+    <t>経験ベースのテスト技法</t>
+  </si>
+  <si>
+    <t>大規模なテスト分析とテスト設計を必要とする技法</t>
+  </si>
+  <si>
+    <t>静的テスト技法</t>
+  </si>
+  <si>
+    <t>3値BVAはテストケースの数が少ない</t>
+  </si>
+  <si>
+    <t>3値BVAは開発者のエラーを考慮しない</t>
+  </si>
+  <si>
+    <t>3値BVAは境界値の前後の値も考慮する</t>
+  </si>
+  <si>
+    <t>3値BVAは2値BVAよりも単純な技法である</t>
+  </si>
+  <si>
+    <t>3値BVAが、2値BVAよりも厳密である理由で、最も適切なものはどれか。次の選択肢の中から1つ選びなさい。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>テスト担当者がテスト結果を伝える際に重要なこととして、最も適切なものはどれか。次の選択肢の中から1つ選びなさい。</t>
+  </si>
+  <si>
+    <t>建設的な方法で情報を伝える</t>
+  </si>
+  <si>
+    <t>欠陥や故障に関するものは最優先となるため、建設的な方法よりもスピード、かみ砕いた内容を意識し伝える</t>
+  </si>
+  <si>
+    <t>わかりやすく口頭でのみ伝える</t>
+  </si>
+  <si>
+    <t>プロダクトやその作成者に対する批判と受け取られる可能性があっても、プロジェクトに影響を与えないよう包み隠すことなく伝える</t>
+  </si>
+  <si>
+    <t>テストが主導するソフトウェア開発において、システム設計プロセスの一環として、受け入れ基準からテストを導き出す特徴を持つものはどれか。次の選択肢の中から1つ選びなさい。</t>
+  </si>
+  <si>
+    <t>静的テスト駆動開発（STDD）</t>
+  </si>
+  <si>
+    <t>受け入れテスト駆動開発（ATDD）</t>
+  </si>
+  <si>
+    <t>振る舞い駆動開発（BDD）</t>
+  </si>
+  <si>
+    <t>テスト駆動開発（TDD）</t>
+  </si>
+  <si>
+    <t>インスペクションの特徴として、最も適切なものはどれか。次の選択肢の中から1つ選びなさい。</t>
+  </si>
+  <si>
+    <t>作成者が主導する</t>
+  </si>
+  <si>
+    <t>非形式的なレビュー</t>
+  </si>
+  <si>
+    <t>テクニカルレビューの一種</t>
+  </si>
+  <si>
+    <t>最も形式的なレビュー</t>
+  </si>
+  <si>
+    <t>非形式的レビューの主な目的として、最も適切なものはどれか。次の選択肢の中から1つ選びなさい。</t>
+  </si>
+  <si>
+    <t>形式的な文書化</t>
+  </si>
+  <si>
+    <t>レビューアの教育</t>
+  </si>
+  <si>
+    <t>テストや操作で見かけるインシデントの一覧がある。「故障」といえるのはどれか。次の選択肢の中から１つ選びなさい。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ダイアログボックスのオプションを選択した時、製品が異常終了した。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>間違ったバージョンのソースコードをビルドした。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>間違った入力変数を使用した計算アルゴリズムを使用した。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>開発者は計算に関する要件のアルゴリズムを誤った解釈をした。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>次の説明においてテストとデバッグの違いを最も適切に説明しているのはどれか。次の選択肢の中から１つ選びなさい。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>テストは欠陥を除去する。デバッグは故障の原因を特定する。</t>
+  </si>
+  <si>
+    <t>動的テストは故障の原因を防ぐ。デバッグは故障を除去する。</t>
+  </si>
+  <si>
+    <t>テストは欠陥から発生する故障を発見する。デバッグはソフトウェアの故障の原因を発見し、解析し、除去を行う。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>テストは欠陥を正確に指摘する。デバッグは欠陥を解析して、事前に除去できるように提案する。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ツールによる静的解析の主な利点の説明文として最も適切なものはどれか。次の選択肢の中から１つ選びなさい。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ツールによる静的解析は、手動によるテスト実行の前に欠陥を検出することができる。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ツールによる静的解析は、ビジネスアナリストや要求エンジニアが要件と一致しないソフトウェアのモデル（状態遷移図など）を構築することを防ぐ。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ツールによる静的解析により、ユーザ受け入れテストのテストケースが少なくなり、テスト実行の期間が短くなる。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ツールを使ってコードの静的解析を行うことで、開発者によるユニットテスト実施のニーズは減少する。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>次の制御フローグラフに示す３つのテストを実行する。</t>
+  </si>
+  <si>
+    <t>テストA：A,B,D,F,Gのパスをカバーする</t>
+  </si>
+  <si>
+    <t>テストB：A,C,F,Gのパスをカバーする</t>
+  </si>
+  <si>
+    <t>テストC：A,C,F,C,F,C,F,Gをカバーする</t>
+  </si>
+  <si>
+    <t>プロジェクトにおけるカバレッジ目標の一つに、100%デシジョンカバレッジがある。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>次のデシジョンカバレッジ目標に関する記述のうち、説明文として最も適切なものはどれか。次の選択肢の中から１つ選びなさい。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>判定（デシジョン／以下、判定）Dは完全にテストされていない。</t>
+  </si>
+  <si>
+    <t>100%デシジョンカバレッジを達成する。</t>
+  </si>
+  <si>
+    <t>判定Eは完全にテストされていない。</t>
+  </si>
+  <si>
+    <t>判定Fは完全にテストされていない。</t>
+  </si>
+  <si>
+    <t>客のクレジット信用枠を決定する銀行のアプリケーションがある。その金額の上限を決定するためのルールは複数存在しており、</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>このアプリケーションはそれらのルールに基づいて計算する。このアプリケーションのテストに最も適したブラックボックステスト設計技法を、</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>次の選択肢の中から１つ選びなさい。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>デシジョンテーブルテスト</t>
+  </si>
+  <si>
+    <t>状態遷移テスト</t>
+  </si>
+  <si>
+    <t>ユースケーステスト</t>
+  </si>
+  <si>
+    <t>同値分割法</t>
+  </si>
+  <si>
+    <t>以下は、ソフトウェア開発やテストの組織における改善目標のリストである。テスト活動の有効性を改善するこれらの目標のうち、</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>テスト管理ツールによって最も効果的に支援できるのはどれか。次の選択肢の中から１つ選びなさい。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>欠陥をより早期に解決することによって有効性を改善する。</t>
+  </si>
+  <si>
+    <t>要求やテスト、バグの間のトレーサビリティを構築することによって有効性を改善する。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>故障を識別するためのテスト能力を最適化することによって有効性を改善する。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>実行するテストケースの選択を自動化することによって有効性を改善する。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>テスト実行ツールの特徴に関する以下の記述のうち、キーワード駆動テスト実行ツールの特徴にもっとも当てはまるものはどれか。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>テスト結果を記録し、期待結果と比較することができる。</t>
+  </si>
+  <si>
+    <t>テスト入力データ、アクションワードや期待結果を含む表が、テスト対象システムの実行を制御する。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>テスト担当者の動作が、何度も繰り返すことができるようにスクリプトに記録される。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>テスト担当者の動作が、様々なテスト入力データによって実行できるように一般化されたスクリプトに記録される。</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -169,6 +1026,72 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>3371850</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>131445</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="図 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9D47E4B4-20B3-8BD9-5E45-7DE9BFC31C42}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="1173480" y="5486400"/>
+          <a:ext cx="3375660" cy="3573780"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -435,11 +1358,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="B2:D6"/>
+  <dimension ref="B2:D243"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
-    <col min="2" max="2" width="4.5" customWidth="1"/>
-    <col min="3" max="3" width="4.83203125" customWidth="1"/>
+    <col min="2" max="3" width="3.296875" customWidth="1"/>
+    <col min="4" max="4" width="85.3984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:4">
@@ -449,7 +1372,7 @@
     </row>
     <row r="3" spans="2:4">
       <c r="C3" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="D3" t="s">
         <v>1</v>
@@ -457,10 +1380,10 @@
     </row>
     <row r="4" spans="2:4">
       <c r="B4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D4" t="s">
         <v>2</v>
@@ -468,7 +1391,7 @@
     </row>
     <row r="5" spans="2:4">
       <c r="C5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D5" t="s">
         <v>3</v>
@@ -476,10 +1399,1585 @@
     </row>
     <row r="6" spans="2:4">
       <c r="C6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D6" t="s">
         <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="2:4">
+      <c r="B8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9" spans="2:4">
+      <c r="C9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10" spans="2:4">
+      <c r="B10" t="s">
+        <v>8</v>
+      </c>
+      <c r="C10" t="s">
+        <v>5</v>
+      </c>
+      <c r="D10" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="11" spans="2:4">
+      <c r="C11" t="s">
+        <v>6</v>
+      </c>
+      <c r="D11" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="12" spans="2:4">
+      <c r="C12" t="s">
+        <v>7</v>
+      </c>
+      <c r="D12" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="14" spans="2:4">
+      <c r="B14" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="15" spans="2:4">
+      <c r="C15" t="s">
+        <v>15</v>
+      </c>
+      <c r="D15" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="16" spans="2:4">
+      <c r="B16" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" t="s">
+        <v>5</v>
+      </c>
+      <c r="D16" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="17" spans="2:4">
+      <c r="C17" t="s">
+        <v>6</v>
+      </c>
+      <c r="D17" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="18" spans="2:4">
+      <c r="C18" t="s">
+        <v>7</v>
+      </c>
+      <c r="D18" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="20" spans="2:4">
+      <c r="B20" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="21" spans="2:4">
+      <c r="C21" t="s">
+        <v>15</v>
+      </c>
+      <c r="D21" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="22" spans="2:4">
+      <c r="B22" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" t="s">
+        <v>5</v>
+      </c>
+      <c r="D22" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="23" spans="2:4">
+      <c r="C23" t="s">
+        <v>6</v>
+      </c>
+      <c r="D23" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="24" spans="2:4">
+      <c r="C24" t="s">
+        <v>7</v>
+      </c>
+      <c r="D24" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="26" spans="2:4">
+      <c r="B26" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="27" spans="2:4">
+      <c r="B27" t="s">
+        <v>8</v>
+      </c>
+      <c r="C27" t="s">
+        <v>15</v>
+      </c>
+      <c r="D27" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="28" spans="2:4">
+      <c r="C28" t="s">
+        <v>5</v>
+      </c>
+      <c r="D28" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="29" spans="2:4">
+      <c r="C29" t="s">
+        <v>6</v>
+      </c>
+      <c r="D29" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="30" spans="2:4">
+      <c r="C30" t="s">
+        <v>7</v>
+      </c>
+      <c r="D30" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="32" spans="2:4">
+      <c r="B32" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="33" spans="2:4">
+      <c r="C33" t="s">
+        <v>15</v>
+      </c>
+      <c r="D33" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="34" spans="2:4">
+      <c r="C34" t="s">
+        <v>5</v>
+      </c>
+      <c r="D34" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="35" spans="2:4">
+      <c r="B35" t="s">
+        <v>8</v>
+      </c>
+      <c r="C35" t="s">
+        <v>6</v>
+      </c>
+      <c r="D35" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="36" spans="2:4">
+      <c r="C36" t="s">
+        <v>7</v>
+      </c>
+      <c r="D36" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="38" spans="2:4">
+      <c r="B38" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="39" spans="2:4">
+      <c r="C39" t="s">
+        <v>15</v>
+      </c>
+      <c r="D39" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="40" spans="2:4">
+      <c r="C40" t="s">
+        <v>5</v>
+      </c>
+      <c r="D40" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="41" spans="2:4">
+      <c r="C41" t="s">
+        <v>6</v>
+      </c>
+      <c r="D41" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="42" spans="2:4">
+      <c r="B42" t="s">
+        <v>8</v>
+      </c>
+      <c r="C42" t="s">
+        <v>7</v>
+      </c>
+      <c r="D42" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="44" spans="2:4">
+      <c r="B44" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="45" spans="2:4">
+      <c r="C45" t="s">
+        <v>15</v>
+      </c>
+      <c r="D45" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="46" spans="2:4">
+      <c r="C46" t="s">
+        <v>5</v>
+      </c>
+      <c r="D46" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="47" spans="2:4">
+      <c r="C47" t="s">
+        <v>6</v>
+      </c>
+      <c r="D47" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="48" spans="2:4">
+      <c r="B48" t="s">
+        <v>8</v>
+      </c>
+      <c r="C48" t="s">
+        <v>7</v>
+      </c>
+      <c r="D48" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="50" spans="2:4">
+      <c r="B50" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="51" spans="2:4">
+      <c r="B51" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="52" spans="2:4">
+      <c r="C52" t="s">
+        <v>15</v>
+      </c>
+      <c r="D52" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="53" spans="2:4">
+      <c r="C53" t="s">
+        <v>5</v>
+      </c>
+      <c r="D53" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="54" spans="2:4">
+      <c r="C54" t="s">
+        <v>6</v>
+      </c>
+      <c r="D54" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="55" spans="2:4">
+      <c r="B55" t="s">
+        <v>8</v>
+      </c>
+      <c r="C55" t="s">
+        <v>7</v>
+      </c>
+      <c r="D55" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="57" spans="2:4">
+      <c r="B57" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="58" spans="2:4">
+      <c r="C58" t="s">
+        <v>15</v>
+      </c>
+      <c r="D58" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="59" spans="2:4">
+      <c r="C59" t="s">
+        <v>5</v>
+      </c>
+      <c r="D59" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="60" spans="2:4">
+      <c r="C60" t="s">
+        <v>6</v>
+      </c>
+      <c r="D60" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="61" spans="2:4">
+      <c r="B61" t="s">
+        <v>8</v>
+      </c>
+      <c r="C61" t="s">
+        <v>7</v>
+      </c>
+      <c r="D61" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="63" spans="2:4">
+      <c r="B63" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="64" spans="2:4">
+      <c r="C64" t="s">
+        <v>15</v>
+      </c>
+      <c r="D64" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="65" spans="2:4">
+      <c r="C65" t="s">
+        <v>5</v>
+      </c>
+      <c r="D65" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="66" spans="2:4">
+      <c r="C66" t="s">
+        <v>6</v>
+      </c>
+      <c r="D66" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="67" spans="2:4">
+      <c r="B67" t="s">
+        <v>8</v>
+      </c>
+      <c r="C67" t="s">
+        <v>7</v>
+      </c>
+      <c r="D67" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="69" spans="2:4">
+      <c r="B69" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="70" spans="2:4">
+      <c r="C70" t="s">
+        <v>15</v>
+      </c>
+      <c r="D70" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="71" spans="2:4">
+      <c r="C71" t="s">
+        <v>5</v>
+      </c>
+      <c r="D71" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="72" spans="2:4">
+      <c r="C72" t="s">
+        <v>6</v>
+      </c>
+      <c r="D72" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="73" spans="2:4">
+      <c r="B73" t="s">
+        <v>8</v>
+      </c>
+      <c r="C73" t="s">
+        <v>7</v>
+      </c>
+      <c r="D73" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="75" spans="2:4">
+      <c r="B75" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="76" spans="2:4">
+      <c r="C76" t="s">
+        <v>15</v>
+      </c>
+      <c r="D76" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="77" spans="2:4">
+      <c r="C77" t="s">
+        <v>5</v>
+      </c>
+      <c r="D77" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="78" spans="2:4">
+      <c r="C78" t="s">
+        <v>6</v>
+      </c>
+      <c r="D78" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="79" spans="2:4">
+      <c r="B79" t="s">
+        <v>8</v>
+      </c>
+      <c r="C79" t="s">
+        <v>7</v>
+      </c>
+      <c r="D79" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="81" spans="2:4">
+      <c r="B81" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="82" spans="2:4">
+      <c r="B82" t="s">
+        <v>8</v>
+      </c>
+      <c r="C82" t="s">
+        <v>15</v>
+      </c>
+      <c r="D82" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="83" spans="2:4">
+      <c r="C83" t="s">
+        <v>5</v>
+      </c>
+      <c r="D83" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="84" spans="2:4">
+      <c r="C84" t="s">
+        <v>6</v>
+      </c>
+      <c r="D84" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="85" spans="2:4">
+      <c r="C85" t="s">
+        <v>7</v>
+      </c>
+      <c r="D85" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="87" spans="2:4">
+      <c r="B87" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="88" spans="2:4">
+      <c r="C88" t="s">
+        <v>15</v>
+      </c>
+      <c r="D88" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="89" spans="2:4">
+      <c r="C89" t="s">
+        <v>5</v>
+      </c>
+      <c r="D89" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="90" spans="2:4">
+      <c r="B90" t="s">
+        <v>8</v>
+      </c>
+      <c r="C90" t="s">
+        <v>6</v>
+      </c>
+      <c r="D90" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="91" spans="2:4">
+      <c r="C91" t="s">
+        <v>7</v>
+      </c>
+      <c r="D91" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="93" spans="2:4">
+      <c r="B93" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="94" spans="2:4">
+      <c r="C94" t="s">
+        <v>15</v>
+      </c>
+      <c r="D94" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="95" spans="2:4">
+      <c r="C95" t="s">
+        <v>5</v>
+      </c>
+      <c r="D95" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="96" spans="2:4">
+      <c r="C96" t="s">
+        <v>6</v>
+      </c>
+      <c r="D96" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="97" spans="2:4">
+      <c r="B97" t="s">
+        <v>8</v>
+      </c>
+      <c r="C97" t="s">
+        <v>7</v>
+      </c>
+      <c r="D97" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="99" spans="2:4">
+      <c r="B99" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="100" spans="2:4">
+      <c r="C100" t="s">
+        <v>15</v>
+      </c>
+      <c r="D100" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="101" spans="2:4">
+      <c r="C101" t="s">
+        <v>5</v>
+      </c>
+      <c r="D101" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="102" spans="2:4">
+      <c r="B102" t="s">
+        <v>8</v>
+      </c>
+      <c r="C102" t="s">
+        <v>6</v>
+      </c>
+      <c r="D102" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="103" spans="2:4">
+      <c r="C103" t="s">
+        <v>7</v>
+      </c>
+      <c r="D103" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="105" spans="2:4">
+      <c r="B105" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="106" spans="2:4">
+      <c r="B106" t="s">
+        <v>8</v>
+      </c>
+      <c r="C106" t="s">
+        <v>15</v>
+      </c>
+      <c r="D106" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="107" spans="2:4">
+      <c r="C107" t="s">
+        <v>5</v>
+      </c>
+      <c r="D107" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="108" spans="2:4">
+      <c r="C108" t="s">
+        <v>6</v>
+      </c>
+      <c r="D108" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="109" spans="2:4">
+      <c r="C109" t="s">
+        <v>7</v>
+      </c>
+      <c r="D109" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="111" spans="2:4">
+      <c r="B111" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="112" spans="2:4">
+      <c r="B112" t="s">
+        <v>8</v>
+      </c>
+      <c r="C112" t="s">
+        <v>15</v>
+      </c>
+      <c r="D112" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="113" spans="2:4">
+      <c r="C113" t="s">
+        <v>5</v>
+      </c>
+      <c r="D113" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="114" spans="2:4">
+      <c r="C114" t="s">
+        <v>6</v>
+      </c>
+      <c r="D114" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="115" spans="2:4">
+      <c r="C115" t="s">
+        <v>7</v>
+      </c>
+      <c r="D115" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="117" spans="2:4">
+      <c r="B117" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="118" spans="2:4">
+      <c r="C118" t="s">
+        <v>10</v>
+      </c>
+      <c r="D118" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="119" spans="2:4">
+      <c r="B119" t="s">
+        <v>8</v>
+      </c>
+      <c r="C119" t="s">
+        <v>5</v>
+      </c>
+      <c r="D119" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="120" spans="2:4">
+      <c r="C120" t="s">
+        <v>6</v>
+      </c>
+      <c r="D120" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="121" spans="2:4">
+      <c r="C121" t="s">
+        <v>7</v>
+      </c>
+      <c r="D121" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="123" spans="2:4">
+      <c r="B123" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="124" spans="2:4">
+      <c r="B124" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="125" spans="2:4">
+      <c r="C125" t="s">
+        <v>10</v>
+      </c>
+      <c r="D125" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="126" spans="2:4">
+      <c r="C126" t="s">
+        <v>5</v>
+      </c>
+      <c r="D126" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="127" spans="2:4">
+      <c r="B127" t="s">
+        <v>8</v>
+      </c>
+      <c r="C127" t="s">
+        <v>6</v>
+      </c>
+      <c r="D127" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="128" spans="2:4">
+      <c r="C128" t="s">
+        <v>7</v>
+      </c>
+      <c r="D128" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="130" spans="2:4">
+      <c r="B130" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="131" spans="2:4">
+      <c r="B131" t="s">
+        <v>8</v>
+      </c>
+      <c r="C131" t="s">
+        <v>10</v>
+      </c>
+      <c r="D131" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="132" spans="2:4">
+      <c r="C132" t="s">
+        <v>5</v>
+      </c>
+      <c r="D132" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="133" spans="2:4">
+      <c r="C133" t="s">
+        <v>6</v>
+      </c>
+      <c r="D133" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="134" spans="2:4">
+      <c r="C134" t="s">
+        <v>7</v>
+      </c>
+      <c r="D134" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="136" spans="2:4">
+      <c r="B136" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="137" spans="2:4">
+      <c r="B137" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="138" spans="2:4">
+      <c r="C138" t="s">
+        <v>10</v>
+      </c>
+      <c r="D138" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="139" spans="2:4">
+      <c r="C139" t="s">
+        <v>5</v>
+      </c>
+      <c r="D139" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="140" spans="2:4">
+      <c r="B140" t="s">
+        <v>8</v>
+      </c>
+      <c r="C140" t="s">
+        <v>6</v>
+      </c>
+      <c r="D140" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="141" spans="2:4">
+      <c r="C141" t="s">
+        <v>7</v>
+      </c>
+      <c r="D141" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="143" spans="2:4">
+      <c r="B143" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="144" spans="2:4">
+      <c r="C144" t="s">
+        <v>10</v>
+      </c>
+      <c r="D144" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="145" spans="2:4">
+      <c r="C145" t="s">
+        <v>5</v>
+      </c>
+      <c r="D145" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="146" spans="2:4">
+      <c r="B146" t="s">
+        <v>8</v>
+      </c>
+      <c r="C146" t="s">
+        <v>6</v>
+      </c>
+      <c r="D146" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="147" spans="2:4">
+      <c r="C147" t="s">
+        <v>7</v>
+      </c>
+      <c r="D147" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="149" spans="2:4">
+      <c r="B149" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="150" spans="2:4">
+      <c r="C150" t="s">
+        <v>10</v>
+      </c>
+      <c r="D150" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="151" spans="2:4">
+      <c r="C151" t="s">
+        <v>5</v>
+      </c>
+      <c r="D151" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="152" spans="2:4">
+      <c r="B152" t="s">
+        <v>8</v>
+      </c>
+      <c r="C152" t="s">
+        <v>6</v>
+      </c>
+      <c r="D152" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="153" spans="2:4">
+      <c r="C153" t="s">
+        <v>7</v>
+      </c>
+      <c r="D153" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="155" spans="2:4">
+      <c r="B155" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="156" spans="2:4">
+      <c r="C156" t="s">
+        <v>10</v>
+      </c>
+      <c r="D156" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="157" spans="2:4">
+      <c r="C157" t="s">
+        <v>5</v>
+      </c>
+      <c r="D157" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="158" spans="2:4">
+      <c r="B158" t="s">
+        <v>8</v>
+      </c>
+      <c r="C158" t="s">
+        <v>6</v>
+      </c>
+      <c r="D158" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="159" spans="2:4">
+      <c r="C159" t="s">
+        <v>7</v>
+      </c>
+      <c r="D159" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="161" spans="2:4">
+      <c r="B161" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="162" spans="2:4">
+      <c r="C162" t="s">
+        <v>147</v>
+      </c>
+      <c r="D162" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="163" spans="2:4">
+      <c r="B163" t="s">
+        <v>8</v>
+      </c>
+      <c r="C163" t="s">
+        <v>5</v>
+      </c>
+      <c r="D163" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="164" spans="2:4">
+      <c r="C164" t="s">
+        <v>6</v>
+      </c>
+      <c r="D164" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="165" spans="2:4">
+      <c r="C165" t="s">
+        <v>7</v>
+      </c>
+      <c r="D165" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="167" spans="2:4">
+      <c r="B167" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="168" spans="2:4">
+      <c r="C168" t="s">
+        <v>147</v>
+      </c>
+      <c r="D168" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="169" spans="2:4">
+      <c r="C169" t="s">
+        <v>5</v>
+      </c>
+      <c r="D169" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="170" spans="2:4">
+      <c r="B170" t="s">
+        <v>8</v>
+      </c>
+      <c r="C170" t="s">
+        <v>6</v>
+      </c>
+      <c r="D170" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="171" spans="2:4">
+      <c r="C171" t="s">
+        <v>7</v>
+      </c>
+      <c r="D171" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="173" spans="2:4">
+      <c r="B173" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="174" spans="2:4">
+      <c r="C174" t="s">
+        <v>147</v>
+      </c>
+      <c r="D174" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="175" spans="2:4">
+      <c r="B175" t="s">
+        <v>8</v>
+      </c>
+      <c r="C175" t="s">
+        <v>5</v>
+      </c>
+      <c r="D175" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="176" spans="2:4">
+      <c r="C176" t="s">
+        <v>6</v>
+      </c>
+      <c r="D176" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="177" spans="2:4">
+      <c r="C177" t="s">
+        <v>7</v>
+      </c>
+      <c r="D177" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="179" spans="2:4">
+      <c r="B179" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="180" spans="2:4">
+      <c r="C180" t="s">
+        <v>147</v>
+      </c>
+      <c r="D180" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="181" spans="2:4">
+      <c r="C181" t="s">
+        <v>5</v>
+      </c>
+      <c r="D181" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="182" spans="2:4">
+      <c r="B182" t="s">
+        <v>8</v>
+      </c>
+      <c r="C182" t="s">
+        <v>6</v>
+      </c>
+      <c r="D182" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="183" spans="2:4">
+      <c r="C183" t="s">
+        <v>7</v>
+      </c>
+      <c r="D183" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="185" spans="2:4">
+      <c r="B185" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="186" spans="2:4">
+      <c r="B186" t="s">
+        <v>8</v>
+      </c>
+      <c r="C186" t="s">
+        <v>147</v>
+      </c>
+      <c r="D186" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="187" spans="2:4">
+      <c r="C187" t="s">
+        <v>5</v>
+      </c>
+      <c r="D187" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="188" spans="2:4">
+      <c r="C188" t="s">
+        <v>6</v>
+      </c>
+      <c r="D188" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="189" spans="2:4">
+      <c r="C189" t="s">
+        <v>7</v>
+      </c>
+      <c r="D189" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="191" spans="2:4">
+      <c r="B191" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="192" spans="2:4">
+      <c r="C192" t="s">
+        <v>147</v>
+      </c>
+      <c r="D192" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="193" spans="2:4">
+      <c r="C193" t="s">
+        <v>5</v>
+      </c>
+      <c r="D193" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="194" spans="2:4">
+      <c r="B194" t="s">
+        <v>8</v>
+      </c>
+      <c r="C194" t="s">
+        <v>6</v>
+      </c>
+      <c r="D194" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="195" spans="2:4">
+      <c r="C195" t="s">
+        <v>7</v>
+      </c>
+      <c r="D195" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="197" spans="2:4">
+      <c r="B197" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="198" spans="2:4">
+      <c r="C198" t="s">
+        <v>147</v>
+      </c>
+      <c r="D198" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="199" spans="2:4">
+      <c r="C199" t="s">
+        <v>5</v>
+      </c>
+      <c r="D199" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="200" spans="2:4">
+      <c r="B200" t="s">
+        <v>8</v>
+      </c>
+      <c r="C200" t="s">
+        <v>6</v>
+      </c>
+      <c r="D200" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="201" spans="2:4">
+      <c r="C201" t="s">
+        <v>7</v>
+      </c>
+      <c r="D201" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="203" spans="2:4">
+      <c r="B203" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="204" spans="2:4">
+      <c r="C204" t="s">
+        <v>147</v>
+      </c>
+      <c r="D204" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="205" spans="2:4">
+      <c r="C205" t="s">
+        <v>5</v>
+      </c>
+      <c r="D205" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="206" spans="2:4">
+      <c r="C206" t="s">
+        <v>6</v>
+      </c>
+      <c r="D206" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="207" spans="2:4">
+      <c r="B207" t="s">
+        <v>8</v>
+      </c>
+      <c r="C207" t="s">
+        <v>7</v>
+      </c>
+      <c r="D207" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="209" spans="2:4">
+      <c r="B209" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="210" spans="2:4">
+      <c r="C210" t="s">
+        <v>147</v>
+      </c>
+      <c r="D210" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="211" spans="2:4">
+      <c r="B211" t="s">
+        <v>8</v>
+      </c>
+      <c r="C211" t="s">
+        <v>5</v>
+      </c>
+      <c r="D211" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="212" spans="2:4">
+      <c r="C212" t="s">
+        <v>6</v>
+      </c>
+      <c r="D212" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="213" spans="2:4">
+      <c r="C213" t="s">
+        <v>7</v>
+      </c>
+      <c r="D213" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="215" spans="2:4">
+      <c r="B215" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="216" spans="2:4">
+      <c r="C216" t="s">
+        <v>147</v>
+      </c>
+      <c r="D216" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="217" spans="2:4">
+      <c r="C217" t="s">
+        <v>5</v>
+      </c>
+      <c r="D217" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="218" spans="2:4">
+      <c r="B218" t="s">
+        <v>8</v>
+      </c>
+      <c r="C218" t="s">
+        <v>6</v>
+      </c>
+      <c r="D218" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="219" spans="2:4">
+      <c r="C219" t="s">
+        <v>7</v>
+      </c>
+      <c r="D219" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="221" spans="2:4">
+      <c r="B221" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="222" spans="2:4">
+      <c r="B222" t="s">
+        <v>8</v>
+      </c>
+      <c r="C222" t="s">
+        <v>147</v>
+      </c>
+      <c r="D222" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="223" spans="2:4">
+      <c r="C223" t="s">
+        <v>5</v>
+      </c>
+      <c r="D223" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="224" spans="2:4">
+      <c r="C224" t="s">
+        <v>6</v>
+      </c>
+      <c r="D224" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="225" spans="2:4">
+      <c r="C225" t="s">
+        <v>7</v>
+      </c>
+      <c r="D225" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="227" spans="2:4">
+      <c r="B227" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="228" spans="2:4">
+      <c r="C228" t="s">
+        <v>147</v>
+      </c>
+      <c r="D228" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="229" spans="2:4">
+      <c r="B229" t="s">
+        <v>8</v>
+      </c>
+      <c r="C229" t="s">
+        <v>5</v>
+      </c>
+      <c r="D229" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="230" spans="2:4">
+      <c r="C230" t="s">
+        <v>6</v>
+      </c>
+      <c r="D230" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="231" spans="2:4">
+      <c r="C231" t="s">
+        <v>7</v>
+      </c>
+      <c r="D231" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="233" spans="2:4">
+      <c r="B233" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="234" spans="2:4">
+      <c r="C234" t="s">
+        <v>147</v>
+      </c>
+      <c r="D234" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="235" spans="2:4">
+      <c r="C235" t="s">
+        <v>5</v>
+      </c>
+      <c r="D235" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="236" spans="2:4">
+      <c r="C236" t="s">
+        <v>6</v>
+      </c>
+      <c r="D236" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="237" spans="2:4">
+      <c r="B237" t="s">
+        <v>8</v>
+      </c>
+      <c r="C237" t="s">
+        <v>7</v>
+      </c>
+      <c r="D237" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="239" spans="2:4">
+      <c r="B239" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="240" spans="2:4">
+      <c r="C240" t="s">
+        <v>147</v>
+      </c>
+      <c r="D240" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="241" spans="2:4">
+      <c r="B241" t="s">
+        <v>8</v>
+      </c>
+      <c r="C241" t="s">
+        <v>5</v>
+      </c>
+      <c r="D241" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="242" spans="2:4">
+      <c r="C242" t="s">
+        <v>6</v>
+      </c>
+      <c r="D242" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="243" spans="2:4">
+      <c r="C243" t="s">
+        <v>7</v>
+      </c>
+      <c r="D243" t="s">
+        <v>210</v>
       </c>
     </row>
   </sheetData>
@@ -491,11 +2989,342 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{61EEA8E1-AFF1-4B2D-8BDC-8FC5E7EC9EE0}">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A1"/>
+  <dimension ref="B2:D67"/>
   <sheetFormatPr defaultRowHeight="18"/>
-  <sheetData/>
+  <cols>
+    <col min="2" max="3" width="3.296875" customWidth="1"/>
+    <col min="4" max="4" width="85.3984375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:4">
+      <c r="B2" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="3" spans="2:4">
+      <c r="B3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="4" spans="2:4">
+      <c r="C4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D4" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="5" spans="2:4">
+      <c r="C5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D5" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="6" spans="2:4">
+      <c r="C6" t="s">
+        <v>7</v>
+      </c>
+      <c r="D6" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="8" spans="2:4">
+      <c r="B8" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="9" spans="2:4">
+      <c r="B9" t="s">
+        <v>8</v>
+      </c>
+      <c r="C9" t="s">
+        <v>10</v>
+      </c>
+      <c r="D9" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="10" spans="2:4">
+      <c r="C10" t="s">
+        <v>5</v>
+      </c>
+      <c r="D10" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="11" spans="2:4">
+      <c r="C11" t="s">
+        <v>6</v>
+      </c>
+      <c r="D11" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="12" spans="2:4">
+      <c r="C12" t="s">
+        <v>7</v>
+      </c>
+      <c r="D12" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="14" spans="2:4">
+      <c r="B14" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="15" spans="2:4">
+      <c r="B15" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15" t="s">
+        <v>10</v>
+      </c>
+      <c r="D15" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="16" spans="2:4">
+      <c r="C16" t="s">
+        <v>5</v>
+      </c>
+      <c r="D16" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="17" spans="2:4">
+      <c r="C17" t="s">
+        <v>6</v>
+      </c>
+      <c r="D17" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="18" spans="2:4">
+      <c r="C18" t="s">
+        <v>7</v>
+      </c>
+      <c r="D18" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="20" spans="2:4">
+      <c r="B20" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="21" spans="2:4">
+      <c r="B21" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="22" spans="2:4">
+      <c r="B22" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="23" spans="2:4">
+      <c r="B23" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="24" spans="2:4">
+      <c r="B24" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="41" spans="2:4">
+      <c r="B41" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="42" spans="2:4">
+      <c r="B42" t="s">
+        <v>8</v>
+      </c>
+      <c r="C42" t="s">
+        <v>147</v>
+      </c>
+      <c r="D42" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="43" spans="2:4">
+      <c r="C43" t="s">
+        <v>5</v>
+      </c>
+      <c r="D43" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="44" spans="2:4">
+      <c r="C44" t="s">
+        <v>6</v>
+      </c>
+      <c r="D44" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="45" spans="2:4">
+      <c r="C45" t="s">
+        <v>7</v>
+      </c>
+      <c r="D45" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="47" spans="2:4">
+      <c r="B47" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="48" spans="2:4">
+      <c r="B48" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="49" spans="2:4">
+      <c r="B49" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="50" spans="2:4">
+      <c r="B50" t="s">
+        <v>8</v>
+      </c>
+      <c r="C50" t="s">
+        <v>147</v>
+      </c>
+      <c r="D50" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="51" spans="2:4">
+      <c r="C51" t="s">
+        <v>5</v>
+      </c>
+      <c r="D51" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="52" spans="2:4">
+      <c r="C52" t="s">
+        <v>6</v>
+      </c>
+      <c r="D52" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="53" spans="2:4">
+      <c r="C53" t="s">
+        <v>7</v>
+      </c>
+      <c r="D53" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="55" spans="2:4">
+      <c r="B55" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="56" spans="2:4">
+      <c r="B56" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="57" spans="2:4">
+      <c r="B57" t="s">
+        <v>8</v>
+      </c>
+      <c r="C57" t="s">
+        <v>147</v>
+      </c>
+      <c r="D57" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="58" spans="2:4">
+      <c r="C58" t="s">
+        <v>5</v>
+      </c>
+      <c r="D58" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="59" spans="2:4">
+      <c r="C59" t="s">
+        <v>6</v>
+      </c>
+      <c r="D59" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="60" spans="2:4">
+      <c r="C60" t="s">
+        <v>7</v>
+      </c>
+      <c r="D60" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="62" spans="2:4">
+      <c r="B62" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="63" spans="2:4">
+      <c r="B63" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="64" spans="2:4">
+      <c r="B64" t="s">
+        <v>8</v>
+      </c>
+      <c r="C64" t="s">
+        <v>147</v>
+      </c>
+      <c r="D64" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="65" spans="3:4">
+      <c r="C65" t="s">
+        <v>5</v>
+      </c>
+      <c r="D65" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="66" spans="3:4">
+      <c r="C66" t="s">
+        <v>6</v>
+      </c>
+      <c r="D66" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="67" spans="3:4">
+      <c r="C67" t="s">
+        <v>7</v>
+      </c>
+      <c r="D67" t="s">
+        <v>250</v>
+      </c>
+    </row>
+  </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -505,10 +3334,10 @@
   <dimension ref="B2:I108"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
-    <col min="5" max="5" width="8.6640625" hidden="1" customWidth="1"/>
-    <col min="6" max="6" width="10.1640625" hidden="1" customWidth="1"/>
-    <col min="7" max="7" width="8.6640625" customWidth="1"/>
-    <col min="9" max="9" width="10.25" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.69921875" hidden="1" customWidth="1"/>
+    <col min="6" max="6" width="10.19921875" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="8.69921875" customWidth="1"/>
+    <col min="9" max="9" width="10.19921875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:9">
@@ -519,10 +3348,10 @@
         <v>1</v>
       </c>
       <c r="D2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" t="s">
         <v>9</v>
-      </c>
-      <c r="E2" t="s">
-        <v>10</v>
       </c>
       <c r="F2" s="1">
         <v>46075</v>
@@ -533,10 +3362,10 @@
         <v>2</v>
       </c>
       <c r="D3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -544,10 +3373,10 @@
         <v>3</v>
       </c>
       <c r="D4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5" spans="2:9">
@@ -555,16 +3384,16 @@
         <v>4</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G5" t="s">
+        <v>8</v>
+      </c>
+      <c r="H5" t="s">
         <v>9</v>
-      </c>
-      <c r="H5" t="s">
-        <v>10</v>
       </c>
       <c r="I5" s="1">
         <v>46092</v>
@@ -575,10 +3404,10 @@
         <v>5</v>
       </c>
       <c r="D6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E6" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7" spans="2:9">
@@ -586,16 +3415,16 @@
         <v>6</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I7" s="1">
         <v>46092</v>
@@ -606,16 +3435,16 @@
         <v>7</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G8" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I8" s="1">
         <v>46092</v>
@@ -626,10 +3455,10 @@
         <v>8</v>
       </c>
       <c r="D9" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E9" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10" spans="2:9">
@@ -637,16 +3466,16 @@
         <v>9</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E10" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G10" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H10" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I10" s="1">
         <v>46092</v>
@@ -657,16 +3486,16 @@
         <v>10</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E11" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H11" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I11" s="1">
         <v>46092</v>
@@ -677,16 +3506,16 @@
         <v>11</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E12" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H12" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I12" s="1">
         <v>46092</v>
@@ -697,16 +3526,16 @@
         <v>12</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E13" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H13" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I13" s="1">
         <v>46092</v>
@@ -717,16 +3546,16 @@
         <v>13</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E14" t="s">
+        <v>10</v>
+      </c>
+      <c r="G14" t="s">
+        <v>8</v>
+      </c>
+      <c r="H14" t="s">
         <v>11</v>
-      </c>
-      <c r="G14" t="s">
-        <v>9</v>
-      </c>
-      <c r="H14" t="s">
-        <v>12</v>
       </c>
       <c r="I14" s="1">
         <v>46092</v>
@@ -737,10 +3566,10 @@
         <v>14</v>
       </c>
       <c r="D15" t="s">
+        <v>8</v>
+      </c>
+      <c r="E15" t="s">
         <v>9</v>
-      </c>
-      <c r="E15" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="16" spans="2:9">
@@ -748,10 +3577,10 @@
         <v>15</v>
       </c>
       <c r="D16" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E16" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="17" spans="2:9">
@@ -759,10 +3588,10 @@
         <v>16</v>
       </c>
       <c r="D17" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E17" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="18" spans="2:9">
@@ -773,19 +3602,19 @@
         <v>1</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E18" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F18" s="1">
         <v>46076</v>
       </c>
       <c r="G18" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H18" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I18" s="1">
         <v>46092</v>
@@ -796,10 +3625,10 @@
         <v>2</v>
       </c>
       <c r="D19" t="s">
+        <v>8</v>
+      </c>
+      <c r="E19" t="s">
         <v>9</v>
-      </c>
-      <c r="E19" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="20" spans="2:9">
@@ -807,10 +3636,10 @@
         <v>3</v>
       </c>
       <c r="D20" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E20" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="21" spans="2:9">
@@ -818,10 +3647,10 @@
         <v>4</v>
       </c>
       <c r="D21" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E21" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="22" spans="2:9">
@@ -829,10 +3658,10 @@
         <v>5</v>
       </c>
       <c r="D22" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E22" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="23" spans="2:9">
@@ -840,16 +3669,16 @@
         <v>6</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E23" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H23" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I23" s="1">
         <v>46093</v>
@@ -860,10 +3689,10 @@
         <v>7</v>
       </c>
       <c r="D24" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E24" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="25" spans="2:9">
@@ -871,16 +3700,16 @@
         <v>8</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E25" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H25" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I25" s="1">
         <v>46093</v>
@@ -891,10 +3720,10 @@
         <v>9</v>
       </c>
       <c r="D26" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E26" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="27" spans="2:9">
@@ -902,10 +3731,10 @@
         <v>10</v>
       </c>
       <c r="D27" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E27" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="28" spans="2:9">
@@ -913,16 +3742,16 @@
         <v>11</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E28" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H28" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I28" s="1">
         <v>46093</v>
@@ -933,16 +3762,16 @@
         <v>12</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E29" t="s">
+        <v>9</v>
+      </c>
+      <c r="G29" t="s">
+        <v>8</v>
+      </c>
+      <c r="H29" t="s">
         <v>10</v>
-      </c>
-      <c r="G29" t="s">
-        <v>9</v>
-      </c>
-      <c r="H29" t="s">
-        <v>11</v>
       </c>
       <c r="I29" s="1">
         <v>46093</v>
@@ -953,10 +3782,10 @@
         <v>13</v>
       </c>
       <c r="D30" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E30" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="31" spans="2:9">
@@ -964,16 +3793,16 @@
         <v>14</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E31" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H31" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I31" s="1">
         <v>46093</v>
@@ -984,10 +3813,10 @@
         <v>15</v>
       </c>
       <c r="D32" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E32" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="33" spans="2:9">
@@ -995,10 +3824,10 @@
         <v>16</v>
       </c>
       <c r="D33" t="s">
+        <v>8</v>
+      </c>
+      <c r="E33" t="s">
         <v>9</v>
-      </c>
-      <c r="E33" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="34" spans="2:9">
@@ -1009,19 +3838,19 @@
         <v>1</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E34" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F34" s="1">
         <v>46081</v>
       </c>
       <c r="G34" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H34" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I34" s="1">
         <v>46094</v>
@@ -1032,16 +3861,16 @@
         <v>2</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E35" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G35" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H35" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I35" s="1">
         <v>46094</v>
@@ -1052,10 +3881,10 @@
         <v>3</v>
       </c>
       <c r="D36" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E36" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="37" spans="2:9">
@@ -1063,10 +3892,10 @@
         <v>4</v>
       </c>
       <c r="D37" t="s">
+        <v>8</v>
+      </c>
+      <c r="E37" t="s">
         <v>9</v>
-      </c>
-      <c r="E37" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="38" spans="2:9">
@@ -1074,10 +3903,10 @@
         <v>5</v>
       </c>
       <c r="D38" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E38" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="39" spans="2:9">
@@ -1085,16 +3914,16 @@
         <v>6</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E39" t="s">
+        <v>11</v>
+      </c>
+      <c r="G39" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H39" t="s">
         <v>12</v>
-      </c>
-      <c r="G39" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H39" t="s">
-        <v>13</v>
       </c>
       <c r="I39" s="1">
         <v>46094</v>
@@ -1105,16 +3934,16 @@
         <v>7</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E40" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H40" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I40" s="1">
         <v>46094</v>
@@ -1125,10 +3954,10 @@
         <v>8</v>
       </c>
       <c r="D41" t="s">
+        <v>8</v>
+      </c>
+      <c r="E41" t="s">
         <v>9</v>
-      </c>
-      <c r="E41" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="42" spans="2:9">
@@ -1139,19 +3968,19 @@
         <v>1</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E42" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F42" s="1">
         <v>46088</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H42" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I42" s="1">
         <v>46094</v>
@@ -1162,10 +3991,10 @@
         <v>2</v>
       </c>
       <c r="D43" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E43" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="44" spans="2:9">
@@ -1173,16 +4002,16 @@
         <v>3</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E44" t="s">
+        <v>10</v>
+      </c>
+      <c r="G44" t="s">
+        <v>8</v>
+      </c>
+      <c r="H44" t="s">
         <v>11</v>
-      </c>
-      <c r="G44" t="s">
-        <v>9</v>
-      </c>
-      <c r="H44" t="s">
-        <v>12</v>
       </c>
       <c r="I44" s="1">
         <v>46094</v>
@@ -1193,16 +4022,16 @@
         <v>4</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E45" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H45" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I45" s="1">
         <v>46094</v>
@@ -1213,10 +4042,10 @@
         <v>5</v>
       </c>
       <c r="D46" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E46" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="47" spans="2:9">
@@ -1224,10 +4053,10 @@
         <v>6</v>
       </c>
       <c r="D47" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E47" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="48" spans="2:9">
@@ -1235,10 +4064,10 @@
         <v>7</v>
       </c>
       <c r="D48" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E48" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="49" spans="2:6">
@@ -1246,10 +4075,10 @@
         <v>8</v>
       </c>
       <c r="D49" t="s">
+        <v>8</v>
+      </c>
+      <c r="E49" t="s">
         <v>9</v>
-      </c>
-      <c r="E49" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="50" spans="2:6">
@@ -1257,10 +4086,10 @@
         <v>9</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E50" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="51" spans="2:6">
@@ -1268,10 +4097,10 @@
         <v>10</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E51" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="52" spans="2:6">
@@ -1279,10 +4108,10 @@
         <v>11</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E52" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="53" spans="2:6">
@@ -1290,10 +4119,10 @@
         <v>12</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E53" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="54" spans="2:6">
@@ -1304,10 +4133,10 @@
         <v>1</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E54" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F54" s="1">
         <v>46089</v>
@@ -1318,10 +4147,10 @@
         <v>2</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E55" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="56" spans="2:6">
@@ -1329,10 +4158,10 @@
         <v>3</v>
       </c>
       <c r="D56" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E56" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="57" spans="2:6">
@@ -1340,10 +4169,10 @@
         <v>4</v>
       </c>
       <c r="D57" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E57" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="58" spans="2:6">
@@ -1351,10 +4180,10 @@
         <v>5</v>
       </c>
       <c r="D58" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E58" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="59" spans="2:6">
@@ -1362,10 +4191,10 @@
         <v>6</v>
       </c>
       <c r="D59" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E59" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="60" spans="2:6">
@@ -1373,10 +4202,10 @@
         <v>7</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E60" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="61" spans="2:6">
@@ -1384,10 +4213,10 @@
         <v>8</v>
       </c>
       <c r="D61" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E61" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="62" spans="2:6">
@@ -1395,10 +4224,10 @@
         <v>9</v>
       </c>
       <c r="D62" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E62" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="63" spans="2:6">
@@ -1406,10 +4235,10 @@
         <v>10</v>
       </c>
       <c r="D63" t="s">
+        <v>8</v>
+      </c>
+      <c r="E63" t="s">
         <v>9</v>
-      </c>
-      <c r="E63" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="64" spans="2:6">
@@ -1417,10 +4246,10 @@
         <v>11</v>
       </c>
       <c r="D64" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E64" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="65" spans="2:6">
@@ -1428,10 +4257,10 @@
         <v>12</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E65" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="66" spans="2:6">
@@ -1442,10 +4271,10 @@
         <v>1</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E66" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F66" s="1">
         <v>46089</v>
@@ -1456,10 +4285,10 @@
         <v>2</v>
       </c>
       <c r="D67" t="s">
+        <v>8</v>
+      </c>
+      <c r="E67" t="s">
         <v>9</v>
-      </c>
-      <c r="E67" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="68" spans="2:6">
@@ -1470,10 +4299,10 @@
         <v>1</v>
       </c>
       <c r="D68" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E68" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F68" s="1">
         <v>46089</v>
@@ -1484,10 +4313,10 @@
         <v>2</v>
       </c>
       <c r="D69" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E69" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="70" spans="2:6">
@@ -1495,10 +4324,10 @@
         <v>3</v>
       </c>
       <c r="D70" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E70" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="71" spans="2:6">
@@ -1506,10 +4335,10 @@
         <v>4</v>
       </c>
       <c r="D71" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E71" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="72" spans="2:6">
@@ -1517,10 +4346,10 @@
         <v>5</v>
       </c>
       <c r="D72" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E72" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="73" spans="2:6">
@@ -1528,10 +4357,10 @@
         <v>6</v>
       </c>
       <c r="D73" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E73" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="74" spans="2:6">
@@ -1539,10 +4368,10 @@
         <v>7</v>
       </c>
       <c r="D74" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E74" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="75" spans="2:6">
@@ -1550,10 +4379,10 @@
         <v>8</v>
       </c>
       <c r="D75" t="s">
+        <v>8</v>
+      </c>
+      <c r="E75" t="s">
         <v>9</v>
-      </c>
-      <c r="E75" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="76" spans="2:6">
@@ -1561,10 +4390,10 @@
         <v>9</v>
       </c>
       <c r="D76" t="s">
+        <v>8</v>
+      </c>
+      <c r="E76" t="s">
         <v>9</v>
-      </c>
-      <c r="E76" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="77" spans="2:6">
@@ -1572,10 +4401,10 @@
         <v>10</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E77" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="78" spans="2:6">
@@ -1583,10 +4412,10 @@
         <v>11</v>
       </c>
       <c r="D78" t="s">
+        <v>8</v>
+      </c>
+      <c r="E78" t="s">
         <v>9</v>
-      </c>
-      <c r="E78" t="s">
-        <v>10</v>
       </c>
       <c r="F78" s="1">
         <v>46090</v>
@@ -1597,10 +4426,10 @@
         <v>12</v>
       </c>
       <c r="D79" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E79" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="80" spans="2:6">
@@ -1608,10 +4437,10 @@
         <v>13</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E80" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="81" spans="3:6">
@@ -1619,10 +4448,10 @@
         <v>14</v>
       </c>
       <c r="D81" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E81" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="82" spans="3:6">
@@ -1630,10 +4459,10 @@
         <v>15</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E82" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F82" s="1">
         <v>46091</v>
@@ -1644,10 +4473,10 @@
         <v>16</v>
       </c>
       <c r="D83" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E83" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="84" spans="3:6">
@@ -1655,10 +4484,10 @@
         <v>17</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E84" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="85" spans="3:6">
@@ -1666,10 +4495,10 @@
         <v>18</v>
       </c>
       <c r="D85" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E85" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="86" spans="3:6">
@@ -1677,10 +4506,10 @@
         <v>19</v>
       </c>
       <c r="D86" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E86" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="87" spans="3:6">
@@ -1688,10 +4517,10 @@
         <v>20</v>
       </c>
       <c r="D87" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E87" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="88" spans="3:6">
@@ -1699,10 +4528,10 @@
         <v>21</v>
       </c>
       <c r="D88" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E88" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="89" spans="3:6">
@@ -1710,10 +4539,10 @@
         <v>22</v>
       </c>
       <c r="D89" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E89" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="90" spans="3:6">
@@ -1721,10 +4550,10 @@
         <v>23</v>
       </c>
       <c r="D90" t="s">
+        <v>8</v>
+      </c>
+      <c r="E90" t="s">
         <v>9</v>
-      </c>
-      <c r="E90" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="91" spans="3:6">
@@ -1732,10 +4561,10 @@
         <v>24</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E91" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="92" spans="3:6">
@@ -1743,10 +4572,10 @@
         <v>25</v>
       </c>
       <c r="D92" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E92" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="93" spans="3:6">
@@ -1754,10 +4583,10 @@
         <v>26</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E93" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="94" spans="3:6">
@@ -1765,10 +4594,10 @@
         <v>27</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E94" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="95" spans="3:6">
@@ -1776,10 +4605,10 @@
         <v>28</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E95" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="96" spans="3:6">
@@ -1787,10 +4616,10 @@
         <v>29</v>
       </c>
       <c r="D96" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E96" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="97" spans="3:8">
@@ -1798,10 +4627,10 @@
         <v>30</v>
       </c>
       <c r="D97" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E97" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="98" spans="3:8">
@@ -1809,10 +4638,10 @@
         <v>31</v>
       </c>
       <c r="D98" t="s">
+        <v>8</v>
+      </c>
+      <c r="E98" t="s">
         <v>9</v>
-      </c>
-      <c r="E98" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="99" spans="3:8">
@@ -1820,10 +4649,10 @@
         <v>32</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E99" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="100" spans="3:8">
@@ -1831,10 +4660,10 @@
         <v>33</v>
       </c>
       <c r="D100" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E100" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="101" spans="3:8">
@@ -1842,10 +4671,10 @@
         <v>34</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E101" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="102" spans="3:8">
@@ -1853,10 +4682,10 @@
         <v>35</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E102" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="103" spans="3:8">
@@ -1864,10 +4693,10 @@
         <v>36</v>
       </c>
       <c r="D103" t="s">
+        <v>8</v>
+      </c>
+      <c r="E103" t="s">
         <v>9</v>
-      </c>
-      <c r="E103" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="104" spans="3:8">
@@ -1875,10 +4704,10 @@
         <v>37</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E104" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="105" spans="3:8">
@@ -1886,10 +4715,10 @@
         <v>38</v>
       </c>
       <c r="D105" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E105" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="106" spans="3:8">
@@ -1897,10 +4726,10 @@
         <v>39</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E106" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="107" spans="3:8">
@@ -1908,10 +4737,10 @@
         <v>40</v>
       </c>
       <c r="D107" t="s">
+        <v>8</v>
+      </c>
+      <c r="E107" t="s">
         <v>9</v>
-      </c>
-      <c r="E107" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="108" spans="3:8">

--- a/JSTQB_Foundation.xlsx
+++ b/JSTQB_Foundation.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27932"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29530"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ドキュメント\勉強\資格(取得)\JSTQB\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ドキュメント\その他\eラーニング\JSTQB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0700C502-3573-4E50-9527-36D8CFB4D9EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54DB1E7C-F3EB-4EB7-A2C9-AE9A08D933B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="テス友" sheetId="1" r:id="rId1"/>
@@ -33,15 +33,12 @@
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="736" uniqueCount="254">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="780" uniqueCount="256">
   <si>
     <t>典型的なテストの目的として、誤っているものはどれか。次の選択肢の中から1つ選びなさい。</t>
     <phoneticPr fontId="1"/>
@@ -947,6 +944,12 @@
   <si>
     <t>テスト担当者の動作が、様々なテスト入力データによって実行できるように一般化されたスクリプトに記録される。</t>
     <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>✕</t>
+  </si>
+  <si>
+    <t>○</t>
   </si>
 </sst>
 </file>
@@ -1005,11 +1008,14 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="パーセント" xfId="1" builtinId="5"/>
@@ -1361,8 +1367,8 @@
   <dimension ref="B2:D243"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
-    <col min="2" max="3" width="3.296875" customWidth="1"/>
-    <col min="4" max="4" width="85.3984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="3.33203125" customWidth="1"/>
+    <col min="4" max="4" width="85.4140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:4">
@@ -2992,8 +2998,8 @@
   <dimension ref="B2:D67"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
-    <col min="2" max="3" width="3.296875" customWidth="1"/>
-    <col min="4" max="4" width="85.3984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="3.33203125" customWidth="1"/>
+    <col min="4" max="4" width="85.4140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:4">
@@ -3324,7 +3330,8 @@
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -3334,10 +3341,10 @@
   <dimension ref="B2:I108"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
-    <col min="5" max="5" width="8.69921875" hidden="1" customWidth="1"/>
-    <col min="6" max="6" width="10.19921875" hidden="1" customWidth="1"/>
-    <col min="7" max="7" width="8.69921875" customWidth="1"/>
-    <col min="9" max="9" width="10.19921875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.6640625" hidden="1" customWidth="1"/>
+    <col min="6" max="6" width="10.1640625" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="8.6640625" customWidth="1"/>
+    <col min="9" max="9" width="10.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:9">
@@ -4070,7 +4077,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="49" spans="2:6">
+    <row r="49" spans="2:9">
       <c r="C49">
         <v>8</v>
       </c>
@@ -4081,7 +4088,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="50" spans="2:6">
+    <row r="50" spans="2:9">
       <c r="C50">
         <v>9</v>
       </c>
@@ -4091,8 +4098,17 @@
       <c r="E50" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="51" spans="2:6">
+      <c r="G50" s="6" t="s">
+        <v>254</v>
+      </c>
+      <c r="H50" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="I50" s="5">
+        <v>46094</v>
+      </c>
+    </row>
+    <row r="51" spans="2:9">
       <c r="C51">
         <v>10</v>
       </c>
@@ -4102,8 +4118,17 @@
       <c r="E51" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="52" spans="2:6">
+      <c r="G51" s="6" t="s">
+        <v>254</v>
+      </c>
+      <c r="H51" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="I51" s="5">
+        <v>46094</v>
+      </c>
+    </row>
+    <row r="52" spans="2:9">
       <c r="C52">
         <v>11</v>
       </c>
@@ -4113,8 +4138,17 @@
       <c r="E52" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="53" spans="2:6">
+      <c r="G52" s="4" t="s">
+        <v>255</v>
+      </c>
+      <c r="H52" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="I52" s="5">
+        <v>46094</v>
+      </c>
+    </row>
+    <row r="53" spans="2:9">
       <c r="C53">
         <v>12</v>
       </c>
@@ -4124,8 +4158,17 @@
       <c r="E53" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="54" spans="2:6">
+      <c r="G53" s="6" t="s">
+        <v>254</v>
+      </c>
+      <c r="H53" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="I53" s="5">
+        <v>46094</v>
+      </c>
+    </row>
+    <row r="54" spans="2:9">
       <c r="B54">
         <v>5</v>
       </c>
@@ -4141,8 +4184,17 @@
       <c r="F54" s="1">
         <v>46089</v>
       </c>
-    </row>
-    <row r="55" spans="2:6">
+      <c r="G54" s="4" t="s">
+        <v>255</v>
+      </c>
+      <c r="H54" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="I54" s="5">
+        <v>46094</v>
+      </c>
+    </row>
+    <row r="55" spans="2:9">
       <c r="C55">
         <v>2</v>
       </c>
@@ -4152,8 +4204,17 @@
       <c r="E55" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="56" spans="2:6">
+      <c r="G55" s="6" t="s">
+        <v>254</v>
+      </c>
+      <c r="H55" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="I55" s="5">
+        <v>46097</v>
+      </c>
+    </row>
+    <row r="56" spans="2:9">
       <c r="C56">
         <v>3</v>
       </c>
@@ -4163,8 +4224,11 @@
       <c r="E56" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="57" spans="2:6">
+      <c r="G56" s="4"/>
+      <c r="H56" s="4"/>
+      <c r="I56" s="4"/>
+    </row>
+    <row r="57" spans="2:9">
       <c r="C57">
         <v>4</v>
       </c>
@@ -4174,8 +4238,11 @@
       <c r="E57" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="58" spans="2:6">
+      <c r="G57" s="4"/>
+      <c r="H57" s="4"/>
+      <c r="I57" s="4"/>
+    </row>
+    <row r="58" spans="2:9">
       <c r="C58">
         <v>5</v>
       </c>
@@ -4185,8 +4252,11 @@
       <c r="E58" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="59" spans="2:6">
+      <c r="G58" s="4"/>
+      <c r="H58" s="4"/>
+      <c r="I58" s="4"/>
+    </row>
+    <row r="59" spans="2:9">
       <c r="C59">
         <v>6</v>
       </c>
@@ -4196,8 +4266,11 @@
       <c r="E59" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="60" spans="2:6">
+      <c r="G59" s="4"/>
+      <c r="H59" s="4"/>
+      <c r="I59" s="4"/>
+    </row>
+    <row r="60" spans="2:9">
       <c r="C60">
         <v>7</v>
       </c>
@@ -4207,8 +4280,17 @@
       <c r="E60" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="61" spans="2:6">
+      <c r="G60" s="6" t="s">
+        <v>254</v>
+      </c>
+      <c r="H60" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="I60" s="5">
+        <v>46097</v>
+      </c>
+    </row>
+    <row r="61" spans="2:9">
       <c r="C61">
         <v>8</v>
       </c>
@@ -4218,8 +4300,11 @@
       <c r="E61" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="62" spans="2:6">
+      <c r="G61" s="4"/>
+      <c r="H61" s="4"/>
+      <c r="I61" s="4"/>
+    </row>
+    <row r="62" spans="2:9">
       <c r="C62">
         <v>9</v>
       </c>
@@ -4229,8 +4314,11 @@
       <c r="E62" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="63" spans="2:6">
+      <c r="G62" s="4"/>
+      <c r="H62" s="4"/>
+      <c r="I62" s="4"/>
+    </row>
+    <row r="63" spans="2:9">
       <c r="C63">
         <v>10</v>
       </c>
@@ -4240,8 +4328,11 @@
       <c r="E63" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="64" spans="2:6">
+      <c r="G63" s="4"/>
+      <c r="H63" s="4"/>
+      <c r="I63" s="4"/>
+    </row>
+    <row r="64" spans="2:9">
       <c r="C64">
         <v>11</v>
       </c>
@@ -4251,8 +4342,11 @@
       <c r="E64" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="65" spans="2:6">
+      <c r="G64" s="4"/>
+      <c r="H64" s="4"/>
+      <c r="I64" s="4"/>
+    </row>
+    <row r="65" spans="2:9">
       <c r="C65">
         <v>12</v>
       </c>
@@ -4262,8 +4356,17 @@
       <c r="E65" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="66" spans="2:6">
+      <c r="G65" s="6" t="s">
+        <v>254</v>
+      </c>
+      <c r="H65" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="I65" s="5">
+        <v>46097</v>
+      </c>
+    </row>
+    <row r="66" spans="2:9">
       <c r="B66">
         <v>6</v>
       </c>
@@ -4279,8 +4382,17 @@
       <c r="F66" s="1">
         <v>46089</v>
       </c>
-    </row>
-    <row r="67" spans="2:6">
+      <c r="G66" s="4" t="s">
+        <v>255</v>
+      </c>
+      <c r="H66" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="I66" s="5">
+        <v>46097</v>
+      </c>
+    </row>
+    <row r="67" spans="2:9">
       <c r="C67">
         <v>2</v>
       </c>
@@ -4290,8 +4402,11 @@
       <c r="E67" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="68" spans="2:6">
+      <c r="G67" s="4"/>
+      <c r="H67" s="4"/>
+      <c r="I67" s="4"/>
+    </row>
+    <row r="68" spans="2:9">
       <c r="B68">
         <v>7</v>
       </c>
@@ -4307,8 +4422,11 @@
       <c r="F68" s="1">
         <v>46089</v>
       </c>
-    </row>
-    <row r="69" spans="2:6">
+      <c r="G68" s="4"/>
+      <c r="H68" s="4"/>
+      <c r="I68" s="4"/>
+    </row>
+    <row r="69" spans="2:9">
       <c r="C69">
         <v>2</v>
       </c>
@@ -4318,8 +4436,11 @@
       <c r="E69" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="70" spans="2:6">
+      <c r="G69" s="4"/>
+      <c r="H69" s="4"/>
+      <c r="I69" s="4"/>
+    </row>
+    <row r="70" spans="2:9">
       <c r="C70">
         <v>3</v>
       </c>
@@ -4329,8 +4450,11 @@
       <c r="E70" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="71" spans="2:6">
+      <c r="G70" s="4"/>
+      <c r="H70" s="4"/>
+      <c r="I70" s="4"/>
+    </row>
+    <row r="71" spans="2:9">
       <c r="C71">
         <v>4</v>
       </c>
@@ -4340,8 +4464,11 @@
       <c r="E71" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="72" spans="2:6">
+      <c r="G71" s="4"/>
+      <c r="H71" s="4"/>
+      <c r="I71" s="4"/>
+    </row>
+    <row r="72" spans="2:9">
       <c r="C72">
         <v>5</v>
       </c>
@@ -4351,8 +4478,11 @@
       <c r="E72" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="73" spans="2:6">
+      <c r="G72" s="4"/>
+      <c r="H72" s="4"/>
+      <c r="I72" s="4"/>
+    </row>
+    <row r="73" spans="2:9">
       <c r="C73">
         <v>6</v>
       </c>
@@ -4362,8 +4492,11 @@
       <c r="E73" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="74" spans="2:6">
+      <c r="G73" s="4"/>
+      <c r="H73" s="4"/>
+      <c r="I73" s="4"/>
+    </row>
+    <row r="74" spans="2:9">
       <c r="C74">
         <v>7</v>
       </c>
@@ -4373,8 +4506,11 @@
       <c r="E74" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="75" spans="2:6">
+      <c r="G74" s="4"/>
+      <c r="H74" s="4"/>
+      <c r="I74" s="4"/>
+    </row>
+    <row r="75" spans="2:9">
       <c r="C75">
         <v>8</v>
       </c>
@@ -4384,8 +4520,11 @@
       <c r="E75" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="76" spans="2:6">
+      <c r="G75" s="4"/>
+      <c r="H75" s="4"/>
+      <c r="I75" s="4"/>
+    </row>
+    <row r="76" spans="2:9">
       <c r="C76">
         <v>9</v>
       </c>
@@ -4395,8 +4534,11 @@
       <c r="E76" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="77" spans="2:6">
+      <c r="G76" s="4"/>
+      <c r="H76" s="4"/>
+      <c r="I76" s="4"/>
+    </row>
+    <row r="77" spans="2:9">
       <c r="C77">
         <v>10</v>
       </c>
@@ -4406,8 +4548,17 @@
       <c r="E77" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="78" spans="2:6">
+      <c r="G77" s="4" t="s">
+        <v>255</v>
+      </c>
+      <c r="H77" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="I77" s="5">
+        <v>46097</v>
+      </c>
+    </row>
+    <row r="78" spans="2:9">
       <c r="C78">
         <v>11</v>
       </c>
@@ -4420,8 +4571,11 @@
       <c r="F78" s="1">
         <v>46090</v>
       </c>
-    </row>
-    <row r="79" spans="2:6">
+      <c r="G78" s="4"/>
+      <c r="H78" s="4"/>
+      <c r="I78" s="4"/>
+    </row>
+    <row r="79" spans="2:9">
       <c r="C79">
         <v>12</v>
       </c>
@@ -4431,8 +4585,11 @@
       <c r="E79" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="80" spans="2:6">
+      <c r="G79" s="4"/>
+      <c r="H79" s="4"/>
+      <c r="I79" s="4"/>
+    </row>
+    <row r="80" spans="2:9">
       <c r="C80">
         <v>13</v>
       </c>
@@ -4442,8 +4599,17 @@
       <c r="E80" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="81" spans="3:6">
+      <c r="G80" s="4" t="s">
+        <v>255</v>
+      </c>
+      <c r="H80" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="I80" s="5">
+        <v>46097</v>
+      </c>
+    </row>
+    <row r="81" spans="3:9">
       <c r="C81">
         <v>14</v>
       </c>
@@ -4453,8 +4619,11 @@
       <c r="E81" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="82" spans="3:6">
+      <c r="G81" s="4"/>
+      <c r="H81" s="4"/>
+      <c r="I81" s="4"/>
+    </row>
+    <row r="82" spans="3:9">
       <c r="C82">
         <v>15</v>
       </c>
@@ -4467,8 +4636,17 @@
       <c r="F82" s="1">
         <v>46091</v>
       </c>
-    </row>
-    <row r="83" spans="3:6">
+      <c r="G82" s="4" t="s">
+        <v>255</v>
+      </c>
+      <c r="H82" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="I82" s="5">
+        <v>46104</v>
+      </c>
+    </row>
+    <row r="83" spans="3:9">
       <c r="C83">
         <v>16</v>
       </c>
@@ -4478,8 +4656,11 @@
       <c r="E83" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="84" spans="3:6">
+      <c r="G83" s="4"/>
+      <c r="H83" s="4"/>
+      <c r="I83" s="4"/>
+    </row>
+    <row r="84" spans="3:9">
       <c r="C84">
         <v>17</v>
       </c>
@@ -4489,8 +4670,17 @@
       <c r="E84" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="85" spans="3:6">
+      <c r="G84" s="4" t="s">
+        <v>255</v>
+      </c>
+      <c r="H84" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="I84" s="5">
+        <v>46104</v>
+      </c>
+    </row>
+    <row r="85" spans="3:9">
       <c r="C85">
         <v>18</v>
       </c>
@@ -4500,8 +4690,11 @@
       <c r="E85" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="86" spans="3:6">
+      <c r="G85" s="4"/>
+      <c r="H85" s="4"/>
+      <c r="I85" s="4"/>
+    </row>
+    <row r="86" spans="3:9">
       <c r="C86">
         <v>19</v>
       </c>
@@ -4511,8 +4704,11 @@
       <c r="E86" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="87" spans="3:6">
+      <c r="G86" s="4"/>
+      <c r="H86" s="4"/>
+      <c r="I86" s="4"/>
+    </row>
+    <row r="87" spans="3:9">
       <c r="C87">
         <v>20</v>
       </c>
@@ -4522,8 +4718,11 @@
       <c r="E87" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="88" spans="3:6">
+      <c r="G87" s="4"/>
+      <c r="H87" s="4"/>
+      <c r="I87" s="4"/>
+    </row>
+    <row r="88" spans="3:9">
       <c r="C88">
         <v>21</v>
       </c>
@@ -4533,8 +4732,11 @@
       <c r="E88" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="89" spans="3:6">
+      <c r="G88" s="4"/>
+      <c r="H88" s="4"/>
+      <c r="I88" s="4"/>
+    </row>
+    <row r="89" spans="3:9">
       <c r="C89">
         <v>22</v>
       </c>
@@ -4544,8 +4746,11 @@
       <c r="E89" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="90" spans="3:6">
+      <c r="G89" s="4"/>
+      <c r="H89" s="4"/>
+      <c r="I89" s="4"/>
+    </row>
+    <row r="90" spans="3:9">
       <c r="C90">
         <v>23</v>
       </c>
@@ -4555,8 +4760,11 @@
       <c r="E90" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="91" spans="3:6">
+      <c r="G90" s="4"/>
+      <c r="H90" s="4"/>
+      <c r="I90" s="4"/>
+    </row>
+    <row r="91" spans="3:9">
       <c r="C91">
         <v>24</v>
       </c>
@@ -4566,8 +4774,17 @@
       <c r="E91" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="92" spans="3:6">
+      <c r="G91" s="6" t="s">
+        <v>254</v>
+      </c>
+      <c r="H91" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="I91" s="5">
+        <v>46104</v>
+      </c>
+    </row>
+    <row r="92" spans="3:9">
       <c r="C92">
         <v>25</v>
       </c>
@@ -4577,8 +4794,11 @@
       <c r="E92" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="93" spans="3:6">
+      <c r="G92" s="4"/>
+      <c r="H92" s="4"/>
+      <c r="I92" s="4"/>
+    </row>
+    <row r="93" spans="3:9">
       <c r="C93">
         <v>26</v>
       </c>
@@ -4588,8 +4808,17 @@
       <c r="E93" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="94" spans="3:6">
+      <c r="G93" s="4" t="s">
+        <v>255</v>
+      </c>
+      <c r="H93" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="I93" s="5">
+        <v>46104</v>
+      </c>
+    </row>
+    <row r="94" spans="3:9">
       <c r="C94">
         <v>27</v>
       </c>
@@ -4599,8 +4828,17 @@
       <c r="E94" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="95" spans="3:6">
+      <c r="G94" s="6" t="s">
+        <v>254</v>
+      </c>
+      <c r="H94" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="I94" s="5">
+        <v>46104</v>
+      </c>
+    </row>
+    <row r="95" spans="3:9">
       <c r="C95">
         <v>28</v>
       </c>
@@ -4610,8 +4848,17 @@
       <c r="E95" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="96" spans="3:6">
+      <c r="G95" s="6" t="s">
+        <v>254</v>
+      </c>
+      <c r="H95" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="I95" s="5">
+        <v>46104</v>
+      </c>
+    </row>
+    <row r="96" spans="3:9">
       <c r="C96">
         <v>29</v>
       </c>
@@ -4621,8 +4868,11 @@
       <c r="E96" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="97" spans="3:8">
+      <c r="G96" s="4"/>
+      <c r="H96" s="4"/>
+      <c r="I96" s="4"/>
+    </row>
+    <row r="97" spans="3:9">
       <c r="C97">
         <v>30</v>
       </c>
@@ -4632,8 +4882,11 @@
       <c r="E97" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="98" spans="3:8">
+      <c r="G97" s="4"/>
+      <c r="H97" s="4"/>
+      <c r="I97" s="4"/>
+    </row>
+    <row r="98" spans="3:9">
       <c r="C98">
         <v>31</v>
       </c>
@@ -4643,8 +4896,11 @@
       <c r="E98" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="99" spans="3:8">
+      <c r="G98" s="4"/>
+      <c r="H98" s="4"/>
+      <c r="I98" s="4"/>
+    </row>
+    <row r="99" spans="3:9">
       <c r="C99">
         <v>32</v>
       </c>
@@ -4654,8 +4910,17 @@
       <c r="E99" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="100" spans="3:8">
+      <c r="G99" s="6" t="s">
+        <v>254</v>
+      </c>
+      <c r="H99" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="I99" s="5">
+        <v>46104</v>
+      </c>
+    </row>
+    <row r="100" spans="3:9">
       <c r="C100">
         <v>33</v>
       </c>
@@ -4665,8 +4930,11 @@
       <c r="E100" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="101" spans="3:8">
+      <c r="G100" s="4"/>
+      <c r="H100" s="4"/>
+      <c r="I100" s="4"/>
+    </row>
+    <row r="101" spans="3:9">
       <c r="C101">
         <v>34</v>
       </c>
@@ -4676,8 +4944,17 @@
       <c r="E101" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="102" spans="3:8">
+      <c r="G101" s="4" t="s">
+        <v>255</v>
+      </c>
+      <c r="H101" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="I101" s="5">
+        <v>46104</v>
+      </c>
+    </row>
+    <row r="102" spans="3:9">
       <c r="C102">
         <v>35</v>
       </c>
@@ -4687,8 +4964,17 @@
       <c r="E102" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="103" spans="3:8">
+      <c r="G102" s="6" t="s">
+        <v>254</v>
+      </c>
+      <c r="H102" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="I102" s="5">
+        <v>46104</v>
+      </c>
+    </row>
+    <row r="103" spans="3:9">
       <c r="C103">
         <v>36</v>
       </c>
@@ -4698,8 +4984,11 @@
       <c r="E103" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="104" spans="3:8">
+      <c r="G103" s="4"/>
+      <c r="H103" s="4"/>
+      <c r="I103" s="4"/>
+    </row>
+    <row r="104" spans="3:9">
       <c r="C104">
         <v>37</v>
       </c>
@@ -4709,8 +4998,17 @@
       <c r="E104" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="105" spans="3:8">
+      <c r="G104" s="6" t="s">
+        <v>254</v>
+      </c>
+      <c r="H104" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="I104" s="5">
+        <v>46104</v>
+      </c>
+    </row>
+    <row r="105" spans="3:9">
       <c r="C105">
         <v>38</v>
       </c>
@@ -4720,8 +5018,11 @@
       <c r="E105" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="106" spans="3:8">
+      <c r="G105" s="4"/>
+      <c r="H105" s="4"/>
+      <c r="I105" s="4"/>
+    </row>
+    <row r="106" spans="3:9">
       <c r="C106">
         <v>39</v>
       </c>
@@ -4731,8 +5032,17 @@
       <c r="E106" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="107" spans="3:8">
+      <c r="G106" s="6" t="s">
+        <v>254</v>
+      </c>
+      <c r="H106" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="I106" s="5">
+        <v>46104</v>
+      </c>
+    </row>
+    <row r="107" spans="3:9">
       <c r="C107">
         <v>40</v>
       </c>
@@ -4743,7 +5053,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="108" spans="3:8">
+    <row r="108" spans="3:9">
       <c r="D108" s="3">
         <f>COUNTIF(D2:D107,"○")/COUNTA(D2:D107)</f>
         <v>0.59433962264150941</v>
@@ -4754,11 +5064,11 @@
       </c>
       <c r="G108" s="3">
         <f>COUNTIF(G2:G107,"○")/COUNTA(G2:G107)</f>
-        <v>0.42857142857142855</v>
-      </c>
-      <c r="H108" s="3" t="e">
+        <v>0.41860465116279072</v>
+      </c>
+      <c r="H108" s="3">
         <f>COUNTIF(G68:G107,"○")/COUNTA(G68:G107)</f>
-        <v>#DIV/0!</v>
+        <v>0.46153846153846156</v>
       </c>
     </row>
   </sheetData>

--- a/JSTQB_Foundation.xlsx
+++ b/JSTQB_Foundation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ドキュメント\その他\eラーニング\JSTQB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54DB1E7C-F3EB-4EB7-A2C9-AE9A08D933B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{120FF5B3-699F-4748-A5FE-3D5B280142DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="780" uniqueCount="256">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="832" uniqueCount="256">
   <si>
     <t>典型的なテストの目的として、誤っているものはどれか。次の選択肢の中から1つ選びなさい。</t>
     <phoneticPr fontId="1"/>
@@ -1008,14 +1008,11 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="パーセント" xfId="1" builtinId="5"/>
@@ -3338,16 +3335,18 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CFBD2AC0-38EC-4B9C-A0BF-1559C25A244C}">
   <sheetPr codeName="Sheet3"/>
-  <dimension ref="B2:I108"/>
+  <dimension ref="B2:L108"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="5" max="5" width="8.6640625" hidden="1" customWidth="1"/>
     <col min="6" max="6" width="10.1640625" hidden="1" customWidth="1"/>
     <col min="7" max="7" width="8.6640625" customWidth="1"/>
-    <col min="9" max="9" width="10.1640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="0" hidden="1" customWidth="1"/>
+    <col min="9" max="9" width="10.1640625" hidden="1" customWidth="1"/>
+    <col min="12" max="12" width="10.25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:9">
+    <row r="2" spans="2:12">
       <c r="B2">
         <v>1</v>
       </c>
@@ -3364,7 +3363,7 @@
         <v>46075</v>
       </c>
     </row>
-    <row r="3" spans="2:9">
+    <row r="3" spans="2:12">
       <c r="C3">
         <v>2</v>
       </c>
@@ -3375,7 +3374,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="2:9">
+    <row r="4" spans="2:12">
       <c r="C4">
         <v>3</v>
       </c>
@@ -3386,7 +3385,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="2:9">
+    <row r="5" spans="2:12">
       <c r="C5">
         <v>4</v>
       </c>
@@ -3406,7 +3405,7 @@
         <v>46092</v>
       </c>
     </row>
-    <row r="6" spans="2:9">
+    <row r="6" spans="2:12">
       <c r="C6">
         <v>5</v>
       </c>
@@ -3417,7 +3416,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="2:9">
+    <row r="7" spans="2:12">
       <c r="C7">
         <v>6</v>
       </c>
@@ -3436,8 +3435,17 @@
       <c r="I7" s="1">
         <v>46092</v>
       </c>
-    </row>
-    <row r="8" spans="2:9">
+      <c r="J7" t="s">
+        <v>8</v>
+      </c>
+      <c r="K7" t="s">
+        <v>11</v>
+      </c>
+      <c r="L7" s="1">
+        <v>46104</v>
+      </c>
+    </row>
+    <row r="8" spans="2:12">
       <c r="C8">
         <v>7</v>
       </c>
@@ -3457,7 +3465,7 @@
         <v>46092</v>
       </c>
     </row>
-    <row r="9" spans="2:9">
+    <row r="9" spans="2:12">
       <c r="C9">
         <v>8</v>
       </c>
@@ -3468,7 +3476,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="2:9">
+    <row r="10" spans="2:12">
       <c r="C10">
         <v>9</v>
       </c>
@@ -3488,7 +3496,7 @@
         <v>46092</v>
       </c>
     </row>
-    <row r="11" spans="2:9">
+    <row r="11" spans="2:12">
       <c r="C11">
         <v>10</v>
       </c>
@@ -3507,8 +3515,17 @@
       <c r="I11" s="1">
         <v>46092</v>
       </c>
-    </row>
-    <row r="12" spans="2:9">
+      <c r="J11" t="s">
+        <v>8</v>
+      </c>
+      <c r="K11" t="s">
+        <v>12</v>
+      </c>
+      <c r="L11" s="1">
+        <v>46104</v>
+      </c>
+    </row>
+    <row r="12" spans="2:12">
       <c r="C12">
         <v>11</v>
       </c>
@@ -3527,8 +3544,17 @@
       <c r="I12" s="1">
         <v>46092</v>
       </c>
-    </row>
-    <row r="13" spans="2:9">
+      <c r="J12" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="K12" t="s">
+        <v>12</v>
+      </c>
+      <c r="L12" s="1">
+        <v>46104</v>
+      </c>
+    </row>
+    <row r="13" spans="2:12">
       <c r="C13">
         <v>12</v>
       </c>
@@ -3547,8 +3573,17 @@
       <c r="I13" s="1">
         <v>46092</v>
       </c>
-    </row>
-    <row r="14" spans="2:9">
+      <c r="J13" t="s">
+        <v>8</v>
+      </c>
+      <c r="K13" t="s">
+        <v>11</v>
+      </c>
+      <c r="L13" s="1">
+        <v>46104</v>
+      </c>
+    </row>
+    <row r="14" spans="2:12">
       <c r="C14">
         <v>13</v>
       </c>
@@ -3568,7 +3603,7 @@
         <v>46092</v>
       </c>
     </row>
-    <row r="15" spans="2:9">
+    <row r="15" spans="2:12">
       <c r="C15">
         <v>14</v>
       </c>
@@ -3579,7 +3614,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="16" spans="2:9">
+    <row r="16" spans="2:12">
       <c r="C16">
         <v>15</v>
       </c>
@@ -3590,7 +3625,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="17" spans="2:9">
+    <row r="17" spans="2:12">
       <c r="C17">
         <v>16</v>
       </c>
@@ -3601,7 +3636,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="18" spans="2:9">
+    <row r="18" spans="2:12">
       <c r="B18">
         <v>2</v>
       </c>
@@ -3627,7 +3662,7 @@
         <v>46092</v>
       </c>
     </row>
-    <row r="19" spans="2:9">
+    <row r="19" spans="2:12">
       <c r="C19">
         <v>2</v>
       </c>
@@ -3638,7 +3673,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="20" spans="2:9">
+    <row r="20" spans="2:12">
       <c r="C20">
         <v>3</v>
       </c>
@@ -3649,7 +3684,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="21" spans="2:9">
+    <row r="21" spans="2:12">
       <c r="C21">
         <v>4</v>
       </c>
@@ -3660,7 +3695,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="22" spans="2:9">
+    <row r="22" spans="2:12">
       <c r="C22">
         <v>5</v>
       </c>
@@ -3671,7 +3706,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="23" spans="2:9">
+    <row r="23" spans="2:12">
       <c r="C23">
         <v>6</v>
       </c>
@@ -3690,8 +3725,17 @@
       <c r="I23" s="1">
         <v>46093</v>
       </c>
-    </row>
-    <row r="24" spans="2:9">
+      <c r="J23" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="K23" t="s">
+        <v>11</v>
+      </c>
+      <c r="L23" s="1">
+        <v>46105</v>
+      </c>
+    </row>
+    <row r="24" spans="2:12">
       <c r="C24">
         <v>7</v>
       </c>
@@ -3702,7 +3746,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="25" spans="2:9">
+    <row r="25" spans="2:12">
       <c r="C25">
         <v>8</v>
       </c>
@@ -3721,8 +3765,17 @@
       <c r="I25" s="1">
         <v>46093</v>
       </c>
-    </row>
-    <row r="26" spans="2:9">
+      <c r="J25" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="K25" t="s">
+        <v>11</v>
+      </c>
+      <c r="L25" s="1">
+        <v>46105</v>
+      </c>
+    </row>
+    <row r="26" spans="2:12">
       <c r="C26">
         <v>9</v>
       </c>
@@ -3733,7 +3786,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="27" spans="2:9">
+    <row r="27" spans="2:12">
       <c r="C27">
         <v>10</v>
       </c>
@@ -3744,7 +3797,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="28" spans="2:9">
+    <row r="28" spans="2:12">
       <c r="C28">
         <v>11</v>
       </c>
@@ -3763,8 +3816,17 @@
       <c r="I28" s="1">
         <v>46093</v>
       </c>
-    </row>
-    <row r="29" spans="2:9">
+      <c r="J28" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="K28" t="s">
+        <v>9</v>
+      </c>
+      <c r="L28" s="1">
+        <v>46105</v>
+      </c>
+    </row>
+    <row r="29" spans="2:12">
       <c r="C29">
         <v>12</v>
       </c>
@@ -3784,7 +3846,7 @@
         <v>46093</v>
       </c>
     </row>
-    <row r="30" spans="2:9">
+    <row r="30" spans="2:12">
       <c r="C30">
         <v>13</v>
       </c>
@@ -3795,7 +3857,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="31" spans="2:9">
+    <row r="31" spans="2:12">
       <c r="C31">
         <v>14</v>
       </c>
@@ -3814,8 +3876,17 @@
       <c r="I31" s="1">
         <v>46093</v>
       </c>
-    </row>
-    <row r="32" spans="2:9">
+      <c r="J31" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="K31" t="s">
+        <v>10</v>
+      </c>
+      <c r="L31" s="1">
+        <v>46105</v>
+      </c>
+    </row>
+    <row r="32" spans="2:12">
       <c r="C32">
         <v>15</v>
       </c>
@@ -3826,7 +3897,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="33" spans="2:9">
+    <row r="33" spans="2:12">
       <c r="C33">
         <v>16</v>
       </c>
@@ -3837,7 +3908,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="34" spans="2:9">
+    <row r="34" spans="2:12">
       <c r="B34">
         <v>3</v>
       </c>
@@ -3863,7 +3934,7 @@
         <v>46094</v>
       </c>
     </row>
-    <row r="35" spans="2:9">
+    <row r="35" spans="2:12">
       <c r="C35">
         <v>2</v>
       </c>
@@ -3883,7 +3954,7 @@
         <v>46094</v>
       </c>
     </row>
-    <row r="36" spans="2:9">
+    <row r="36" spans="2:12">
       <c r="C36">
         <v>3</v>
       </c>
@@ -3894,7 +3965,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="37" spans="2:9">
+    <row r="37" spans="2:12">
       <c r="C37">
         <v>4</v>
       </c>
@@ -3905,7 +3976,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="38" spans="2:9">
+    <row r="38" spans="2:12">
       <c r="C38">
         <v>5</v>
       </c>
@@ -3916,7 +3987,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="39" spans="2:9">
+    <row r="39" spans="2:12">
       <c r="C39">
         <v>6</v>
       </c>
@@ -3935,8 +4006,17 @@
       <c r="I39" s="1">
         <v>46094</v>
       </c>
-    </row>
-    <row r="40" spans="2:9">
+      <c r="J39" t="s">
+        <v>8</v>
+      </c>
+      <c r="K39" t="s">
+        <v>9</v>
+      </c>
+      <c r="L39" s="1">
+        <v>46105</v>
+      </c>
+    </row>
+    <row r="40" spans="2:12">
       <c r="C40">
         <v>7</v>
       </c>
@@ -3955,8 +4035,17 @@
       <c r="I40" s="1">
         <v>46094</v>
       </c>
-    </row>
-    <row r="41" spans="2:9">
+      <c r="J40" t="s">
+        <v>8</v>
+      </c>
+      <c r="K40" t="s">
+        <v>11</v>
+      </c>
+      <c r="L40" s="1">
+        <v>46105</v>
+      </c>
+    </row>
+    <row r="41" spans="2:12">
       <c r="C41">
         <v>8</v>
       </c>
@@ -3967,7 +4056,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="42" spans="2:9">
+    <row r="42" spans="2:12">
       <c r="B42">
         <v>4</v>
       </c>
@@ -3992,8 +4081,17 @@
       <c r="I42" s="1">
         <v>46094</v>
       </c>
-    </row>
-    <row r="43" spans="2:9">
+      <c r="J42" t="s">
+        <v>8</v>
+      </c>
+      <c r="K42" t="s">
+        <v>12</v>
+      </c>
+      <c r="L42" s="1">
+        <v>46105</v>
+      </c>
+    </row>
+    <row r="43" spans="2:12">
       <c r="C43">
         <v>2</v>
       </c>
@@ -4004,7 +4102,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="44" spans="2:9">
+    <row r="44" spans="2:12">
       <c r="C44">
         <v>3</v>
       </c>
@@ -4024,7 +4122,7 @@
         <v>46094</v>
       </c>
     </row>
-    <row r="45" spans="2:9">
+    <row r="45" spans="2:12">
       <c r="C45">
         <v>4</v>
       </c>
@@ -4043,8 +4141,17 @@
       <c r="I45" s="1">
         <v>46094</v>
       </c>
-    </row>
-    <row r="46" spans="2:9">
+      <c r="J45" t="s">
+        <v>8</v>
+      </c>
+      <c r="K45" t="s">
+        <v>11</v>
+      </c>
+      <c r="L45" s="1">
+        <v>46105</v>
+      </c>
+    </row>
+    <row r="46" spans="2:12">
       <c r="C46">
         <v>5</v>
       </c>
@@ -4055,7 +4162,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="47" spans="2:9">
+    <row r="47" spans="2:12">
       <c r="C47">
         <v>6</v>
       </c>
@@ -4066,7 +4173,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="48" spans="2:9">
+    <row r="48" spans="2:12">
       <c r="C48">
         <v>7</v>
       </c>
@@ -4077,7 +4184,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="49" spans="2:9">
+    <row r="49" spans="2:12">
       <c r="C49">
         <v>8</v>
       </c>
@@ -4088,7 +4195,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="50" spans="2:9">
+    <row r="50" spans="2:12">
       <c r="C50">
         <v>9</v>
       </c>
@@ -4098,17 +4205,26 @@
       <c r="E50" t="s">
         <v>11</v>
       </c>
-      <c r="G50" s="6" t="s">
+      <c r="G50" s="2" t="s">
         <v>254</v>
       </c>
-      <c r="H50" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="I50" s="5">
+      <c r="H50" t="s">
+        <v>5</v>
+      </c>
+      <c r="I50" s="1">
         <v>46094</v>
       </c>
-    </row>
-    <row r="51" spans="2:9">
+      <c r="J50" t="s">
+        <v>8</v>
+      </c>
+      <c r="K50" t="s">
+        <v>12</v>
+      </c>
+      <c r="L50" s="1">
+        <v>46105</v>
+      </c>
+    </row>
+    <row r="51" spans="2:12">
       <c r="C51">
         <v>10</v>
       </c>
@@ -4118,17 +4234,26 @@
       <c r="E51" t="s">
         <v>9</v>
       </c>
-      <c r="G51" s="6" t="s">
+      <c r="G51" s="2" t="s">
         <v>254</v>
       </c>
-      <c r="H51" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="I51" s="5">
+      <c r="H51" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I51" s="1">
         <v>46094</v>
       </c>
-    </row>
-    <row r="52" spans="2:9">
+      <c r="J51" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="K51" t="s">
+        <v>11</v>
+      </c>
+      <c r="L51" s="1">
+        <v>46105</v>
+      </c>
+    </row>
+    <row r="52" spans="2:12">
       <c r="C52">
         <v>11</v>
       </c>
@@ -4138,17 +4263,17 @@
       <c r="E52" t="s">
         <v>10</v>
       </c>
-      <c r="G52" s="4" t="s">
+      <c r="G52" t="s">
         <v>255</v>
       </c>
-      <c r="H52" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="I52" s="5">
+      <c r="H52" t="s">
+        <v>7</v>
+      </c>
+      <c r="I52" s="1">
         <v>46094</v>
       </c>
     </row>
-    <row r="53" spans="2:9">
+    <row r="53" spans="2:12">
       <c r="C53">
         <v>12</v>
       </c>
@@ -4158,17 +4283,26 @@
       <c r="E53" t="s">
         <v>12</v>
       </c>
-      <c r="G53" s="6" t="s">
+      <c r="G53" s="2" t="s">
         <v>254</v>
       </c>
-      <c r="H53" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="I53" s="5">
+      <c r="H53" t="s">
+        <v>7</v>
+      </c>
+      <c r="I53" s="1">
         <v>46094</v>
       </c>
-    </row>
-    <row r="54" spans="2:9">
+      <c r="J53" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="K53" t="s">
+        <v>11</v>
+      </c>
+      <c r="L53" s="1">
+        <v>46105</v>
+      </c>
+    </row>
+    <row r="54" spans="2:12">
       <c r="B54">
         <v>5</v>
       </c>
@@ -4184,17 +4318,17 @@
       <c r="F54" s="1">
         <v>46089</v>
       </c>
-      <c r="G54" s="4" t="s">
+      <c r="G54" t="s">
         <v>255</v>
       </c>
-      <c r="H54" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="I54" s="5">
+      <c r="H54" t="s">
+        <v>7</v>
+      </c>
+      <c r="I54" s="1">
         <v>46094</v>
       </c>
     </row>
-    <row r="55" spans="2:9">
+    <row r="55" spans="2:12">
       <c r="C55">
         <v>2</v>
       </c>
@@ -4204,17 +4338,26 @@
       <c r="E55" t="s">
         <v>11</v>
       </c>
-      <c r="G55" s="6" t="s">
+      <c r="G55" s="2" t="s">
         <v>254</v>
       </c>
-      <c r="H55" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="I55" s="5">
+      <c r="H55" t="s">
+        <v>5</v>
+      </c>
+      <c r="I55" s="1">
         <v>46097</v>
       </c>
-    </row>
-    <row r="56" spans="2:9">
+      <c r="J55" t="s">
+        <v>8</v>
+      </c>
+      <c r="K55" t="s">
+        <v>10</v>
+      </c>
+      <c r="L55" s="1">
+        <v>46105</v>
+      </c>
+    </row>
+    <row r="56" spans="2:12">
       <c r="C56">
         <v>3</v>
       </c>
@@ -4224,11 +4367,8 @@
       <c r="E56" t="s">
         <v>11</v>
       </c>
-      <c r="G56" s="4"/>
-      <c r="H56" s="4"/>
-      <c r="I56" s="4"/>
-    </row>
-    <row r="57" spans="2:9">
+    </row>
+    <row r="57" spans="2:12">
       <c r="C57">
         <v>4</v>
       </c>
@@ -4238,11 +4378,8 @@
       <c r="E57" t="s">
         <v>11</v>
       </c>
-      <c r="G57" s="4"/>
-      <c r="H57" s="4"/>
-      <c r="I57" s="4"/>
-    </row>
-    <row r="58" spans="2:9">
+    </row>
+    <row r="58" spans="2:12">
       <c r="C58">
         <v>5</v>
       </c>
@@ -4252,11 +4389,8 @@
       <c r="E58" t="s">
         <v>11</v>
       </c>
-      <c r="G58" s="4"/>
-      <c r="H58" s="4"/>
-      <c r="I58" s="4"/>
-    </row>
-    <row r="59" spans="2:9">
+    </row>
+    <row r="59" spans="2:12">
       <c r="C59">
         <v>6</v>
       </c>
@@ -4266,11 +4400,8 @@
       <c r="E59" t="s">
         <v>12</v>
       </c>
-      <c r="G59" s="4"/>
-      <c r="H59" s="4"/>
-      <c r="I59" s="4"/>
-    </row>
-    <row r="60" spans="2:9">
+    </row>
+    <row r="60" spans="2:12">
       <c r="C60">
         <v>7</v>
       </c>
@@ -4280,17 +4411,26 @@
       <c r="E60" t="s">
         <v>12</v>
       </c>
-      <c r="G60" s="6" t="s">
+      <c r="G60" s="2" t="s">
         <v>254</v>
       </c>
-      <c r="H60" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="I60" s="5">
+      <c r="H60" t="s">
+        <v>5</v>
+      </c>
+      <c r="I60" s="1">
         <v>46097</v>
       </c>
-    </row>
-    <row r="61" spans="2:9">
+      <c r="J60" t="s">
+        <v>8</v>
+      </c>
+      <c r="K60" t="s">
+        <v>11</v>
+      </c>
+      <c r="L60" s="1">
+        <v>46105</v>
+      </c>
+    </row>
+    <row r="61" spans="2:12">
       <c r="C61">
         <v>8</v>
       </c>
@@ -4300,11 +4440,8 @@
       <c r="E61" t="s">
         <v>10</v>
       </c>
-      <c r="G61" s="4"/>
-      <c r="H61" s="4"/>
-      <c r="I61" s="4"/>
-    </row>
-    <row r="62" spans="2:9">
+    </row>
+    <row r="62" spans="2:12">
       <c r="C62">
         <v>9</v>
       </c>
@@ -4314,11 +4451,8 @@
       <c r="E62" t="s">
         <v>12</v>
       </c>
-      <c r="G62" s="4"/>
-      <c r="H62" s="4"/>
-      <c r="I62" s="4"/>
-    </row>
-    <row r="63" spans="2:9">
+    </row>
+    <row r="63" spans="2:12">
       <c r="C63">
         <v>10</v>
       </c>
@@ -4328,11 +4462,8 @@
       <c r="E63" t="s">
         <v>9</v>
       </c>
-      <c r="G63" s="4"/>
-      <c r="H63" s="4"/>
-      <c r="I63" s="4"/>
-    </row>
-    <row r="64" spans="2:9">
+    </row>
+    <row r="64" spans="2:12">
       <c r="C64">
         <v>11</v>
       </c>
@@ -4342,11 +4473,8 @@
       <c r="E64" t="s">
         <v>11</v>
       </c>
-      <c r="G64" s="4"/>
-      <c r="H64" s="4"/>
-      <c r="I64" s="4"/>
-    </row>
-    <row r="65" spans="2:9">
+    </row>
+    <row r="65" spans="2:12">
       <c r="C65">
         <v>12</v>
       </c>
@@ -4356,17 +4484,26 @@
       <c r="E65" t="s">
         <v>11</v>
       </c>
-      <c r="G65" s="6" t="s">
+      <c r="G65" s="2" t="s">
         <v>254</v>
       </c>
-      <c r="H65" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="I65" s="5">
+      <c r="H65" t="s">
+        <v>6</v>
+      </c>
+      <c r="I65" s="1">
         <v>46097</v>
       </c>
-    </row>
-    <row r="66" spans="2:9">
+      <c r="J65" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="K65" t="s">
+        <v>11</v>
+      </c>
+      <c r="L65" s="1">
+        <v>46105</v>
+      </c>
+    </row>
+    <row r="66" spans="2:12">
       <c r="B66">
         <v>6</v>
       </c>
@@ -4382,17 +4519,26 @@
       <c r="F66" s="1">
         <v>46089</v>
       </c>
-      <c r="G66" s="4" t="s">
+      <c r="G66" t="s">
         <v>255</v>
       </c>
-      <c r="H66" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="I66" s="5">
+      <c r="H66" t="s">
+        <v>7</v>
+      </c>
+      <c r="I66" s="1">
         <v>46097</v>
       </c>
-    </row>
-    <row r="67" spans="2:9">
+      <c r="J66" t="s">
+        <v>8</v>
+      </c>
+      <c r="K66" t="s">
+        <v>12</v>
+      </c>
+      <c r="L66" s="1">
+        <v>46105</v>
+      </c>
+    </row>
+    <row r="67" spans="2:12">
       <c r="C67">
         <v>2</v>
       </c>
@@ -4402,11 +4548,8 @@
       <c r="E67" t="s">
         <v>9</v>
       </c>
-      <c r="G67" s="4"/>
-      <c r="H67" s="4"/>
-      <c r="I67" s="4"/>
-    </row>
-    <row r="68" spans="2:9">
+    </row>
+    <row r="68" spans="2:12">
       <c r="B68">
         <v>7</v>
       </c>
@@ -4422,11 +4565,8 @@
       <c r="F68" s="1">
         <v>46089</v>
       </c>
-      <c r="G68" s="4"/>
-      <c r="H68" s="4"/>
-      <c r="I68" s="4"/>
-    </row>
-    <row r="69" spans="2:9">
+    </row>
+    <row r="69" spans="2:12">
       <c r="C69">
         <v>2</v>
       </c>
@@ -4436,11 +4576,8 @@
       <c r="E69" t="s">
         <v>11</v>
       </c>
-      <c r="G69" s="4"/>
-      <c r="H69" s="4"/>
-      <c r="I69" s="4"/>
-    </row>
-    <row r="70" spans="2:9">
+    </row>
+    <row r="70" spans="2:12">
       <c r="C70">
         <v>3</v>
       </c>
@@ -4450,11 +4587,8 @@
       <c r="E70" t="s">
         <v>12</v>
       </c>
-      <c r="G70" s="4"/>
-      <c r="H70" s="4"/>
-      <c r="I70" s="4"/>
-    </row>
-    <row r="71" spans="2:9">
+    </row>
+    <row r="71" spans="2:12">
       <c r="C71">
         <v>4</v>
       </c>
@@ -4464,11 +4598,8 @@
       <c r="E71" t="s">
         <v>11</v>
       </c>
-      <c r="G71" s="4"/>
-      <c r="H71" s="4"/>
-      <c r="I71" s="4"/>
-    </row>
-    <row r="72" spans="2:9">
+    </row>
+    <row r="72" spans="2:12">
       <c r="C72">
         <v>5</v>
       </c>
@@ -4478,11 +4609,8 @@
       <c r="E72" t="s">
         <v>12</v>
       </c>
-      <c r="G72" s="4"/>
-      <c r="H72" s="4"/>
-      <c r="I72" s="4"/>
-    </row>
-    <row r="73" spans="2:9">
+    </row>
+    <row r="73" spans="2:12">
       <c r="C73">
         <v>6</v>
       </c>
@@ -4492,11 +4620,8 @@
       <c r="E73" t="s">
         <v>12</v>
       </c>
-      <c r="G73" s="4"/>
-      <c r="H73" s="4"/>
-      <c r="I73" s="4"/>
-    </row>
-    <row r="74" spans="2:9">
+    </row>
+    <row r="74" spans="2:12">
       <c r="C74">
         <v>7</v>
       </c>
@@ -4506,11 +4631,8 @@
       <c r="E74" t="s">
         <v>11</v>
       </c>
-      <c r="G74" s="4"/>
-      <c r="H74" s="4"/>
-      <c r="I74" s="4"/>
-    </row>
-    <row r="75" spans="2:9">
+    </row>
+    <row r="75" spans="2:12">
       <c r="C75">
         <v>8</v>
       </c>
@@ -4520,11 +4642,8 @@
       <c r="E75" t="s">
         <v>9</v>
       </c>
-      <c r="G75" s="4"/>
-      <c r="H75" s="4"/>
-      <c r="I75" s="4"/>
-    </row>
-    <row r="76" spans="2:9">
+    </row>
+    <row r="76" spans="2:12">
       <c r="C76">
         <v>9</v>
       </c>
@@ -4534,11 +4653,8 @@
       <c r="E76" t="s">
         <v>9</v>
       </c>
-      <c r="G76" s="4"/>
-      <c r="H76" s="4"/>
-      <c r="I76" s="4"/>
-    </row>
-    <row r="77" spans="2:9">
+    </row>
+    <row r="77" spans="2:12">
       <c r="C77">
         <v>10</v>
       </c>
@@ -4548,17 +4664,17 @@
       <c r="E77" t="s">
         <v>10</v>
       </c>
-      <c r="G77" s="4" t="s">
+      <c r="G77" t="s">
         <v>255</v>
       </c>
-      <c r="H77" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="I77" s="5">
+      <c r="H77" t="s">
+        <v>7</v>
+      </c>
+      <c r="I77" s="1">
         <v>46097</v>
       </c>
     </row>
-    <row r="78" spans="2:9">
+    <row r="78" spans="2:12">
       <c r="C78">
         <v>11</v>
       </c>
@@ -4571,11 +4687,8 @@
       <c r="F78" s="1">
         <v>46090</v>
       </c>
-      <c r="G78" s="4"/>
-      <c r="H78" s="4"/>
-      <c r="I78" s="4"/>
-    </row>
-    <row r="79" spans="2:9">
+    </row>
+    <row r="79" spans="2:12">
       <c r="C79">
         <v>12</v>
       </c>
@@ -4585,11 +4698,8 @@
       <c r="E79" t="s">
         <v>12</v>
       </c>
-      <c r="G79" s="4"/>
-      <c r="H79" s="4"/>
-      <c r="I79" s="4"/>
-    </row>
-    <row r="80" spans="2:9">
+    </row>
+    <row r="80" spans="2:12">
       <c r="C80">
         <v>13</v>
       </c>
@@ -4599,17 +4709,17 @@
       <c r="E80" t="s">
         <v>12</v>
       </c>
-      <c r="G80" s="4" t="s">
+      <c r="G80" t="s">
         <v>255</v>
       </c>
-      <c r="H80" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="I80" s="5">
+      <c r="H80" t="s">
+        <v>6</v>
+      </c>
+      <c r="I80" s="1">
         <v>46097</v>
       </c>
     </row>
-    <row r="81" spans="3:9">
+    <row r="81" spans="3:12">
       <c r="C81">
         <v>14</v>
       </c>
@@ -4619,11 +4729,8 @@
       <c r="E81" t="s">
         <v>11</v>
       </c>
-      <c r="G81" s="4"/>
-      <c r="H81" s="4"/>
-      <c r="I81" s="4"/>
-    </row>
-    <row r="82" spans="3:9">
+    </row>
+    <row r="82" spans="3:12">
       <c r="C82">
         <v>15</v>
       </c>
@@ -4636,17 +4743,17 @@
       <c r="F82" s="1">
         <v>46091</v>
       </c>
-      <c r="G82" s="4" t="s">
+      <c r="G82" t="s">
         <v>255</v>
       </c>
-      <c r="H82" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="I82" s="5">
+      <c r="H82" t="s">
+        <v>6</v>
+      </c>
+      <c r="I82" s="1">
         <v>46104</v>
       </c>
     </row>
-    <row r="83" spans="3:9">
+    <row r="83" spans="3:12">
       <c r="C83">
         <v>16</v>
       </c>
@@ -4656,11 +4763,8 @@
       <c r="E83" t="s">
         <v>12</v>
       </c>
-      <c r="G83" s="4"/>
-      <c r="H83" s="4"/>
-      <c r="I83" s="4"/>
-    </row>
-    <row r="84" spans="3:9">
+    </row>
+    <row r="84" spans="3:12">
       <c r="C84">
         <v>17</v>
       </c>
@@ -4670,17 +4774,17 @@
       <c r="E84" t="s">
         <v>9</v>
       </c>
-      <c r="G84" s="4" t="s">
+      <c r="G84" t="s">
         <v>255</v>
       </c>
-      <c r="H84" s="4" t="s">
+      <c r="H84" t="s">
         <v>147</v>
       </c>
-      <c r="I84" s="5">
+      <c r="I84" s="1">
         <v>46104</v>
       </c>
     </row>
-    <row r="85" spans="3:9">
+    <row r="85" spans="3:12">
       <c r="C85">
         <v>18</v>
       </c>
@@ -4690,11 +4794,8 @@
       <c r="E85" t="s">
         <v>10</v>
       </c>
-      <c r="G85" s="4"/>
-      <c r="H85" s="4"/>
-      <c r="I85" s="4"/>
-    </row>
-    <row r="86" spans="3:9">
+    </row>
+    <row r="86" spans="3:12">
       <c r="C86">
         <v>19</v>
       </c>
@@ -4704,11 +4805,8 @@
       <c r="E86" t="s">
         <v>11</v>
       </c>
-      <c r="G86" s="4"/>
-      <c r="H86" s="4"/>
-      <c r="I86" s="4"/>
-    </row>
-    <row r="87" spans="3:9">
+    </row>
+    <row r="87" spans="3:12">
       <c r="C87">
         <v>20</v>
       </c>
@@ -4718,11 +4816,8 @@
       <c r="E87" t="s">
         <v>12</v>
       </c>
-      <c r="G87" s="4"/>
-      <c r="H87" s="4"/>
-      <c r="I87" s="4"/>
-    </row>
-    <row r="88" spans="3:9">
+    </row>
+    <row r="88" spans="3:12">
       <c r="C88">
         <v>21</v>
       </c>
@@ -4732,11 +4827,8 @@
       <c r="E88" t="s">
         <v>11</v>
       </c>
-      <c r="G88" s="4"/>
-      <c r="H88" s="4"/>
-      <c r="I88" s="4"/>
-    </row>
-    <row r="89" spans="3:9">
+    </row>
+    <row r="89" spans="3:12">
       <c r="C89">
         <v>22</v>
       </c>
@@ -4746,11 +4838,8 @@
       <c r="E89" t="s">
         <v>12</v>
       </c>
-      <c r="G89" s="4"/>
-      <c r="H89" s="4"/>
-      <c r="I89" s="4"/>
-    </row>
-    <row r="90" spans="3:9">
+    </row>
+    <row r="90" spans="3:12">
       <c r="C90">
         <v>23</v>
       </c>
@@ -4760,11 +4849,8 @@
       <c r="E90" t="s">
         <v>9</v>
       </c>
-      <c r="G90" s="4"/>
-      <c r="H90" s="4"/>
-      <c r="I90" s="4"/>
-    </row>
-    <row r="91" spans="3:9">
+    </row>
+    <row r="91" spans="3:12">
       <c r="C91">
         <v>24</v>
       </c>
@@ -4774,17 +4860,26 @@
       <c r="E91" t="s">
         <v>11</v>
       </c>
-      <c r="G91" s="6" t="s">
+      <c r="G91" s="2" t="s">
         <v>254</v>
       </c>
-      <c r="H91" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="I91" s="5">
+      <c r="H91" t="s">
+        <v>5</v>
+      </c>
+      <c r="I91" s="1">
         <v>46104</v>
       </c>
-    </row>
-    <row r="92" spans="3:9">
+      <c r="J91" t="s">
+        <v>255</v>
+      </c>
+      <c r="K91" t="s">
+        <v>12</v>
+      </c>
+      <c r="L91" s="1">
+        <v>46105</v>
+      </c>
+    </row>
+    <row r="92" spans="3:12">
       <c r="C92">
         <v>25</v>
       </c>
@@ -4794,11 +4889,8 @@
       <c r="E92" t="s">
         <v>11</v>
       </c>
-      <c r="G92" s="4"/>
-      <c r="H92" s="4"/>
-      <c r="I92" s="4"/>
-    </row>
-    <row r="93" spans="3:9">
+    </row>
+    <row r="93" spans="3:12">
       <c r="C93">
         <v>26</v>
       </c>
@@ -4808,17 +4900,17 @@
       <c r="E93" t="s">
         <v>9</v>
       </c>
-      <c r="G93" s="4" t="s">
+      <c r="G93" t="s">
         <v>255</v>
       </c>
-      <c r="H93" s="4" t="s">
+      <c r="H93" t="s">
         <v>147</v>
       </c>
-      <c r="I93" s="5">
+      <c r="I93" s="1">
         <v>46104</v>
       </c>
     </row>
-    <row r="94" spans="3:9">
+    <row r="94" spans="3:12">
       <c r="C94">
         <v>27</v>
       </c>
@@ -4828,17 +4920,26 @@
       <c r="E94" t="s">
         <v>9</v>
       </c>
-      <c r="G94" s="6" t="s">
+      <c r="G94" s="2" t="s">
         <v>254</v>
       </c>
-      <c r="H94" s="4" t="s">
+      <c r="H94" t="s">
         <v>147</v>
       </c>
-      <c r="I94" s="5">
+      <c r="I94" s="1">
         <v>46104</v>
       </c>
-    </row>
-    <row r="95" spans="3:9">
+      <c r="J94" t="s">
+        <v>255</v>
+      </c>
+      <c r="K94" t="s">
+        <v>12</v>
+      </c>
+      <c r="L94" s="1">
+        <v>46105</v>
+      </c>
+    </row>
+    <row r="95" spans="3:12">
       <c r="C95">
         <v>28</v>
       </c>
@@ -4848,17 +4949,26 @@
       <c r="E95" t="s">
         <v>9</v>
       </c>
-      <c r="G95" s="6" t="s">
+      <c r="G95" s="2" t="s">
         <v>254</v>
       </c>
-      <c r="H95" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="I95" s="5">
+      <c r="H95" t="s">
+        <v>5</v>
+      </c>
+      <c r="I95" s="1">
         <v>46104</v>
       </c>
-    </row>
-    <row r="96" spans="3:9">
+      <c r="J95" t="s">
+        <v>255</v>
+      </c>
+      <c r="K95" t="s">
+        <v>12</v>
+      </c>
+      <c r="L95" s="1">
+        <v>46105</v>
+      </c>
+    </row>
+    <row r="96" spans="3:12">
       <c r="C96">
         <v>29</v>
       </c>
@@ -4868,11 +4978,8 @@
       <c r="E96" t="s">
         <v>10</v>
       </c>
-      <c r="G96" s="4"/>
-      <c r="H96" s="4"/>
-      <c r="I96" s="4"/>
-    </row>
-    <row r="97" spans="3:9">
+    </row>
+    <row r="97" spans="3:12">
       <c r="C97">
         <v>30</v>
       </c>
@@ -4882,11 +4989,8 @@
       <c r="E97" t="s">
         <v>12</v>
       </c>
-      <c r="G97" s="4"/>
-      <c r="H97" s="4"/>
-      <c r="I97" s="4"/>
-    </row>
-    <row r="98" spans="3:9">
+    </row>
+    <row r="98" spans="3:12">
       <c r="C98">
         <v>31</v>
       </c>
@@ -4896,11 +5000,8 @@
       <c r="E98" t="s">
         <v>9</v>
       </c>
-      <c r="G98" s="4"/>
-      <c r="H98" s="4"/>
-      <c r="I98" s="4"/>
-    </row>
-    <row r="99" spans="3:9">
+    </row>
+    <row r="99" spans="3:12">
       <c r="C99">
         <v>32</v>
       </c>
@@ -4910,17 +5011,26 @@
       <c r="E99" t="s">
         <v>12</v>
       </c>
-      <c r="G99" s="6" t="s">
+      <c r="G99" s="2" t="s">
         <v>254</v>
       </c>
-      <c r="H99" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="I99" s="5">
+      <c r="H99" t="s">
+        <v>7</v>
+      </c>
+      <c r="I99" s="1">
         <v>46104</v>
       </c>
-    </row>
-    <row r="100" spans="3:9">
+      <c r="J99" t="s">
+        <v>255</v>
+      </c>
+      <c r="K99" t="s">
+        <v>10</v>
+      </c>
+      <c r="L99" s="1">
+        <v>46105</v>
+      </c>
+    </row>
+    <row r="100" spans="3:12">
       <c r="C100">
         <v>33</v>
       </c>
@@ -4930,11 +5040,8 @@
       <c r="E100" t="s">
         <v>10</v>
       </c>
-      <c r="G100" s="4"/>
-      <c r="H100" s="4"/>
-      <c r="I100" s="4"/>
-    </row>
-    <row r="101" spans="3:9">
+    </row>
+    <row r="101" spans="3:12">
       <c r="C101">
         <v>34</v>
       </c>
@@ -4944,17 +5051,17 @@
       <c r="E101" t="s">
         <v>11</v>
       </c>
-      <c r="G101" s="4" t="s">
+      <c r="G101" t="s">
         <v>255</v>
       </c>
-      <c r="H101" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="I101" s="5">
+      <c r="H101" t="s">
+        <v>7</v>
+      </c>
+      <c r="I101" s="1">
         <v>46104</v>
       </c>
     </row>
-    <row r="102" spans="3:9">
+    <row r="102" spans="3:12">
       <c r="C102">
         <v>35</v>
       </c>
@@ -4964,17 +5071,26 @@
       <c r="E102" t="s">
         <v>11</v>
       </c>
-      <c r="G102" s="6" t="s">
+      <c r="G102" s="2" t="s">
         <v>254</v>
       </c>
-      <c r="H102" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="I102" s="5">
+      <c r="H102" t="s">
+        <v>6</v>
+      </c>
+      <c r="I102" s="1">
         <v>46104</v>
       </c>
-    </row>
-    <row r="103" spans="3:9">
+      <c r="J102" t="s">
+        <v>255</v>
+      </c>
+      <c r="K102" t="s">
+        <v>9</v>
+      </c>
+      <c r="L102" s="1">
+        <v>46105</v>
+      </c>
+    </row>
+    <row r="103" spans="3:12">
       <c r="C103">
         <v>36</v>
       </c>
@@ -4984,11 +5100,8 @@
       <c r="E103" t="s">
         <v>9</v>
       </c>
-      <c r="G103" s="4"/>
-      <c r="H103" s="4"/>
-      <c r="I103" s="4"/>
-    </row>
-    <row r="104" spans="3:9">
+    </row>
+    <row r="104" spans="3:12">
       <c r="C104">
         <v>37</v>
       </c>
@@ -4998,17 +5111,26 @@
       <c r="E104" t="s">
         <v>12</v>
       </c>
-      <c r="G104" s="6" t="s">
+      <c r="G104" s="2" t="s">
         <v>254</v>
       </c>
-      <c r="H104" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="I104" s="5">
+      <c r="H104" t="s">
+        <v>5</v>
+      </c>
+      <c r="I104" s="1">
         <v>46104</v>
       </c>
-    </row>
-    <row r="105" spans="3:9">
+      <c r="J104" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="K104" t="s">
+        <v>9</v>
+      </c>
+      <c r="L104" s="1">
+        <v>46105</v>
+      </c>
+    </row>
+    <row r="105" spans="3:12">
       <c r="C105">
         <v>38</v>
       </c>
@@ -5018,11 +5140,8 @@
       <c r="E105" t="s">
         <v>11</v>
       </c>
-      <c r="G105" s="4"/>
-      <c r="H105" s="4"/>
-      <c r="I105" s="4"/>
-    </row>
-    <row r="106" spans="3:9">
+    </row>
+    <row r="106" spans="3:12">
       <c r="C106">
         <v>39</v>
       </c>
@@ -5032,17 +5151,26 @@
       <c r="E106" t="s">
         <v>9</v>
       </c>
-      <c r="G106" s="6" t="s">
+      <c r="G106" s="2" t="s">
         <v>254</v>
       </c>
-      <c r="H106" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="I106" s="5">
+      <c r="H106" t="s">
+        <v>6</v>
+      </c>
+      <c r="I106" s="1">
         <v>46104</v>
       </c>
-    </row>
-    <row r="107" spans="3:9">
+      <c r="J106" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="K106" t="s">
+        <v>11</v>
+      </c>
+      <c r="L106" s="1">
+        <v>46105</v>
+      </c>
+    </row>
+    <row r="107" spans="3:12">
       <c r="C107">
         <v>40</v>
       </c>
@@ -5053,7 +5181,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="108" spans="3:9">
+    <row r="108" spans="3:12">
       <c r="D108" s="3">
         <f>COUNTIF(D2:D107,"○")/COUNTA(D2:D107)</f>
         <v>0.59433962264150941</v>
@@ -5069,6 +5197,10 @@
       <c r="H108" s="3">
         <f>COUNTIF(G68:G107,"○")/COUNTA(G68:G107)</f>
         <v>0.46153846153846156</v>
+      </c>
+      <c r="J108" s="3">
+        <f>COUNTIF(J2:J107,"○")/COUNTA(J2:J107)</f>
+        <v>0.61538461538461542</v>
       </c>
     </row>
   </sheetData>

--- a/JSTQB_Foundation.xlsx
+++ b/JSTQB_Foundation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ドキュメント\その他\eラーニング\JSTQB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{120FF5B3-699F-4748-A5FE-3D5B280142DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BED4A523-E5F1-42B6-B778-D6F614AA3E1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="テス友" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="832" uniqueCount="256">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="834" uniqueCount="256">
   <si>
     <t>典型的なテストの目的として、誤っているものはどれか。次の選択肢の中から1つ選びなさい。</t>
     <phoneticPr fontId="1"/>
@@ -3335,7 +3335,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CFBD2AC0-38EC-4B9C-A0BF-1559C25A244C}">
   <sheetPr codeName="Sheet3"/>
-  <dimension ref="B2:L108"/>
+  <dimension ref="B2:O108"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="5" max="5" width="8.6640625" hidden="1" customWidth="1"/>
@@ -3343,10 +3343,12 @@
     <col min="7" max="7" width="8.6640625" customWidth="1"/>
     <col min="8" max="8" width="0" hidden="1" customWidth="1"/>
     <col min="9" max="9" width="10.1640625" hidden="1" customWidth="1"/>
-    <col min="12" max="12" width="10.25" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="0" hidden="1" customWidth="1"/>
+    <col min="12" max="12" width="10.25" hidden="1" customWidth="1"/>
+    <col min="15" max="15" width="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:12">
+    <row r="2" spans="2:15">
       <c r="B2">
         <v>1</v>
       </c>
@@ -3363,7 +3365,7 @@
         <v>46075</v>
       </c>
     </row>
-    <row r="3" spans="2:12">
+    <row r="3" spans="2:15">
       <c r="C3">
         <v>2</v>
       </c>
@@ -3374,7 +3376,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="2:12">
+    <row r="4" spans="2:15">
       <c r="C4">
         <v>3</v>
       </c>
@@ -3385,7 +3387,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="2:12">
+    <row r="5" spans="2:15">
       <c r="C5">
         <v>4</v>
       </c>
@@ -3405,7 +3407,7 @@
         <v>46092</v>
       </c>
     </row>
-    <row r="6" spans="2:12">
+    <row r="6" spans="2:15">
       <c r="C6">
         <v>5</v>
       </c>
@@ -3416,7 +3418,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="2:12">
+    <row r="7" spans="2:15">
       <c r="C7">
         <v>6</v>
       </c>
@@ -3445,7 +3447,7 @@
         <v>46104</v>
       </c>
     </row>
-    <row r="8" spans="2:12">
+    <row r="8" spans="2:15">
       <c r="C8">
         <v>7</v>
       </c>
@@ -3465,7 +3467,7 @@
         <v>46092</v>
       </c>
     </row>
-    <row r="9" spans="2:12">
+    <row r="9" spans="2:15">
       <c r="C9">
         <v>8</v>
       </c>
@@ -3476,7 +3478,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="2:12">
+    <row r="10" spans="2:15">
       <c r="C10">
         <v>9</v>
       </c>
@@ -3496,7 +3498,7 @@
         <v>46092</v>
       </c>
     </row>
-    <row r="11" spans="2:12">
+    <row r="11" spans="2:15">
       <c r="C11">
         <v>10</v>
       </c>
@@ -3525,7 +3527,7 @@
         <v>46104</v>
       </c>
     </row>
-    <row r="12" spans="2:12">
+    <row r="12" spans="2:15">
       <c r="C12">
         <v>11</v>
       </c>
@@ -3553,8 +3555,17 @@
       <c r="L12" s="1">
         <v>46104</v>
       </c>
-    </row>
-    <row r="13" spans="2:12">
+      <c r="M12" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="N12" t="s">
+        <v>12</v>
+      </c>
+      <c r="O12" s="1">
+        <v>46106</v>
+      </c>
+    </row>
+    <row r="13" spans="2:15">
       <c r="C13">
         <v>12</v>
       </c>
@@ -3583,7 +3594,7 @@
         <v>46104</v>
       </c>
     </row>
-    <row r="14" spans="2:12">
+    <row r="14" spans="2:15">
       <c r="C14">
         <v>13</v>
       </c>
@@ -3603,7 +3614,7 @@
         <v>46092</v>
       </c>
     </row>
-    <row r="15" spans="2:12">
+    <row r="15" spans="2:15">
       <c r="C15">
         <v>14</v>
       </c>
@@ -3614,7 +3625,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="16" spans="2:12">
+    <row r="16" spans="2:15">
       <c r="C16">
         <v>15</v>
       </c>
@@ -3625,7 +3636,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="17" spans="2:12">
+    <row r="17" spans="2:15">
       <c r="C17">
         <v>16</v>
       </c>
@@ -3636,7 +3647,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="18" spans="2:12">
+    <row r="18" spans="2:15">
       <c r="B18">
         <v>2</v>
       </c>
@@ -3662,7 +3673,7 @@
         <v>46092</v>
       </c>
     </row>
-    <row r="19" spans="2:12">
+    <row r="19" spans="2:15">
       <c r="C19">
         <v>2</v>
       </c>
@@ -3673,7 +3684,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="20" spans="2:12">
+    <row r="20" spans="2:15">
       <c r="C20">
         <v>3</v>
       </c>
@@ -3684,7 +3695,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="21" spans="2:12">
+    <row r="21" spans="2:15">
       <c r="C21">
         <v>4</v>
       </c>
@@ -3695,7 +3706,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="22" spans="2:12">
+    <row r="22" spans="2:15">
       <c r="C22">
         <v>5</v>
       </c>
@@ -3706,7 +3717,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="23" spans="2:12">
+    <row r="23" spans="2:15">
       <c r="C23">
         <v>6</v>
       </c>
@@ -3734,8 +3745,11 @@
       <c r="L23" s="1">
         <v>46105</v>
       </c>
-    </row>
-    <row r="24" spans="2:12">
+      <c r="O23" s="1">
+        <v>46106</v>
+      </c>
+    </row>
+    <row r="24" spans="2:15">
       <c r="C24">
         <v>7</v>
       </c>
@@ -3746,7 +3760,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="25" spans="2:12">
+    <row r="25" spans="2:15">
       <c r="C25">
         <v>8</v>
       </c>
@@ -3775,7 +3789,7 @@
         <v>46105</v>
       </c>
     </row>
-    <row r="26" spans="2:12">
+    <row r="26" spans="2:15">
       <c r="C26">
         <v>9</v>
       </c>
@@ -3786,7 +3800,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="27" spans="2:12">
+    <row r="27" spans="2:15">
       <c r="C27">
         <v>10</v>
       </c>
@@ -3797,7 +3811,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="28" spans="2:12">
+    <row r="28" spans="2:15">
       <c r="C28">
         <v>11</v>
       </c>
@@ -3826,7 +3840,7 @@
         <v>46105</v>
       </c>
     </row>
-    <row r="29" spans="2:12">
+    <row r="29" spans="2:15">
       <c r="C29">
         <v>12</v>
       </c>
@@ -3846,7 +3860,7 @@
         <v>46093</v>
       </c>
     </row>
-    <row r="30" spans="2:12">
+    <row r="30" spans="2:15">
       <c r="C30">
         <v>13</v>
       </c>
@@ -3857,7 +3871,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="31" spans="2:12">
+    <row r="31" spans="2:15">
       <c r="C31">
         <v>14</v>
       </c>
@@ -3886,7 +3900,7 @@
         <v>46105</v>
       </c>
     </row>
-    <row r="32" spans="2:12">
+    <row r="32" spans="2:15">
       <c r="C32">
         <v>15</v>
       </c>

--- a/JSTQB_Foundation.xlsx
+++ b/JSTQB_Foundation.xlsx
@@ -1,21 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27932"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ドキュメント\その他\eラーニング\JSTQB\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ドキュメント\勉強\資格(取得)\JSTQB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BED4A523-E5F1-42B6-B778-D6F614AA3E1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6DE5720-C978-48D6-B118-8D207D0CDC33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="テス友" sheetId="1" r:id="rId1"/>
-    <sheet name="2011" sheetId="2" r:id="rId2"/>
-    <sheet name="2023" sheetId="3" r:id="rId3"/>
+    <sheet name="テス友_解答" sheetId="5" r:id="rId2"/>
+    <sheet name="2011" sheetId="2" r:id="rId3"/>
+    <sheet name="2011_解答" sheetId="4" r:id="rId4"/>
+    <sheet name="2023" sheetId="3" r:id="rId5"/>
+    <sheet name="Udemy_概要" sheetId="6" r:id="rId6"/>
+    <sheet name="Udemy_概要_解答" sheetId="7" r:id="rId7"/>
+    <sheet name="Udemy_JSTQB" sheetId="8" r:id="rId8"/>
+    <sheet name="Udemy_JSTQB_解答" sheetId="9" r:id="rId9"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -33,12 +39,15 @@
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="834" uniqueCount="256">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1027" uniqueCount="277">
   <si>
     <t>典型的なテストの目的として、誤っているものはどれか。次の選択肢の中から1つ選びなさい。</t>
     <phoneticPr fontId="1"/>
@@ -950,6 +959,243 @@
   </si>
   <si>
     <t>○</t>
+  </si>
+  <si>
+    <t>ソフトウェアテストの目的として正しいものをすべて選びなさい。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>E</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>F</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ソフトウェアを早く完成させる</t>
+    <rPh sb="7" eb="8">
+      <t>ハヤ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>カンセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>欠陥を発見する</t>
+    <rPh sb="0" eb="2">
+      <t>ケッカン</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ハッケン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>品質を評価する</t>
+    <rPh sb="0" eb="2">
+      <t>ヒンシツ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ヒョウカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ネットワークを作る</t>
+    <rPh sb="7" eb="8">
+      <t>ツク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>妥当性を確認する</t>
+    <rPh sb="0" eb="3">
+      <t>ダトウセイ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>カクニン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>利用者数を増やす</t>
+    <rPh sb="0" eb="3">
+      <t>リヨウシャ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>スウ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>フ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>静的テストの具体例として正しいものをすべて選びなさい</t>
+    <rPh sb="0" eb="2">
+      <t>セイテキ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>グタイ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>レイ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>タダ</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>エラ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>設計図（要件定義書）のレビュー</t>
+    <rPh sb="0" eb="3">
+      <t>セッケイズ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ヨウケン</t>
+    </rPh>
+    <rPh sb="6" eb="9">
+      <t>テイギショ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アプリを実際に操作して確認する</t>
+    <rPh sb="4" eb="6">
+      <t>ジッサイ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ソウサ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>カクニン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ソースコードのレビュー</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>銀行アプリで送金動作を確認する</t>
+    <rPh sb="0" eb="2">
+      <t>ギンコウ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ソウキン</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ドウサ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>カクニン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>要件定義書の矛盾を指摘する</t>
+    <rPh sb="0" eb="2">
+      <t>ヨウケン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>テイギ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ショ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ムジュン</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>シテキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>実機での速度を測る</t>
+    <rPh sb="0" eb="2">
+      <t>ジッキ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ソクド</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>ハカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>以下のうち、ソフトウェアテストの目的として最も適切なものを選んでください</t>
+    <rPh sb="0" eb="2">
+      <t>イカ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>モクテキ</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>モット</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>テキセツ</t>
+    </rPh>
+    <rPh sb="29" eb="30">
+      <t>エラ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ソフトウェアの開発期間を短縮するため</t>
+    <rPh sb="7" eb="9">
+      <t>カイハツ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>キカン</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>タンシュク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ソフトウェアがユーザーの期待通りに動作することを確認するため</t>
+    <rPh sb="12" eb="14">
+      <t>キタイ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>ドオ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>ドウサ</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>カクニン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ソフトウェアのすべてのバグを完全に修正するため</t>
+    <rPh sb="14" eb="16">
+      <t>カンゼン</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>シュウセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ソフトウェアの機能を拡張するため</t>
+    <rPh sb="7" eb="9">
+      <t>キノウ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>カクチョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
   </si>
 </sst>
 </file>
@@ -1042,7 +1288,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>3371850</xdr:colOff>
+      <xdr:colOff>3368040</xdr:colOff>
       <xdr:row>39</xdr:row>
       <xdr:rowOff>131445</xdr:rowOff>
     </xdr:to>
@@ -1361,30 +1607,40 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="B2:D243"/>
+  <dimension ref="B2:J244"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
-    <col min="2" max="3" width="3.33203125" customWidth="1"/>
-    <col min="4" max="4" width="85.4140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="3.296875" customWidth="1"/>
+    <col min="4" max="4" width="85.3984375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.19921875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:4">
-      <c r="B2" t="s">
+    <row r="2" spans="2:10">
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="2:4">
+    <row r="3" spans="2:10">
       <c r="C3" t="s">
         <v>15</v>
       </c>
       <c r="D3" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="2:4">
-      <c r="B4" t="s">
-        <v>8</v>
-      </c>
+      <c r="H3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I3" t="s">
+        <v>9</v>
+      </c>
+      <c r="J3" s="1">
+        <v>46109</v>
+      </c>
+    </row>
+    <row r="4" spans="2:10">
       <c r="C4" t="s">
         <v>5</v>
       </c>
@@ -1392,7 +1648,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="2:4">
+    <row r="5" spans="2:10">
       <c r="C5" t="s">
         <v>6</v>
       </c>
@@ -1400,7 +1656,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="2:4">
+    <row r="6" spans="2:10">
       <c r="C6" t="s">
         <v>7</v>
       </c>
@@ -1408,23 +1664,32 @@
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="2:4">
-      <c r="B8" t="s">
+    <row r="8" spans="2:10">
+      <c r="B8">
+        <v>2</v>
+      </c>
+      <c r="C8" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="2:4">
+    <row r="9" spans="2:10">
       <c r="C9" t="s">
         <v>15</v>
       </c>
       <c r="D9" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="10" spans="2:4">
-      <c r="B10" t="s">
-        <v>8</v>
-      </c>
+      <c r="H9" t="s">
+        <v>8</v>
+      </c>
+      <c r="I9" t="s">
+        <v>9</v>
+      </c>
+      <c r="J9" s="1">
+        <v>46109</v>
+      </c>
+    </row>
+    <row r="10" spans="2:10">
       <c r="C10" t="s">
         <v>5</v>
       </c>
@@ -1432,7 +1697,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="11" spans="2:4">
+    <row r="11" spans="2:10">
       <c r="C11" t="s">
         <v>6</v>
       </c>
@@ -1440,7 +1705,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="12" spans="2:4">
+    <row r="12" spans="2:10">
       <c r="C12" t="s">
         <v>7</v>
       </c>
@@ -1448,23 +1713,32 @@
         <v>18</v>
       </c>
     </row>
-    <row r="14" spans="2:4">
-      <c r="B14" t="s">
+    <row r="14" spans="2:10">
+      <c r="B14">
+        <v>3</v>
+      </c>
+      <c r="C14" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="15" spans="2:4">
+    <row r="15" spans="2:10">
       <c r="C15" t="s">
         <v>15</v>
       </c>
       <c r="D15" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="16" spans="2:4">
-      <c r="B16" t="s">
-        <v>8</v>
-      </c>
+      <c r="H15" t="s">
+        <v>8</v>
+      </c>
+      <c r="I15" t="s">
+        <v>9</v>
+      </c>
+      <c r="J15" s="1">
+        <v>46109</v>
+      </c>
+    </row>
+    <row r="16" spans="2:10">
       <c r="C16" t="s">
         <v>5</v>
       </c>
@@ -1472,7 +1746,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="17" spans="2:4">
+    <row r="17" spans="2:10">
       <c r="C17" t="s">
         <v>6</v>
       </c>
@@ -1480,7 +1754,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="18" spans="2:4">
+    <row r="18" spans="2:10">
       <c r="C18" t="s">
         <v>7</v>
       </c>
@@ -1488,23 +1762,32 @@
         <v>21</v>
       </c>
     </row>
-    <row r="20" spans="2:4">
-      <c r="B20" t="s">
+    <row r="20" spans="2:10">
+      <c r="B20">
+        <v>4</v>
+      </c>
+      <c r="C20" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="21" spans="2:4">
+    <row r="21" spans="2:10">
       <c r="C21" t="s">
         <v>15</v>
       </c>
       <c r="D21" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="22" spans="2:4">
-      <c r="B22" t="s">
-        <v>8</v>
-      </c>
+      <c r="H21" t="s">
+        <v>8</v>
+      </c>
+      <c r="I21" t="s">
+        <v>9</v>
+      </c>
+      <c r="J21" s="1">
+        <v>46109</v>
+      </c>
+    </row>
+    <row r="22" spans="2:10">
       <c r="C22" t="s">
         <v>5</v>
       </c>
@@ -1512,7 +1795,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="23" spans="2:4">
+    <row r="23" spans="2:10">
       <c r="C23" t="s">
         <v>6</v>
       </c>
@@ -1520,7 +1803,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="24" spans="2:4">
+    <row r="24" spans="2:10">
       <c r="C24" t="s">
         <v>7</v>
       </c>
@@ -1528,23 +1811,32 @@
         <v>24</v>
       </c>
     </row>
-    <row r="26" spans="2:4">
-      <c r="B26" t="s">
+    <row r="26" spans="2:10">
+      <c r="B26">
+        <v>5</v>
+      </c>
+      <c r="C26" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="27" spans="2:4">
-      <c r="B27" t="s">
-        <v>8</v>
-      </c>
+    <row r="27" spans="2:10">
       <c r="C27" t="s">
         <v>15</v>
       </c>
       <c r="D27" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="28" spans="2:4">
+      <c r="H27" t="s">
+        <v>8</v>
+      </c>
+      <c r="I27" t="s">
+        <v>10</v>
+      </c>
+      <c r="J27" s="1">
+        <v>46109</v>
+      </c>
+    </row>
+    <row r="28" spans="2:10">
       <c r="C28" t="s">
         <v>5</v>
       </c>
@@ -1552,7 +1844,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="29" spans="2:4">
+    <row r="29" spans="2:10">
       <c r="C29" t="s">
         <v>6</v>
       </c>
@@ -1560,7 +1852,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="30" spans="2:4">
+    <row r="30" spans="2:10">
       <c r="C30" t="s">
         <v>7</v>
       </c>
@@ -1568,20 +1860,32 @@
         <v>34</v>
       </c>
     </row>
-    <row r="32" spans="2:4">
-      <c r="B32" t="s">
+    <row r="32" spans="2:10">
+      <c r="B32">
+        <v>6</v>
+      </c>
+      <c r="C32" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="33" spans="2:4">
+    <row r="33" spans="2:10">
       <c r="C33" t="s">
         <v>15</v>
       </c>
       <c r="D33" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="34" spans="2:4">
+      <c r="H33" t="s">
+        <v>8</v>
+      </c>
+      <c r="I33" t="s">
+        <v>11</v>
+      </c>
+      <c r="J33" s="1">
+        <v>46109</v>
+      </c>
+    </row>
+    <row r="34" spans="2:10">
       <c r="C34" t="s">
         <v>5</v>
       </c>
@@ -1589,10 +1893,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="35" spans="2:4">
-      <c r="B35" t="s">
-        <v>8</v>
-      </c>
+    <row r="35" spans="2:10">
       <c r="C35" t="s">
         <v>6</v>
       </c>
@@ -1600,7 +1901,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="36" spans="2:4">
+    <row r="36" spans="2:10">
       <c r="C36" t="s">
         <v>7</v>
       </c>
@@ -1608,20 +1909,32 @@
         <v>39</v>
       </c>
     </row>
-    <row r="38" spans="2:4">
-      <c r="B38" t="s">
+    <row r="38" spans="2:10">
+      <c r="B38">
+        <v>7</v>
+      </c>
+      <c r="C38" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="39" spans="2:4">
+    <row r="39" spans="2:10">
       <c r="C39" t="s">
         <v>15</v>
       </c>
       <c r="D39" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="40" spans="2:4">
+      <c r="H39" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I39" t="s">
+        <v>10</v>
+      </c>
+      <c r="J39" s="1">
+        <v>46109</v>
+      </c>
+    </row>
+    <row r="40" spans="2:10">
       <c r="C40" t="s">
         <v>5</v>
       </c>
@@ -1629,7 +1942,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="41" spans="2:4">
+    <row r="41" spans="2:10">
       <c r="C41" t="s">
         <v>6</v>
       </c>
@@ -1637,10 +1950,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="42" spans="2:4">
-      <c r="B42" t="s">
-        <v>8</v>
-      </c>
+    <row r="42" spans="2:10">
       <c r="C42" t="s">
         <v>7</v>
       </c>
@@ -1648,20 +1958,32 @@
         <v>44</v>
       </c>
     </row>
-    <row r="44" spans="2:4">
-      <c r="B44" t="s">
+    <row r="44" spans="2:10">
+      <c r="B44">
+        <v>8</v>
+      </c>
+      <c r="C44" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="45" spans="2:4">
+    <row r="45" spans="2:10">
       <c r="C45" t="s">
         <v>15</v>
       </c>
       <c r="D45" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="46" spans="2:4">
+      <c r="H45" t="s">
+        <v>8</v>
+      </c>
+      <c r="I45" t="s">
+        <v>12</v>
+      </c>
+      <c r="J45" s="1">
+        <v>46109</v>
+      </c>
+    </row>
+    <row r="46" spans="2:10">
       <c r="C46" t="s">
         <v>5</v>
       </c>
@@ -1669,7 +1991,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="47" spans="2:4">
+    <row r="47" spans="2:10">
       <c r="C47" t="s">
         <v>6</v>
       </c>
@@ -1677,10 +1999,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="48" spans="2:4">
-      <c r="B48" t="s">
-        <v>8</v>
-      </c>
+    <row r="48" spans="2:10">
       <c r="C48" t="s">
         <v>7</v>
       </c>
@@ -1688,25 +2007,37 @@
         <v>48</v>
       </c>
     </row>
-    <row r="50" spans="2:4">
-      <c r="B50" t="s">
+    <row r="50" spans="2:10">
+      <c r="B50">
+        <v>9</v>
+      </c>
+      <c r="C50" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="51" spans="2:4">
-      <c r="B51" t="s">
+    <row r="51" spans="2:10">
+      <c r="C51" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="52" spans="2:4">
+    <row r="52" spans="2:10">
       <c r="C52" t="s">
         <v>15</v>
       </c>
       <c r="D52" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="53" spans="2:4">
+      <c r="H52" t="s">
+        <v>8</v>
+      </c>
+      <c r="I52" t="s">
+        <v>12</v>
+      </c>
+      <c r="J52" s="1">
+        <v>46109</v>
+      </c>
+    </row>
+    <row r="53" spans="2:10">
       <c r="C53" t="s">
         <v>5</v>
       </c>
@@ -1714,7 +2045,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="54" spans="2:4">
+    <row r="54" spans="2:10">
       <c r="C54" t="s">
         <v>6</v>
       </c>
@@ -1722,10 +2053,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="55" spans="2:4">
-      <c r="B55" t="s">
-        <v>8</v>
-      </c>
+    <row r="55" spans="2:10">
       <c r="C55" t="s">
         <v>7</v>
       </c>
@@ -1733,20 +2061,32 @@
         <v>54</v>
       </c>
     </row>
-    <row r="57" spans="2:4">
-      <c r="B57" t="s">
+    <row r="57" spans="2:10">
+      <c r="B57">
+        <v>10</v>
+      </c>
+      <c r="C57" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="58" spans="2:4">
+    <row r="58" spans="2:10">
       <c r="C58" t="s">
         <v>15</v>
       </c>
       <c r="D58" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="59" spans="2:4">
+      <c r="H58" t="s">
+        <v>8</v>
+      </c>
+      <c r="I58" t="s">
+        <v>12</v>
+      </c>
+      <c r="J58" s="1">
+        <v>46109</v>
+      </c>
+    </row>
+    <row r="59" spans="2:10">
       <c r="C59" t="s">
         <v>5</v>
       </c>
@@ -1754,7 +2094,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="60" spans="2:4">
+    <row r="60" spans="2:10">
       <c r="C60" t="s">
         <v>6</v>
       </c>
@@ -1762,10 +2102,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="61" spans="2:4">
-      <c r="B61" t="s">
-        <v>8</v>
-      </c>
+    <row r="61" spans="2:10">
       <c r="C61" t="s">
         <v>7</v>
       </c>
@@ -1773,20 +2110,32 @@
         <v>59</v>
       </c>
     </row>
-    <row r="63" spans="2:4">
-      <c r="B63" t="s">
+    <row r="63" spans="2:10">
+      <c r="B63">
+        <v>11</v>
+      </c>
+      <c r="C63" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="64" spans="2:4">
+    <row r="64" spans="2:10">
       <c r="C64" t="s">
         <v>15</v>
       </c>
       <c r="D64" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="65" spans="2:4">
+      <c r="H64" t="s">
+        <v>8</v>
+      </c>
+      <c r="I64" t="s">
+        <v>12</v>
+      </c>
+      <c r="J64" s="1">
+        <v>46109</v>
+      </c>
+    </row>
+    <row r="65" spans="2:10">
       <c r="C65" t="s">
         <v>5</v>
       </c>
@@ -1794,7 +2143,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="66" spans="2:4">
+    <row r="66" spans="2:10">
       <c r="C66" t="s">
         <v>6</v>
       </c>
@@ -1802,10 +2151,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="67" spans="2:4">
-      <c r="B67" t="s">
-        <v>8</v>
-      </c>
+    <row r="67" spans="2:10">
       <c r="C67" t="s">
         <v>7</v>
       </c>
@@ -1813,20 +2159,32 @@
         <v>64</v>
       </c>
     </row>
-    <row r="69" spans="2:4">
-      <c r="B69" t="s">
+    <row r="69" spans="2:10">
+      <c r="B69">
+        <v>12</v>
+      </c>
+      <c r="C69" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="70" spans="2:4">
+    <row r="70" spans="2:10">
       <c r="C70" t="s">
         <v>15</v>
       </c>
       <c r="D70" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="71" spans="2:4">
+      <c r="H70" t="s">
+        <v>8</v>
+      </c>
+      <c r="I70" t="s">
+        <v>12</v>
+      </c>
+      <c r="J70" s="1">
+        <v>46109</v>
+      </c>
+    </row>
+    <row r="71" spans="2:10">
       <c r="C71" t="s">
         <v>5</v>
       </c>
@@ -1834,7 +2192,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="72" spans="2:4">
+    <row r="72" spans="2:10">
       <c r="C72" t="s">
         <v>6</v>
       </c>
@@ -1842,10 +2200,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="73" spans="2:4">
-      <c r="B73" t="s">
-        <v>8</v>
-      </c>
+    <row r="73" spans="2:10">
       <c r="C73" t="s">
         <v>7</v>
       </c>
@@ -1853,20 +2208,32 @@
         <v>69</v>
       </c>
     </row>
-    <row r="75" spans="2:4">
-      <c r="B75" t="s">
+    <row r="75" spans="2:10">
+      <c r="B75">
+        <v>13</v>
+      </c>
+      <c r="C75" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="76" spans="2:4">
+    <row r="76" spans="2:10">
       <c r="C76" t="s">
         <v>15</v>
       </c>
       <c r="D76" t="s">
         <v>71</v>
       </c>
-    </row>
-    <row r="77" spans="2:4">
+      <c r="H76" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I76" t="s">
+        <v>10</v>
+      </c>
+      <c r="J76" s="1">
+        <v>46109</v>
+      </c>
+    </row>
+    <row r="77" spans="2:10">
       <c r="C77" t="s">
         <v>5</v>
       </c>
@@ -1874,7 +2241,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="78" spans="2:4">
+    <row r="78" spans="2:10">
       <c r="C78" t="s">
         <v>6</v>
       </c>
@@ -1882,10 +2249,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="79" spans="2:4">
-      <c r="B79" t="s">
-        <v>8</v>
-      </c>
+    <row r="79" spans="2:10">
       <c r="C79" t="s">
         <v>7</v>
       </c>
@@ -1893,23 +2257,32 @@
         <v>74</v>
       </c>
     </row>
-    <row r="81" spans="2:4">
-      <c r="B81" t="s">
+    <row r="81" spans="2:10">
+      <c r="B81">
+        <v>14</v>
+      </c>
+      <c r="C81" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="82" spans="2:4">
-      <c r="B82" t="s">
-        <v>8</v>
-      </c>
+    <row r="82" spans="2:10">
       <c r="C82" t="s">
         <v>15</v>
       </c>
       <c r="D82" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="83" spans="2:4">
+      <c r="H82" t="s">
+        <v>8</v>
+      </c>
+      <c r="I82" t="s">
+        <v>10</v>
+      </c>
+      <c r="J82" s="1">
+        <v>46109</v>
+      </c>
+    </row>
+    <row r="83" spans="2:10">
       <c r="C83" t="s">
         <v>5</v>
       </c>
@@ -1917,7 +2290,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="84" spans="2:4">
+    <row r="84" spans="2:10">
       <c r="C84" t="s">
         <v>6</v>
       </c>
@@ -1925,7 +2298,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="85" spans="2:4">
+    <row r="85" spans="2:10">
       <c r="C85" t="s">
         <v>7</v>
       </c>
@@ -1933,20 +2306,32 @@
         <v>79</v>
       </c>
     </row>
-    <row r="87" spans="2:4">
-      <c r="B87" t="s">
+    <row r="87" spans="2:10">
+      <c r="B87">
+        <v>15</v>
+      </c>
+      <c r="C87" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="88" spans="2:4">
+    <row r="88" spans="2:10">
       <c r="C88" t="s">
         <v>15</v>
       </c>
       <c r="D88" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="89" spans="2:4">
+      <c r="H88" t="s">
+        <v>8</v>
+      </c>
+      <c r="I88" t="s">
+        <v>11</v>
+      </c>
+      <c r="J88" s="1">
+        <v>46109</v>
+      </c>
+    </row>
+    <row r="89" spans="2:10">
       <c r="C89" t="s">
         <v>5</v>
       </c>
@@ -1954,10 +2339,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="90" spans="2:4">
-      <c r="B90" t="s">
-        <v>8</v>
-      </c>
+    <row r="90" spans="2:10">
       <c r="C90" t="s">
         <v>6</v>
       </c>
@@ -1965,7 +2347,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="91" spans="2:4">
+    <row r="91" spans="2:10">
       <c r="C91" t="s">
         <v>7</v>
       </c>
@@ -1973,20 +2355,32 @@
         <v>84</v>
       </c>
     </row>
-    <row r="93" spans="2:4">
-      <c r="B93" t="s">
+    <row r="93" spans="2:10">
+      <c r="B93">
+        <v>16</v>
+      </c>
+      <c r="C93" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="94" spans="2:4">
+    <row r="94" spans="2:10">
       <c r="C94" t="s">
         <v>15</v>
       </c>
       <c r="D94" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="95" spans="2:4">
+      <c r="H94" t="s">
+        <v>8</v>
+      </c>
+      <c r="I94" t="s">
+        <v>12</v>
+      </c>
+      <c r="J94" s="1">
+        <v>46109</v>
+      </c>
+    </row>
+    <row r="95" spans="2:10">
       <c r="C95" t="s">
         <v>5</v>
       </c>
@@ -1994,7 +2388,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="96" spans="2:4">
+    <row r="96" spans="2:10">
       <c r="C96" t="s">
         <v>6</v>
       </c>
@@ -2002,10 +2396,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="97" spans="2:4">
-      <c r="B97" t="s">
-        <v>8</v>
-      </c>
+    <row r="97" spans="2:10">
       <c r="C97" t="s">
         <v>7</v>
       </c>
@@ -2013,20 +2404,32 @@
         <v>89</v>
       </c>
     </row>
-    <row r="99" spans="2:4">
-      <c r="B99" t="s">
+    <row r="99" spans="2:10">
+      <c r="B99">
+        <v>17</v>
+      </c>
+      <c r="C99" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="100" spans="2:4">
+    <row r="100" spans="2:10">
       <c r="C100" t="s">
         <v>15</v>
       </c>
       <c r="D100" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="101" spans="2:4">
+      <c r="H100" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I100" t="s">
+        <v>12</v>
+      </c>
+      <c r="J100" s="1">
+        <v>46109</v>
+      </c>
+    </row>
+    <row r="101" spans="2:10">
       <c r="C101" t="s">
         <v>5</v>
       </c>
@@ -2034,10 +2437,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="102" spans="2:4">
-      <c r="B102" t="s">
-        <v>8</v>
-      </c>
+    <row r="102" spans="2:10">
       <c r="C102" t="s">
         <v>6</v>
       </c>
@@ -2045,7 +2445,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="103" spans="2:4">
+    <row r="103" spans="2:10">
       <c r="C103" t="s">
         <v>7</v>
       </c>
@@ -2053,23 +2453,32 @@
         <v>94</v>
       </c>
     </row>
-    <row r="105" spans="2:4">
-      <c r="B105" t="s">
+    <row r="105" spans="2:10">
+      <c r="B105">
+        <v>18</v>
+      </c>
+      <c r="C105" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="106" spans="2:4">
-      <c r="B106" t="s">
-        <v>8</v>
-      </c>
+    <row r="106" spans="2:10">
       <c r="C106" t="s">
         <v>15</v>
       </c>
       <c r="D106" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="107" spans="2:4">
+      <c r="H106" t="s">
+        <v>8</v>
+      </c>
+      <c r="I106" t="s">
+        <v>10</v>
+      </c>
+      <c r="J106" s="1">
+        <v>46109</v>
+      </c>
+    </row>
+    <row r="107" spans="2:10">
       <c r="C107" t="s">
         <v>5</v>
       </c>
@@ -2077,7 +2486,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="108" spans="2:4">
+    <row r="108" spans="2:10">
       <c r="C108" t="s">
         <v>6</v>
       </c>
@@ -2085,7 +2494,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="109" spans="2:4">
+    <row r="109" spans="2:10">
       <c r="C109" t="s">
         <v>7</v>
       </c>
@@ -2093,23 +2502,32 @@
         <v>99</v>
       </c>
     </row>
-    <row r="111" spans="2:4">
-      <c r="B111" t="s">
+    <row r="111" spans="2:10">
+      <c r="B111">
+        <v>19</v>
+      </c>
+      <c r="C111" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="112" spans="2:4">
-      <c r="B112" t="s">
-        <v>8</v>
-      </c>
+    <row r="112" spans="2:10">
       <c r="C112" t="s">
         <v>15</v>
       </c>
       <c r="D112" t="s">
         <v>101</v>
       </c>
-    </row>
-    <row r="113" spans="2:4">
+      <c r="H112" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I112" t="s">
+        <v>12</v>
+      </c>
+      <c r="J112" s="1">
+        <v>46109</v>
+      </c>
+    </row>
+    <row r="113" spans="2:10">
       <c r="C113" t="s">
         <v>5</v>
       </c>
@@ -2117,7 +2535,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="114" spans="2:4">
+    <row r="114" spans="2:10">
       <c r="C114" t="s">
         <v>6</v>
       </c>
@@ -2125,7 +2543,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="115" spans="2:4">
+    <row r="115" spans="2:10">
       <c r="C115" t="s">
         <v>7</v>
       </c>
@@ -2133,23 +2551,32 @@
         <v>104</v>
       </c>
     </row>
-    <row r="117" spans="2:4">
-      <c r="B117" t="s">
+    <row r="117" spans="2:10">
+      <c r="B117">
+        <v>20</v>
+      </c>
+      <c r="C117" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="118" spans="2:4">
+    <row r="118" spans="2:10">
       <c r="C118" t="s">
         <v>10</v>
       </c>
       <c r="D118" t="s">
         <v>106</v>
       </c>
-    </row>
-    <row r="119" spans="2:4">
-      <c r="B119" t="s">
-        <v>8</v>
-      </c>
+      <c r="H118" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I118" t="s">
+        <v>12</v>
+      </c>
+      <c r="J118" s="1">
+        <v>46109</v>
+      </c>
+    </row>
+    <row r="119" spans="2:10">
       <c r="C119" t="s">
         <v>5</v>
       </c>
@@ -2157,7 +2584,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="120" spans="2:4">
+    <row r="120" spans="2:10">
       <c r="C120" t="s">
         <v>6</v>
       </c>
@@ -2165,7 +2592,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="121" spans="2:4">
+    <row r="121" spans="2:10">
       <c r="C121" t="s">
         <v>7</v>
       </c>
@@ -2173,25 +2600,37 @@
         <v>109</v>
       </c>
     </row>
-    <row r="123" spans="2:4">
-      <c r="B123" t="s">
+    <row r="123" spans="2:10">
+      <c r="B123">
+        <v>21</v>
+      </c>
+      <c r="C123" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="124" spans="2:4">
-      <c r="B124" t="s">
+    <row r="124" spans="2:10">
+      <c r="C124" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="125" spans="2:4">
+    <row r="125" spans="2:10">
       <c r="C125" t="s">
         <v>10</v>
       </c>
       <c r="D125" t="s">
         <v>112</v>
       </c>
-    </row>
-    <row r="126" spans="2:4">
+      <c r="H125" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I125" t="s">
+        <v>9</v>
+      </c>
+      <c r="J125" s="1">
+        <v>46109</v>
+      </c>
+    </row>
+    <row r="126" spans="2:10">
       <c r="C126" t="s">
         <v>5</v>
       </c>
@@ -2199,10 +2638,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="127" spans="2:4">
-      <c r="B127" t="s">
-        <v>8</v>
-      </c>
+    <row r="127" spans="2:10">
       <c r="C127" t="s">
         <v>6</v>
       </c>
@@ -2210,7 +2646,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="128" spans="2:4">
+    <row r="128" spans="2:10">
       <c r="C128" t="s">
         <v>7</v>
       </c>
@@ -2218,23 +2654,32 @@
         <v>115</v>
       </c>
     </row>
-    <row r="130" spans="2:4">
-      <c r="B130" t="s">
+    <row r="130" spans="2:10">
+      <c r="B130">
+        <v>22</v>
+      </c>
+      <c r="C130" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="131" spans="2:4">
-      <c r="B131" t="s">
-        <v>8</v>
-      </c>
+    <row r="131" spans="2:10">
       <c r="C131" t="s">
         <v>10</v>
       </c>
       <c r="D131" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="132" spans="2:4">
+      <c r="H131" t="s">
+        <v>8</v>
+      </c>
+      <c r="I131" t="s">
+        <v>10</v>
+      </c>
+      <c r="J131" s="1">
+        <v>46109</v>
+      </c>
+    </row>
+    <row r="132" spans="2:10">
       <c r="C132" t="s">
         <v>5</v>
       </c>
@@ -2242,7 +2687,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="133" spans="2:4">
+    <row r="133" spans="2:10">
       <c r="C133" t="s">
         <v>6</v>
       </c>
@@ -2250,7 +2695,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="134" spans="2:4">
+    <row r="134" spans="2:10">
       <c r="C134" t="s">
         <v>7</v>
       </c>
@@ -2258,17 +2703,29 @@
         <v>120</v>
       </c>
     </row>
-    <row r="136" spans="2:4">
-      <c r="B136" t="s">
+    <row r="136" spans="2:10">
+      <c r="B136">
+        <v>23</v>
+      </c>
+      <c r="C136" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="137" spans="2:4">
-      <c r="B137" t="s">
+    <row r="137" spans="2:10">
+      <c r="C137" t="s">
         <v>122</v>
       </c>
-    </row>
-    <row r="138" spans="2:4">
+      <c r="H137" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I137" t="s">
+        <v>12</v>
+      </c>
+      <c r="J137" s="1">
+        <v>46109</v>
+      </c>
+    </row>
+    <row r="138" spans="2:10">
       <c r="C138" t="s">
         <v>10</v>
       </c>
@@ -2276,7 +2733,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="139" spans="2:4">
+    <row r="139" spans="2:10">
       <c r="C139" t="s">
         <v>5</v>
       </c>
@@ -2284,10 +2741,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="140" spans="2:4">
-      <c r="B140" t="s">
-        <v>8</v>
-      </c>
+    <row r="140" spans="2:10">
       <c r="C140" t="s">
         <v>6</v>
       </c>
@@ -2295,7 +2749,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="141" spans="2:4">
+    <row r="141" spans="2:10">
       <c r="C141" t="s">
         <v>7</v>
       </c>
@@ -2303,20 +2757,32 @@
         <v>126</v>
       </c>
     </row>
-    <row r="143" spans="2:4">
-      <c r="B143" t="s">
+    <row r="143" spans="2:10">
+      <c r="B143">
+        <v>24</v>
+      </c>
+      <c r="C143" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="144" spans="2:4">
+    <row r="144" spans="2:10">
       <c r="C144" t="s">
         <v>10</v>
       </c>
       <c r="D144" t="s">
         <v>128</v>
       </c>
-    </row>
-    <row r="145" spans="2:4">
+      <c r="H144" t="s">
+        <v>8</v>
+      </c>
+      <c r="I144" t="s">
+        <v>11</v>
+      </c>
+      <c r="J144" s="1">
+        <v>46109</v>
+      </c>
+    </row>
+    <row r="145" spans="2:10">
       <c r="C145" t="s">
         <v>5</v>
       </c>
@@ -2324,10 +2790,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="146" spans="2:4">
-      <c r="B146" t="s">
-        <v>8</v>
-      </c>
+    <row r="146" spans="2:10">
       <c r="C146" t="s">
         <v>6</v>
       </c>
@@ -2335,7 +2798,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="147" spans="2:4">
+    <row r="147" spans="2:10">
       <c r="C147" t="s">
         <v>7</v>
       </c>
@@ -2343,20 +2806,32 @@
         <v>131</v>
       </c>
     </row>
-    <row r="149" spans="2:4">
-      <c r="B149" t="s">
+    <row r="149" spans="2:10">
+      <c r="B149">
+        <v>25</v>
+      </c>
+      <c r="C149" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="150" spans="2:4">
+    <row r="150" spans="2:10">
       <c r="C150" t="s">
         <v>10</v>
       </c>
       <c r="D150" t="s">
         <v>133</v>
       </c>
-    </row>
-    <row r="151" spans="2:4">
+      <c r="H150" t="s">
+        <v>8</v>
+      </c>
+      <c r="I150" t="s">
+        <v>11</v>
+      </c>
+      <c r="J150" s="1">
+        <v>46109</v>
+      </c>
+    </row>
+    <row r="151" spans="2:10">
       <c r="C151" t="s">
         <v>5</v>
       </c>
@@ -2364,10 +2839,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="152" spans="2:4">
-      <c r="B152" t="s">
-        <v>8</v>
-      </c>
+    <row r="152" spans="2:10">
       <c r="C152" t="s">
         <v>6</v>
       </c>
@@ -2375,7 +2847,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="153" spans="2:4">
+    <row r="153" spans="2:10">
       <c r="C153" t="s">
         <v>7</v>
       </c>
@@ -2383,20 +2855,32 @@
         <v>136</v>
       </c>
     </row>
-    <row r="155" spans="2:4">
-      <c r="B155" t="s">
+    <row r="155" spans="2:10">
+      <c r="B155">
+        <v>26</v>
+      </c>
+      <c r="C155" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="156" spans="2:4">
+    <row r="156" spans="2:10">
       <c r="C156" t="s">
         <v>10</v>
       </c>
       <c r="D156" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="157" spans="2:4">
+      <c r="H156" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I156" t="s">
+        <v>10</v>
+      </c>
+      <c r="J156" s="1">
+        <v>46109</v>
+      </c>
+    </row>
+    <row r="157" spans="2:10">
       <c r="C157" t="s">
         <v>5</v>
       </c>
@@ -2404,10 +2888,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="158" spans="2:4">
-      <c r="B158" t="s">
-        <v>8</v>
-      </c>
+    <row r="158" spans="2:10">
       <c r="C158" t="s">
         <v>6</v>
       </c>
@@ -2415,7 +2896,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="159" spans="2:4">
+    <row r="159" spans="2:10">
       <c r="C159" t="s">
         <v>7</v>
       </c>
@@ -2423,23 +2904,32 @@
         <v>141</v>
       </c>
     </row>
-    <row r="161" spans="2:4">
-      <c r="B161" t="s">
+    <row r="161" spans="2:10">
+      <c r="B161">
+        <v>27</v>
+      </c>
+      <c r="C161" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="162" spans="2:4">
+    <row r="162" spans="2:10">
       <c r="C162" t="s">
         <v>147</v>
       </c>
       <c r="D162" t="s">
         <v>143</v>
       </c>
-    </row>
-    <row r="163" spans="2:4">
-      <c r="B163" t="s">
-        <v>8</v>
-      </c>
+      <c r="H162" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I162" t="s">
+        <v>12</v>
+      </c>
+      <c r="J162" s="1">
+        <v>46109</v>
+      </c>
+    </row>
+    <row r="163" spans="2:10">
       <c r="C163" t="s">
         <v>5</v>
       </c>
@@ -2447,7 +2937,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="164" spans="2:4">
+    <row r="164" spans="2:10">
       <c r="C164" t="s">
         <v>6</v>
       </c>
@@ -2455,7 +2945,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="165" spans="2:4">
+    <row r="165" spans="2:10">
       <c r="C165" t="s">
         <v>7</v>
       </c>
@@ -2463,20 +2953,32 @@
         <v>146</v>
       </c>
     </row>
-    <row r="167" spans="2:4">
-      <c r="B167" t="s">
+    <row r="167" spans="2:10">
+      <c r="B167">
+        <v>28</v>
+      </c>
+      <c r="C167" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="168" spans="2:4">
+    <row r="168" spans="2:10">
       <c r="C168" t="s">
         <v>147</v>
       </c>
       <c r="D168" t="s">
         <v>149</v>
       </c>
-    </row>
-    <row r="169" spans="2:4">
+      <c r="H168" t="s">
+        <v>8</v>
+      </c>
+      <c r="I168" t="s">
+        <v>11</v>
+      </c>
+      <c r="J168" s="1">
+        <v>46109</v>
+      </c>
+    </row>
+    <row r="169" spans="2:10">
       <c r="C169" t="s">
         <v>5</v>
       </c>
@@ -2484,10 +2986,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="170" spans="2:4">
-      <c r="B170" t="s">
-        <v>8</v>
-      </c>
+    <row r="170" spans="2:10">
       <c r="C170" t="s">
         <v>6</v>
       </c>
@@ -2495,7 +2994,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="171" spans="2:4">
+    <row r="171" spans="2:10">
       <c r="C171" t="s">
         <v>7</v>
       </c>
@@ -2503,23 +3002,32 @@
         <v>152</v>
       </c>
     </row>
-    <row r="173" spans="2:4">
-      <c r="B173" t="s">
+    <row r="173" spans="2:10">
+      <c r="B173">
+        <v>29</v>
+      </c>
+      <c r="C173" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="174" spans="2:4">
+    <row r="174" spans="2:10">
       <c r="C174" t="s">
         <v>147</v>
       </c>
       <c r="D174" t="s">
         <v>154</v>
       </c>
-    </row>
-    <row r="175" spans="2:4">
-      <c r="B175" t="s">
-        <v>8</v>
-      </c>
+      <c r="H174" t="s">
+        <v>8</v>
+      </c>
+      <c r="I174" t="s">
+        <v>9</v>
+      </c>
+      <c r="J174" s="1">
+        <v>46109</v>
+      </c>
+    </row>
+    <row r="175" spans="2:10">
       <c r="C175" t="s">
         <v>5</v>
       </c>
@@ -2527,7 +3035,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="176" spans="2:4">
+    <row r="176" spans="2:10">
       <c r="C176" t="s">
         <v>6</v>
       </c>
@@ -2535,7 +3043,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="177" spans="2:4">
+    <row r="177" spans="2:10">
       <c r="C177" t="s">
         <v>7</v>
       </c>
@@ -2543,20 +3051,32 @@
         <v>157</v>
       </c>
     </row>
-    <row r="179" spans="2:4">
-      <c r="B179" t="s">
+    <row r="179" spans="2:10">
+      <c r="B179">
+        <v>30</v>
+      </c>
+      <c r="C179" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="180" spans="2:4">
+    <row r="180" spans="2:10">
       <c r="C180" t="s">
         <v>147</v>
       </c>
       <c r="D180" t="s">
         <v>159</v>
       </c>
-    </row>
-    <row r="181" spans="2:4">
+      <c r="H180" t="s">
+        <v>8</v>
+      </c>
+      <c r="I180" t="s">
+        <v>11</v>
+      </c>
+      <c r="J180" s="1">
+        <v>46109</v>
+      </c>
+    </row>
+    <row r="181" spans="2:10">
       <c r="C181" t="s">
         <v>5</v>
       </c>
@@ -2564,10 +3084,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="182" spans="2:4">
-      <c r="B182" t="s">
-        <v>8</v>
-      </c>
+    <row r="182" spans="2:10">
       <c r="C182" t="s">
         <v>6</v>
       </c>
@@ -2575,7 +3092,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="183" spans="2:4">
+    <row r="183" spans="2:10">
       <c r="C183" t="s">
         <v>7</v>
       </c>
@@ -2583,23 +3100,32 @@
         <v>162</v>
       </c>
     </row>
-    <row r="185" spans="2:4">
-      <c r="B185" t="s">
+    <row r="185" spans="2:10">
+      <c r="B185">
+        <v>31</v>
+      </c>
+      <c r="C185" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="186" spans="2:4">
-      <c r="B186" t="s">
-        <v>8</v>
-      </c>
+    <row r="186" spans="2:10">
       <c r="C186" t="s">
         <v>147</v>
       </c>
       <c r="D186" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="187" spans="2:4">
+      <c r="H186" t="s">
+        <v>8</v>
+      </c>
+      <c r="I186" t="s">
+        <v>10</v>
+      </c>
+      <c r="J186" s="1">
+        <v>46109</v>
+      </c>
+    </row>
+    <row r="187" spans="2:10">
       <c r="C187" t="s">
         <v>5</v>
       </c>
@@ -2607,7 +3133,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="188" spans="2:4">
+    <row r="188" spans="2:10">
       <c r="C188" t="s">
         <v>6</v>
       </c>
@@ -2615,7 +3141,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="189" spans="2:4">
+    <row r="189" spans="2:10">
       <c r="C189" t="s">
         <v>7</v>
       </c>
@@ -2623,20 +3149,32 @@
         <v>167</v>
       </c>
     </row>
-    <row r="191" spans="2:4">
-      <c r="B191" t="s">
+    <row r="191" spans="2:10">
+      <c r="B191">
+        <v>32</v>
+      </c>
+      <c r="C191" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="192" spans="2:4">
+    <row r="192" spans="2:10">
       <c r="C192" t="s">
         <v>147</v>
       </c>
       <c r="D192" t="s">
         <v>169</v>
       </c>
-    </row>
-    <row r="193" spans="2:4">
+      <c r="H192" t="s">
+        <v>8</v>
+      </c>
+      <c r="I192" t="s">
+        <v>11</v>
+      </c>
+      <c r="J192" s="1">
+        <v>46109</v>
+      </c>
+    </row>
+    <row r="193" spans="2:10">
       <c r="C193" t="s">
         <v>5</v>
       </c>
@@ -2644,10 +3182,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="194" spans="2:4">
-      <c r="B194" t="s">
-        <v>8</v>
-      </c>
+    <row r="194" spans="2:10">
       <c r="C194" t="s">
         <v>6</v>
       </c>
@@ -2655,7 +3190,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="195" spans="2:4">
+    <row r="195" spans="2:10">
       <c r="C195" t="s">
         <v>7</v>
       </c>
@@ -2663,20 +3198,32 @@
         <v>172</v>
       </c>
     </row>
-    <row r="197" spans="2:4">
-      <c r="B197" t="s">
+    <row r="197" spans="2:10">
+      <c r="B197">
+        <v>33</v>
+      </c>
+      <c r="C197" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="198" spans="2:4">
+    <row r="198" spans="2:10">
       <c r="C198" t="s">
         <v>147</v>
       </c>
       <c r="D198" t="s">
         <v>174</v>
       </c>
-    </row>
-    <row r="199" spans="2:4">
+      <c r="H198" t="s">
+        <v>8</v>
+      </c>
+      <c r="I198" t="s">
+        <v>11</v>
+      </c>
+      <c r="J198" s="1">
+        <v>46109</v>
+      </c>
+    </row>
+    <row r="199" spans="2:10">
       <c r="C199" t="s">
         <v>5</v>
       </c>
@@ -2684,10 +3231,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="200" spans="2:4">
-      <c r="B200" t="s">
-        <v>8</v>
-      </c>
+    <row r="200" spans="2:10">
       <c r="C200" t="s">
         <v>6</v>
       </c>
@@ -2695,7 +3239,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="201" spans="2:4">
+    <row r="201" spans="2:10">
       <c r="C201" t="s">
         <v>7</v>
       </c>
@@ -2703,20 +3247,32 @@
         <v>177</v>
       </c>
     </row>
-    <row r="203" spans="2:4">
-      <c r="B203" t="s">
+    <row r="203" spans="2:10">
+      <c r="B203">
+        <v>34</v>
+      </c>
+      <c r="C203" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="204" spans="2:4">
+    <row r="204" spans="2:10">
       <c r="C204" t="s">
         <v>147</v>
       </c>
       <c r="D204" t="s">
         <v>179</v>
       </c>
-    </row>
-    <row r="205" spans="2:4">
+      <c r="H204" t="s">
+        <v>8</v>
+      </c>
+      <c r="I204" t="s">
+        <v>12</v>
+      </c>
+      <c r="J204" s="1">
+        <v>46109</v>
+      </c>
+    </row>
+    <row r="205" spans="2:10">
       <c r="C205" t="s">
         <v>5</v>
       </c>
@@ -2724,7 +3280,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="206" spans="2:4">
+    <row r="206" spans="2:10">
       <c r="C206" t="s">
         <v>6</v>
       </c>
@@ -2732,10 +3288,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="207" spans="2:4">
-      <c r="B207" t="s">
-        <v>8</v>
-      </c>
+    <row r="207" spans="2:10">
       <c r="C207" t="s">
         <v>7</v>
       </c>
@@ -2743,23 +3296,32 @@
         <v>182</v>
       </c>
     </row>
-    <row r="209" spans="2:4">
-      <c r="B209" t="s">
+    <row r="209" spans="2:10">
+      <c r="B209">
+        <v>35</v>
+      </c>
+      <c r="C209" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="210" spans="2:4">
+    <row r="210" spans="2:10">
       <c r="C210" t="s">
         <v>147</v>
       </c>
       <c r="D210" t="s">
         <v>184</v>
       </c>
-    </row>
-    <row r="211" spans="2:4">
-      <c r="B211" t="s">
-        <v>8</v>
-      </c>
+      <c r="H210" t="s">
+        <v>8</v>
+      </c>
+      <c r="I210" t="s">
+        <v>9</v>
+      </c>
+      <c r="J210" s="1">
+        <v>46109</v>
+      </c>
+    </row>
+    <row r="211" spans="2:10">
       <c r="C211" t="s">
         <v>5</v>
       </c>
@@ -2767,7 +3329,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="212" spans="2:4">
+    <row r="212" spans="2:10">
       <c r="C212" t="s">
         <v>6</v>
       </c>
@@ -2775,7 +3337,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="213" spans="2:4">
+    <row r="213" spans="2:10">
       <c r="C213" t="s">
         <v>7</v>
       </c>
@@ -2783,20 +3345,32 @@
         <v>187</v>
       </c>
     </row>
-    <row r="215" spans="2:4">
-      <c r="B215" t="s">
+    <row r="215" spans="2:10">
+      <c r="B215">
+        <v>36</v>
+      </c>
+      <c r="C215" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="216" spans="2:4">
+    <row r="216" spans="2:10">
       <c r="C216" t="s">
         <v>147</v>
       </c>
       <c r="D216" t="s">
         <v>188</v>
       </c>
-    </row>
-    <row r="217" spans="2:4">
+      <c r="H216" t="s">
+        <v>8</v>
+      </c>
+      <c r="I216" t="s">
+        <v>11</v>
+      </c>
+      <c r="J216" s="1">
+        <v>46109</v>
+      </c>
+    </row>
+    <row r="217" spans="2:10">
       <c r="C217" t="s">
         <v>5</v>
       </c>
@@ -2804,10 +3378,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="218" spans="2:4">
-      <c r="B218" t="s">
-        <v>8</v>
-      </c>
+    <row r="218" spans="2:10">
       <c r="C218" t="s">
         <v>6</v>
       </c>
@@ -2815,7 +3386,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="219" spans="2:4">
+    <row r="219" spans="2:10">
       <c r="C219" t="s">
         <v>7</v>
       </c>
@@ -2823,23 +3394,32 @@
         <v>191</v>
       </c>
     </row>
-    <row r="221" spans="2:4">
-      <c r="B221" t="s">
+    <row r="221" spans="2:10">
+      <c r="B221">
+        <v>37</v>
+      </c>
+      <c r="C221" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="222" spans="2:4">
-      <c r="B222" t="s">
-        <v>8</v>
-      </c>
+    <row r="222" spans="2:10">
       <c r="C222" t="s">
         <v>147</v>
       </c>
       <c r="D222" t="s">
         <v>194</v>
       </c>
-    </row>
-    <row r="223" spans="2:4">
+      <c r="H222" t="s">
+        <v>8</v>
+      </c>
+      <c r="I222" t="s">
+        <v>10</v>
+      </c>
+      <c r="J222" s="1">
+        <v>46109</v>
+      </c>
+    </row>
+    <row r="223" spans="2:10">
       <c r="C223" t="s">
         <v>5</v>
       </c>
@@ -2847,7 +3427,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="224" spans="2:4">
+    <row r="224" spans="2:10">
       <c r="C224" t="s">
         <v>6</v>
       </c>
@@ -2855,7 +3435,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="225" spans="2:4">
+    <row r="225" spans="2:10">
       <c r="C225" t="s">
         <v>7</v>
       </c>
@@ -2863,23 +3443,32 @@
         <v>197</v>
       </c>
     </row>
-    <row r="227" spans="2:4">
-      <c r="B227" t="s">
+    <row r="227" spans="2:10">
+      <c r="B227">
+        <v>38</v>
+      </c>
+      <c r="C227" t="s">
         <v>198</v>
       </c>
     </row>
-    <row r="228" spans="2:4">
+    <row r="228" spans="2:10">
       <c r="C228" t="s">
         <v>147</v>
       </c>
       <c r="D228" t="s">
         <v>199</v>
       </c>
-    </row>
-    <row r="229" spans="2:4">
-      <c r="B229" t="s">
-        <v>8</v>
-      </c>
+      <c r="H228" t="s">
+        <v>8</v>
+      </c>
+      <c r="I228" t="s">
+        <v>9</v>
+      </c>
+      <c r="J228" s="1">
+        <v>46109</v>
+      </c>
+    </row>
+    <row r="229" spans="2:10">
       <c r="C229" t="s">
         <v>5</v>
       </c>
@@ -2887,7 +3476,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="230" spans="2:4">
+    <row r="230" spans="2:10">
       <c r="C230" t="s">
         <v>6</v>
       </c>
@@ -2895,7 +3484,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="231" spans="2:4">
+    <row r="231" spans="2:10">
       <c r="C231" t="s">
         <v>7</v>
       </c>
@@ -2903,20 +3492,32 @@
         <v>202</v>
       </c>
     </row>
-    <row r="233" spans="2:4">
-      <c r="B233" t="s">
+    <row r="233" spans="2:10">
+      <c r="B233">
+        <v>39</v>
+      </c>
+      <c r="C233" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="234" spans="2:4">
+    <row r="234" spans="2:10">
       <c r="C234" t="s">
         <v>147</v>
       </c>
       <c r="D234" t="s">
         <v>204</v>
       </c>
-    </row>
-    <row r="235" spans="2:4">
+      <c r="H234" t="s">
+        <v>8</v>
+      </c>
+      <c r="I234" t="s">
+        <v>12</v>
+      </c>
+      <c r="J234" s="1">
+        <v>46109</v>
+      </c>
+    </row>
+    <row r="235" spans="2:10">
       <c r="C235" t="s">
         <v>5</v>
       </c>
@@ -2924,7 +3525,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="236" spans="2:4">
+    <row r="236" spans="2:10">
       <c r="C236" t="s">
         <v>6</v>
       </c>
@@ -2932,10 +3533,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="237" spans="2:4">
-      <c r="B237" t="s">
-        <v>8</v>
-      </c>
+    <row r="237" spans="2:10">
       <c r="C237" t="s">
         <v>7</v>
       </c>
@@ -2943,23 +3541,32 @@
         <v>207</v>
       </c>
     </row>
-    <row r="239" spans="2:4">
-      <c r="B239" t="s">
+    <row r="239" spans="2:10">
+      <c r="B239">
+        <v>40</v>
+      </c>
+      <c r="C239" t="s">
         <v>208</v>
       </c>
     </row>
-    <row r="240" spans="2:4">
+    <row r="240" spans="2:10">
       <c r="C240" t="s">
         <v>147</v>
       </c>
       <c r="D240" t="s">
         <v>209</v>
       </c>
-    </row>
-    <row r="241" spans="2:4">
-      <c r="B241" t="s">
-        <v>8</v>
-      </c>
+      <c r="H240" t="s">
+        <v>8</v>
+      </c>
+      <c r="I240" t="s">
+        <v>9</v>
+      </c>
+      <c r="J240" s="1">
+        <v>46109</v>
+      </c>
+    </row>
+    <row r="241" spans="3:8">
       <c r="C241" t="s">
         <v>5</v>
       </c>
@@ -2967,7 +3574,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="242" spans="2:4">
+    <row r="242" spans="3:8">
       <c r="C242" t="s">
         <v>6</v>
       </c>
@@ -2975,12 +3582,18 @@
         <v>155</v>
       </c>
     </row>
-    <row r="243" spans="2:4">
+    <row r="243" spans="3:8">
       <c r="C243" t="s">
         <v>7</v>
       </c>
       <c r="D243" t="s">
         <v>210</v>
+      </c>
+    </row>
+    <row r="244" spans="3:8">
+      <c r="H244" s="3">
+        <f>COUNTIF(H2:H243,"○")/COUNTA(H2:H243)</f>
+        <v>0.77500000000000002</v>
       </c>
     </row>
   </sheetData>
@@ -2990,24 +3603,365 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F23626FA-243D-40DB-B02C-BB081C523183}">
+  <dimension ref="B2:C41"/>
+  <sheetFormatPr defaultRowHeight="18"/>
+  <sheetData>
+    <row r="2" spans="2:3">
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="2:3">
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="2:3">
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="2:3">
+      <c r="B5">
+        <v>4</v>
+      </c>
+      <c r="C5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="2:3">
+      <c r="B6">
+        <v>5</v>
+      </c>
+      <c r="C6" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="2:3">
+      <c r="B7">
+        <v>6</v>
+      </c>
+      <c r="C7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="2:3">
+      <c r="B8">
+        <v>7</v>
+      </c>
+      <c r="C8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="2:3">
+      <c r="B9">
+        <v>8</v>
+      </c>
+      <c r="C9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" spans="2:3">
+      <c r="B10">
+        <v>9</v>
+      </c>
+      <c r="C10" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="2:3">
+      <c r="B11">
+        <v>10</v>
+      </c>
+      <c r="C11" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12" spans="2:3">
+      <c r="B12">
+        <v>11</v>
+      </c>
+      <c r="C12" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13" spans="2:3">
+      <c r="B13">
+        <v>12</v>
+      </c>
+      <c r="C13" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14" spans="2:3">
+      <c r="B14">
+        <v>13</v>
+      </c>
+      <c r="C14" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="15" spans="2:3">
+      <c r="B15">
+        <v>14</v>
+      </c>
+      <c r="C15" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16" spans="2:3">
+      <c r="B16">
+        <v>15</v>
+      </c>
+      <c r="C16" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="17" spans="2:3">
+      <c r="B17">
+        <v>16</v>
+      </c>
+      <c r="C17" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="18" spans="2:3">
+      <c r="B18">
+        <v>17</v>
+      </c>
+      <c r="C18" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="19" spans="2:3">
+      <c r="B19">
+        <v>18</v>
+      </c>
+      <c r="C19" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="20" spans="2:3">
+      <c r="B20">
+        <v>19</v>
+      </c>
+      <c r="C20" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="21" spans="2:3">
+      <c r="B21">
+        <v>20</v>
+      </c>
+      <c r="C21" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="2:3">
+      <c r="B22">
+        <v>21</v>
+      </c>
+      <c r="C22" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="23" spans="2:3">
+      <c r="B23">
+        <v>22</v>
+      </c>
+      <c r="C23" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="24" spans="2:3">
+      <c r="B24">
+        <v>23</v>
+      </c>
+      <c r="C24" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="25" spans="2:3">
+      <c r="B25">
+        <v>24</v>
+      </c>
+      <c r="C25" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="26" spans="2:3">
+      <c r="B26">
+        <v>25</v>
+      </c>
+      <c r="C26" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="27" spans="2:3">
+      <c r="B27">
+        <v>26</v>
+      </c>
+      <c r="C27" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="28" spans="2:3">
+      <c r="B28">
+        <v>27</v>
+      </c>
+      <c r="C28" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="29" spans="2:3">
+      <c r="B29">
+        <v>28</v>
+      </c>
+      <c r="C29" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="30" spans="2:3">
+      <c r="B30">
+        <v>29</v>
+      </c>
+      <c r="C30" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="31" spans="2:3">
+      <c r="B31">
+        <v>30</v>
+      </c>
+      <c r="C31" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="32" spans="2:3">
+      <c r="B32">
+        <v>31</v>
+      </c>
+      <c r="C32" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="33" spans="2:3">
+      <c r="B33">
+        <v>32</v>
+      </c>
+      <c r="C33" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="34" spans="2:3">
+      <c r="B34">
+        <v>33</v>
+      </c>
+      <c r="C34" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="35" spans="2:3">
+      <c r="B35">
+        <v>34</v>
+      </c>
+      <c r="C35" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="36" spans="2:3">
+      <c r="B36">
+        <v>35</v>
+      </c>
+      <c r="C36" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="37" spans="2:3">
+      <c r="B37">
+        <v>36</v>
+      </c>
+      <c r="C37" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="38" spans="2:3">
+      <c r="B38">
+        <v>37</v>
+      </c>
+      <c r="C38" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="39" spans="2:3">
+      <c r="B39">
+        <v>38</v>
+      </c>
+      <c r="C39" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="40" spans="2:3">
+      <c r="B40">
+        <v>39</v>
+      </c>
+      <c r="C40" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="41" spans="2:3">
+      <c r="B41">
+        <v>40</v>
+      </c>
+      <c r="C41" t="s">
+        <v>5</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{61EEA8E1-AFF1-4B2D-8BDC-8FC5E7EC9EE0}">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="B2:D67"/>
+  <dimension ref="B2:L68"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
-    <col min="2" max="3" width="3.33203125" customWidth="1"/>
-    <col min="4" max="4" width="85.4140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="3.296875" customWidth="1"/>
+    <col min="4" max="4" width="85.3984375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.19921875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:4">
-      <c r="B2" t="s">
+    <row r="2" spans="2:12">
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2" t="s">
         <v>211</v>
       </c>
-    </row>
-    <row r="3" spans="2:4">
-      <c r="B3" t="s">
-        <v>8</v>
-      </c>
+      <c r="J2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K2" t="s">
+        <v>10</v>
+      </c>
+      <c r="L2" s="1">
+        <v>46109</v>
+      </c>
+    </row>
+    <row r="3" spans="2:12">
       <c r="C3" t="s">
         <v>10</v>
       </c>
@@ -3015,7 +3969,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="4" spans="2:4">
+    <row r="4" spans="2:12">
       <c r="C4" t="s">
         <v>5</v>
       </c>
@@ -3023,7 +3977,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="5" spans="2:4">
+    <row r="5" spans="2:12">
       <c r="C5" t="s">
         <v>6</v>
       </c>
@@ -3031,7 +3985,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="6" spans="2:4">
+    <row r="6" spans="2:12">
       <c r="C6" t="s">
         <v>7</v>
       </c>
@@ -3039,15 +3993,24 @@
         <v>215</v>
       </c>
     </row>
-    <row r="8" spans="2:4">
-      <c r="B8" t="s">
+    <row r="8" spans="2:12">
+      <c r="B8">
+        <v>2</v>
+      </c>
+      <c r="C8" t="s">
         <v>216</v>
       </c>
-    </row>
-    <row r="9" spans="2:4">
-      <c r="B9" t="s">
-        <v>8</v>
-      </c>
+      <c r="J8" t="s">
+        <v>8</v>
+      </c>
+      <c r="K8" t="s">
+        <v>10</v>
+      </c>
+      <c r="L8" s="1">
+        <v>46109</v>
+      </c>
+    </row>
+    <row r="9" spans="2:12">
       <c r="C9" t="s">
         <v>10</v>
       </c>
@@ -3055,7 +4018,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="10" spans="2:4">
+    <row r="10" spans="2:12">
       <c r="C10" t="s">
         <v>5</v>
       </c>
@@ -3063,7 +4026,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="11" spans="2:4">
+    <row r="11" spans="2:12">
       <c r="C11" t="s">
         <v>6</v>
       </c>
@@ -3071,7 +4034,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="12" spans="2:4">
+    <row r="12" spans="2:12">
       <c r="C12" t="s">
         <v>7</v>
       </c>
@@ -3079,15 +4042,24 @@
         <v>218</v>
       </c>
     </row>
-    <row r="14" spans="2:4">
-      <c r="B14" t="s">
+    <row r="14" spans="2:12">
+      <c r="B14">
+        <v>3</v>
+      </c>
+      <c r="C14" t="s">
         <v>221</v>
       </c>
-    </row>
-    <row r="15" spans="2:4">
-      <c r="B15" t="s">
-        <v>8</v>
-      </c>
+      <c r="J14" t="s">
+        <v>8</v>
+      </c>
+      <c r="K14" t="s">
+        <v>10</v>
+      </c>
+      <c r="L14" s="1">
+        <v>46109</v>
+      </c>
+    </row>
+    <row r="15" spans="2:12">
       <c r="C15" t="s">
         <v>10</v>
       </c>
@@ -3095,7 +4067,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="16" spans="2:4">
+    <row r="16" spans="2:12">
       <c r="C16" t="s">
         <v>5</v>
       </c>
@@ -3103,7 +4075,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="17" spans="2:4">
+    <row r="17" spans="2:12">
       <c r="C17" t="s">
         <v>6</v>
       </c>
@@ -3111,7 +4083,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="18" spans="2:4">
+    <row r="18" spans="2:12">
       <c r="C18" t="s">
         <v>7</v>
       </c>
@@ -3119,40 +4091,49 @@
         <v>225</v>
       </c>
     </row>
-    <row r="20" spans="2:4">
-      <c r="B20" t="s">
+    <row r="20" spans="2:12">
+      <c r="B20">
+        <v>4</v>
+      </c>
+      <c r="C20" t="s">
         <v>230</v>
       </c>
-    </row>
-    <row r="21" spans="2:4">
-      <c r="B21" t="s">
+      <c r="J20" t="s">
+        <v>8</v>
+      </c>
+      <c r="K20" t="s">
+        <v>10</v>
+      </c>
+      <c r="L20" s="1">
+        <v>46109</v>
+      </c>
+    </row>
+    <row r="21" spans="2:12">
+      <c r="C21" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="22" spans="2:4">
-      <c r="B22" t="s">
+    <row r="22" spans="2:12">
+      <c r="C22" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="23" spans="2:4">
-      <c r="B23" t="s">
+    <row r="23" spans="2:12">
+      <c r="C23" t="s">
         <v>228</v>
       </c>
     </row>
-    <row r="24" spans="2:4">
-      <c r="B24" t="s">
+    <row r="24" spans="2:12">
+      <c r="C24" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="41" spans="2:4">
-      <c r="B41" t="s">
+    <row r="41" spans="2:12">
+      <c r="C41" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="42" spans="2:4">
-      <c r="B42" t="s">
-        <v>8</v>
-      </c>
+    <row r="42" spans="2:12">
       <c r="C42" t="s">
         <v>147</v>
       </c>
@@ -3160,7 +4141,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="43" spans="2:4">
+    <row r="43" spans="2:12">
       <c r="C43" t="s">
         <v>5</v>
       </c>
@@ -3168,7 +4149,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="44" spans="2:4">
+    <row r="44" spans="2:12">
       <c r="C44" t="s">
         <v>6</v>
       </c>
@@ -3176,7 +4157,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="45" spans="2:4">
+    <row r="45" spans="2:12">
       <c r="C45" t="s">
         <v>7</v>
       </c>
@@ -3184,25 +4165,34 @@
         <v>235</v>
       </c>
     </row>
-    <row r="47" spans="2:4">
-      <c r="B47" t="s">
+    <row r="47" spans="2:12">
+      <c r="B47">
+        <v>5</v>
+      </c>
+      <c r="C47" t="s">
         <v>236</v>
       </c>
-    </row>
-    <row r="48" spans="2:4">
-      <c r="B48" t="s">
+      <c r="J47" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="K47" t="s">
+        <v>12</v>
+      </c>
+      <c r="L47" s="1">
+        <v>46109</v>
+      </c>
+    </row>
+    <row r="48" spans="2:12">
+      <c r="C48" t="s">
         <v>237</v>
       </c>
     </row>
-    <row r="49" spans="2:4">
-      <c r="B49" t="s">
+    <row r="49" spans="2:12">
+      <c r="C49" t="s">
         <v>238</v>
       </c>
     </row>
-    <row r="50" spans="2:4">
-      <c r="B50" t="s">
-        <v>8</v>
-      </c>
+    <row r="50" spans="2:12">
       <c r="C50" t="s">
         <v>147</v>
       </c>
@@ -3210,7 +4200,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="51" spans="2:4">
+    <row r="51" spans="2:12">
       <c r="C51" t="s">
         <v>5</v>
       </c>
@@ -3218,7 +4208,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="52" spans="2:4">
+    <row r="52" spans="2:12">
       <c r="C52" t="s">
         <v>6</v>
       </c>
@@ -3226,7 +4216,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="53" spans="2:4">
+    <row r="53" spans="2:12">
       <c r="C53" t="s">
         <v>7</v>
       </c>
@@ -3234,20 +4224,29 @@
         <v>242</v>
       </c>
     </row>
-    <row r="55" spans="2:4">
-      <c r="B55" t="s">
+    <row r="55" spans="2:12">
+      <c r="B55">
+        <v>6</v>
+      </c>
+      <c r="C55" t="s">
         <v>243</v>
       </c>
-    </row>
-    <row r="56" spans="2:4">
-      <c r="B56" t="s">
+      <c r="J55" t="s">
+        <v>8</v>
+      </c>
+      <c r="K55" t="s">
+        <v>10</v>
+      </c>
+      <c r="L55" s="1">
+        <v>46109</v>
+      </c>
+    </row>
+    <row r="56" spans="2:12">
+      <c r="C56" t="s">
         <v>244</v>
       </c>
     </row>
-    <row r="57" spans="2:4">
-      <c r="B57" t="s">
-        <v>8</v>
-      </c>
+    <row r="57" spans="2:12">
       <c r="C57" t="s">
         <v>147</v>
       </c>
@@ -3255,7 +4254,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="58" spans="2:4">
+    <row r="58" spans="2:12">
       <c r="C58" t="s">
         <v>5</v>
       </c>
@@ -3263,7 +4262,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="59" spans="2:4">
+    <row r="59" spans="2:12">
       <c r="C59" t="s">
         <v>6</v>
       </c>
@@ -3271,7 +4270,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="60" spans="2:4">
+    <row r="60" spans="2:12">
       <c r="C60" t="s">
         <v>7</v>
       </c>
@@ -3279,20 +4278,29 @@
         <v>248</v>
       </c>
     </row>
-    <row r="62" spans="2:4">
-      <c r="B62" t="s">
+    <row r="62" spans="2:12">
+      <c r="B62">
+        <v>7</v>
+      </c>
+      <c r="C62" t="s">
         <v>249</v>
       </c>
-    </row>
-    <row r="63" spans="2:4">
-      <c r="B63" t="s">
+      <c r="J62" t="s">
+        <v>8</v>
+      </c>
+      <c r="K62" t="s">
+        <v>10</v>
+      </c>
+      <c r="L62" s="1">
+        <v>46109</v>
+      </c>
+    </row>
+    <row r="63" spans="2:12">
+      <c r="C63" t="s">
         <v>238</v>
       </c>
     </row>
-    <row r="64" spans="2:4">
-      <c r="B64" t="s">
-        <v>8</v>
-      </c>
+    <row r="64" spans="2:12">
       <c r="C64" t="s">
         <v>147</v>
       </c>
@@ -3300,7 +4308,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="65" spans="3:4">
+    <row r="65" spans="3:10">
       <c r="C65" t="s">
         <v>5</v>
       </c>
@@ -3308,7 +4316,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="66" spans="3:4">
+    <row r="66" spans="3:10">
       <c r="C66" t="s">
         <v>6</v>
       </c>
@@ -3316,12 +4324,18 @@
         <v>253</v>
       </c>
     </row>
-    <row r="67" spans="3:4">
+    <row r="67" spans="3:10">
       <c r="C67" t="s">
         <v>7</v>
       </c>
       <c r="D67" t="s">
         <v>250</v>
+      </c>
+    </row>
+    <row r="68" spans="3:10">
+      <c r="J68" s="3">
+        <f>COUNTIF(J2:J67,"○")/COUNTA(J2:J67)</f>
+        <v>0.8571428571428571</v>
       </c>
     </row>
   </sheetData>
@@ -3332,23 +4346,93 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{14668F10-8DE2-47B9-8E79-4C07054C4344}">
+  <dimension ref="B2:C8"/>
+  <sheetFormatPr defaultRowHeight="18"/>
+  <sheetData>
+    <row r="2" spans="2:3">
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="2:3">
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="2:3">
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="2:3">
+      <c r="B5">
+        <v>4</v>
+      </c>
+      <c r="C5" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="6" spans="2:3">
+      <c r="B6">
+        <v>5</v>
+      </c>
+      <c r="C6" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="7" spans="2:3">
+      <c r="B7">
+        <v>6</v>
+      </c>
+      <c r="C7" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="8" spans="2:3">
+      <c r="B8">
+        <v>7</v>
+      </c>
+      <c r="C8" t="s">
+        <v>147</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CFBD2AC0-38EC-4B9C-A0BF-1559C25A244C}">
   <sheetPr codeName="Sheet3"/>
-  <dimension ref="B2:O108"/>
+  <dimension ref="B2:R108"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
-    <col min="5" max="5" width="8.6640625" hidden="1" customWidth="1"/>
-    <col min="6" max="6" width="10.1640625" hidden="1" customWidth="1"/>
-    <col min="7" max="7" width="8.6640625" customWidth="1"/>
+    <col min="5" max="5" width="8.69921875" hidden="1" customWidth="1"/>
+    <col min="6" max="6" width="10.19921875" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="8.69921875" customWidth="1"/>
     <col min="8" max="8" width="0" hidden="1" customWidth="1"/>
-    <col min="9" max="9" width="10.1640625" hidden="1" customWidth="1"/>
-    <col min="11" max="11" width="0" hidden="1" customWidth="1"/>
-    <col min="12" max="12" width="10.25" hidden="1" customWidth="1"/>
-    <col min="15" max="15" width="10" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.19921875" hidden="1" customWidth="1"/>
+    <col min="10" max="10" width="0" hidden="1" customWidth="1"/>
+    <col min="11" max="11" width="8.796875" hidden="1" customWidth="1"/>
+    <col min="12" max="12" width="10.19921875" hidden="1" customWidth="1"/>
+    <col min="14" max="14" width="8.796875" hidden="1" customWidth="1"/>
+    <col min="15" max="15" width="10.19921875" hidden="1" customWidth="1"/>
+    <col min="18" max="18" width="10.19921875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:15">
+    <row r="2" spans="2:18">
       <c r="B2">
         <v>1</v>
       </c>
@@ -3365,7 +4449,7 @@
         <v>46075</v>
       </c>
     </row>
-    <row r="3" spans="2:15">
+    <row r="3" spans="2:18">
       <c r="C3">
         <v>2</v>
       </c>
@@ -3376,7 +4460,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="2:15">
+    <row r="4" spans="2:18">
       <c r="C4">
         <v>3</v>
       </c>
@@ -3387,7 +4471,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="2:15">
+    <row r="5" spans="2:18">
       <c r="C5">
         <v>4</v>
       </c>
@@ -3407,7 +4491,7 @@
         <v>46092</v>
       </c>
     </row>
-    <row r="6" spans="2:15">
+    <row r="6" spans="2:18">
       <c r="C6">
         <v>5</v>
       </c>
@@ -3418,7 +4502,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="2:15">
+    <row r="7" spans="2:18">
       <c r="C7">
         <v>6</v>
       </c>
@@ -3446,8 +4530,17 @@
       <c r="L7" s="1">
         <v>46104</v>
       </c>
-    </row>
-    <row r="8" spans="2:15">
+      <c r="M7" t="s">
+        <v>8</v>
+      </c>
+      <c r="N7" t="s">
+        <v>11</v>
+      </c>
+      <c r="O7" s="1">
+        <v>46109</v>
+      </c>
+    </row>
+    <row r="8" spans="2:18">
       <c r="C8">
         <v>7</v>
       </c>
@@ -3467,7 +4560,7 @@
         <v>46092</v>
       </c>
     </row>
-    <row r="9" spans="2:15">
+    <row r="9" spans="2:18">
       <c r="C9">
         <v>8</v>
       </c>
@@ -3478,7 +4571,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="2:15">
+    <row r="10" spans="2:18">
       <c r="C10">
         <v>9</v>
       </c>
@@ -3498,7 +4591,7 @@
         <v>46092</v>
       </c>
     </row>
-    <row r="11" spans="2:15">
+    <row r="11" spans="2:18">
       <c r="C11">
         <v>10</v>
       </c>
@@ -3527,7 +4620,7 @@
         <v>46104</v>
       </c>
     </row>
-    <row r="12" spans="2:15">
+    <row r="12" spans="2:18">
       <c r="C12">
         <v>11</v>
       </c>
@@ -3564,8 +4657,17 @@
       <c r="O12" s="1">
         <v>46106</v>
       </c>
-    </row>
-    <row r="13" spans="2:15">
+      <c r="P12" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>12</v>
+      </c>
+      <c r="R12" s="1">
+        <v>46109</v>
+      </c>
+    </row>
+    <row r="13" spans="2:18">
       <c r="C13">
         <v>12</v>
       </c>
@@ -3594,7 +4696,7 @@
         <v>46104</v>
       </c>
     </row>
-    <row r="14" spans="2:15">
+    <row r="14" spans="2:18">
       <c r="C14">
         <v>13</v>
       </c>
@@ -3614,7 +4716,7 @@
         <v>46092</v>
       </c>
     </row>
-    <row r="15" spans="2:15">
+    <row r="15" spans="2:18">
       <c r="C15">
         <v>14</v>
       </c>
@@ -3625,7 +4727,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="16" spans="2:15">
+    <row r="16" spans="2:18">
       <c r="C16">
         <v>15</v>
       </c>
@@ -3636,7 +4738,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="17" spans="2:15">
+    <row r="17" spans="2:18">
       <c r="C17">
         <v>16</v>
       </c>
@@ -3647,7 +4749,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="18" spans="2:15">
+    <row r="18" spans="2:18">
       <c r="B18">
         <v>2</v>
       </c>
@@ -3673,7 +4775,7 @@
         <v>46092</v>
       </c>
     </row>
-    <row r="19" spans="2:15">
+    <row r="19" spans="2:18">
       <c r="C19">
         <v>2</v>
       </c>
@@ -3684,7 +4786,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="20" spans="2:15">
+    <row r="20" spans="2:18">
       <c r="C20">
         <v>3</v>
       </c>
@@ -3695,7 +4797,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="21" spans="2:15">
+    <row r="21" spans="2:18">
       <c r="C21">
         <v>4</v>
       </c>
@@ -3706,7 +4808,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="22" spans="2:15">
+    <row r="22" spans="2:18">
       <c r="C22">
         <v>5</v>
       </c>
@@ -3717,7 +4819,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="23" spans="2:15">
+    <row r="23" spans="2:18">
       <c r="C23">
         <v>6</v>
       </c>
@@ -3745,11 +4847,17 @@
       <c r="L23" s="1">
         <v>46105</v>
       </c>
+      <c r="M23" t="s">
+        <v>8</v>
+      </c>
+      <c r="N23" t="s">
+        <v>10</v>
+      </c>
       <c r="O23" s="1">
-        <v>46106</v>
-      </c>
-    </row>
-    <row r="24" spans="2:15">
+        <v>46109</v>
+      </c>
+    </row>
+    <row r="24" spans="2:18">
       <c r="C24">
         <v>7</v>
       </c>
@@ -3760,7 +4868,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="25" spans="2:15">
+    <row r="25" spans="2:18">
       <c r="C25">
         <v>8</v>
       </c>
@@ -3788,8 +4896,17 @@
       <c r="L25" s="1">
         <v>46105</v>
       </c>
-    </row>
-    <row r="26" spans="2:15">
+      <c r="M25" t="s">
+        <v>8</v>
+      </c>
+      <c r="N25" t="s">
+        <v>10</v>
+      </c>
+      <c r="O25" s="1">
+        <v>46109</v>
+      </c>
+    </row>
+    <row r="26" spans="2:18">
       <c r="C26">
         <v>9</v>
       </c>
@@ -3800,7 +4917,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="27" spans="2:15">
+    <row r="27" spans="2:18">
       <c r="C27">
         <v>10</v>
       </c>
@@ -3811,7 +4928,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="28" spans="2:15">
+    <row r="28" spans="2:18">
       <c r="C28">
         <v>11</v>
       </c>
@@ -3839,8 +4956,26 @@
       <c r="L28" s="1">
         <v>46105</v>
       </c>
-    </row>
-    <row r="29" spans="2:15">
+      <c r="M28" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="N28" t="s">
+        <v>9</v>
+      </c>
+      <c r="O28" s="1">
+        <v>46109</v>
+      </c>
+      <c r="P28" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q28" t="s">
+        <v>11</v>
+      </c>
+      <c r="R28" s="1">
+        <v>46109</v>
+      </c>
+    </row>
+    <row r="29" spans="2:18">
       <c r="C29">
         <v>12</v>
       </c>
@@ -3860,7 +4995,7 @@
         <v>46093</v>
       </c>
     </row>
-    <row r="30" spans="2:15">
+    <row r="30" spans="2:18">
       <c r="C30">
         <v>13</v>
       </c>
@@ -3871,7 +5006,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="31" spans="2:15">
+    <row r="31" spans="2:18">
       <c r="C31">
         <v>14</v>
       </c>
@@ -3899,8 +5034,26 @@
       <c r="L31" s="1">
         <v>46105</v>
       </c>
-    </row>
-    <row r="32" spans="2:15">
+      <c r="M31" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="N31" t="s">
+        <v>10</v>
+      </c>
+      <c r="O31" s="1">
+        <v>46109</v>
+      </c>
+      <c r="P31" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q31" t="s">
+        <v>9</v>
+      </c>
+      <c r="R31" s="1">
+        <v>46109</v>
+      </c>
+    </row>
+    <row r="32" spans="2:18">
       <c r="C32">
         <v>15</v>
       </c>
@@ -3911,7 +5064,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="33" spans="2:12">
+    <row r="33" spans="2:18">
       <c r="C33">
         <v>16</v>
       </c>
@@ -3922,7 +5075,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="34" spans="2:12">
+    <row r="34" spans="2:18">
       <c r="B34">
         <v>3</v>
       </c>
@@ -3948,7 +5101,7 @@
         <v>46094</v>
       </c>
     </row>
-    <row r="35" spans="2:12">
+    <row r="35" spans="2:18">
       <c r="C35">
         <v>2</v>
       </c>
@@ -3968,7 +5121,7 @@
         <v>46094</v>
       </c>
     </row>
-    <row r="36" spans="2:12">
+    <row r="36" spans="2:18">
       <c r="C36">
         <v>3</v>
       </c>
@@ -3979,7 +5132,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="37" spans="2:12">
+    <row r="37" spans="2:18">
       <c r="C37">
         <v>4</v>
       </c>
@@ -3990,7 +5143,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="38" spans="2:12">
+    <row r="38" spans="2:18">
       <c r="C38">
         <v>5</v>
       </c>
@@ -4001,7 +5154,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="39" spans="2:12">
+    <row r="39" spans="2:18">
       <c r="C39">
         <v>6</v>
       </c>
@@ -4029,8 +5182,17 @@
       <c r="L39" s="1">
         <v>46105</v>
       </c>
-    </row>
-    <row r="40" spans="2:12">
+      <c r="M39" t="s">
+        <v>8</v>
+      </c>
+      <c r="N39" t="s">
+        <v>9</v>
+      </c>
+      <c r="O39" s="1">
+        <v>46109</v>
+      </c>
+    </row>
+    <row r="40" spans="2:18">
       <c r="C40">
         <v>7</v>
       </c>
@@ -4058,8 +5220,26 @@
       <c r="L40" s="1">
         <v>46105</v>
       </c>
-    </row>
-    <row r="41" spans="2:12">
+      <c r="M40" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="N40" t="s">
+        <v>10</v>
+      </c>
+      <c r="O40" s="1">
+        <v>46109</v>
+      </c>
+      <c r="P40" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q40" t="s">
+        <v>11</v>
+      </c>
+      <c r="R40" s="1">
+        <v>46109</v>
+      </c>
+    </row>
+    <row r="41" spans="2:18">
       <c r="C41">
         <v>8</v>
       </c>
@@ -4070,7 +5250,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="42" spans="2:12">
+    <row r="42" spans="2:18">
       <c r="B42">
         <v>4</v>
       </c>
@@ -4104,8 +5284,26 @@
       <c r="L42" s="1">
         <v>46105</v>
       </c>
-    </row>
-    <row r="43" spans="2:12">
+      <c r="M42" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="N42" t="s">
+        <v>10</v>
+      </c>
+      <c r="O42" s="1">
+        <v>46109</v>
+      </c>
+      <c r="P42" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q42" t="s">
+        <v>12</v>
+      </c>
+      <c r="R42" s="1">
+        <v>46109</v>
+      </c>
+    </row>
+    <row r="43" spans="2:18">
       <c r="C43">
         <v>2</v>
       </c>
@@ -4116,7 +5314,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="44" spans="2:12">
+    <row r="44" spans="2:18">
       <c r="C44">
         <v>3</v>
       </c>
@@ -4136,7 +5334,7 @@
         <v>46094</v>
       </c>
     </row>
-    <row r="45" spans="2:12">
+    <row r="45" spans="2:18">
       <c r="C45">
         <v>4</v>
       </c>
@@ -4164,8 +5362,17 @@
       <c r="L45" s="1">
         <v>46105</v>
       </c>
-    </row>
-    <row r="46" spans="2:12">
+      <c r="M45" t="s">
+        <v>8</v>
+      </c>
+      <c r="N45" t="s">
+        <v>11</v>
+      </c>
+      <c r="O45" s="1">
+        <v>46109</v>
+      </c>
+    </row>
+    <row r="46" spans="2:18">
       <c r="C46">
         <v>5</v>
       </c>
@@ -4176,7 +5383,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="47" spans="2:12">
+    <row r="47" spans="2:18">
       <c r="C47">
         <v>6</v>
       </c>
@@ -4187,7 +5394,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="48" spans="2:12">
+    <row r="48" spans="2:18">
       <c r="C48">
         <v>7</v>
       </c>
@@ -4198,7 +5405,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="49" spans="2:12">
+    <row r="49" spans="2:18">
       <c r="C49">
         <v>8</v>
       </c>
@@ -4209,7 +5416,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="50" spans="2:12">
+    <row r="50" spans="2:18">
       <c r="C50">
         <v>9</v>
       </c>
@@ -4237,8 +5444,26 @@
       <c r="L50" s="1">
         <v>46105</v>
       </c>
-    </row>
-    <row r="51" spans="2:12">
+      <c r="M50" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="N50" t="s">
+        <v>9</v>
+      </c>
+      <c r="O50" s="1">
+        <v>46109</v>
+      </c>
+      <c r="P50" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q50" t="s">
+        <v>12</v>
+      </c>
+      <c r="R50" s="1">
+        <v>46109</v>
+      </c>
+    </row>
+    <row r="51" spans="2:18">
       <c r="C51">
         <v>10</v>
       </c>
@@ -4266,8 +5491,26 @@
       <c r="L51" s="1">
         <v>46105</v>
       </c>
-    </row>
-    <row r="52" spans="2:12">
+      <c r="M51" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="N51" t="s">
+        <v>9</v>
+      </c>
+      <c r="O51" s="1">
+        <v>46109</v>
+      </c>
+      <c r="P51" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q51" t="s">
+        <v>10</v>
+      </c>
+      <c r="R51" s="1">
+        <v>46109</v>
+      </c>
+    </row>
+    <row r="52" spans="2:18">
       <c r="C52">
         <v>11</v>
       </c>
@@ -4287,7 +5530,7 @@
         <v>46094</v>
       </c>
     </row>
-    <row r="53" spans="2:12">
+    <row r="53" spans="2:18">
       <c r="C53">
         <v>12</v>
       </c>
@@ -4315,8 +5558,17 @@
       <c r="L53" s="1">
         <v>46105</v>
       </c>
-    </row>
-    <row r="54" spans="2:12">
+      <c r="M53" t="s">
+        <v>8</v>
+      </c>
+      <c r="N53" t="s">
+        <v>9</v>
+      </c>
+      <c r="O53" s="1">
+        <v>46109</v>
+      </c>
+    </row>
+    <row r="54" spans="2:18">
       <c r="B54">
         <v>5</v>
       </c>
@@ -4342,7 +5594,7 @@
         <v>46094</v>
       </c>
     </row>
-    <row r="55" spans="2:12">
+    <row r="55" spans="2:18">
       <c r="C55">
         <v>2</v>
       </c>
@@ -4370,8 +5622,17 @@
       <c r="L55" s="1">
         <v>46105</v>
       </c>
-    </row>
-    <row r="56" spans="2:12">
+      <c r="M55" t="s">
+        <v>8</v>
+      </c>
+      <c r="N55" t="s">
+        <v>10</v>
+      </c>
+      <c r="O55" s="1">
+        <v>46109</v>
+      </c>
+    </row>
+    <row r="56" spans="2:18">
       <c r="C56">
         <v>3</v>
       </c>
@@ -4382,7 +5643,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="57" spans="2:12">
+    <row r="57" spans="2:18">
       <c r="C57">
         <v>4</v>
       </c>
@@ -4393,7 +5654,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="58" spans="2:12">
+    <row r="58" spans="2:18">
       <c r="C58">
         <v>5</v>
       </c>
@@ -4404,7 +5665,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="59" spans="2:12">
+    <row r="59" spans="2:18">
       <c r="C59">
         <v>6</v>
       </c>
@@ -4415,7 +5676,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="60" spans="2:12">
+    <row r="60" spans="2:18">
       <c r="C60">
         <v>7</v>
       </c>
@@ -4443,8 +5704,26 @@
       <c r="L60" s="1">
         <v>46105</v>
       </c>
-    </row>
-    <row r="61" spans="2:12">
+      <c r="M60" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="N60" t="s">
+        <v>12</v>
+      </c>
+      <c r="O60" s="1">
+        <v>46109</v>
+      </c>
+      <c r="P60" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q60" t="s">
+        <v>11</v>
+      </c>
+      <c r="R60" s="1">
+        <v>46109</v>
+      </c>
+    </row>
+    <row r="61" spans="2:18">
       <c r="C61">
         <v>8</v>
       </c>
@@ -4455,7 +5734,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="62" spans="2:12">
+    <row r="62" spans="2:18">
       <c r="C62">
         <v>9</v>
       </c>
@@ -4466,7 +5745,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="63" spans="2:12">
+    <row r="63" spans="2:18">
       <c r="C63">
         <v>10</v>
       </c>
@@ -4477,7 +5756,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="64" spans="2:12">
+    <row r="64" spans="2:18">
       <c r="C64">
         <v>11</v>
       </c>
@@ -4488,7 +5767,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="65" spans="2:12">
+    <row r="65" spans="2:15">
       <c r="C65">
         <v>12</v>
       </c>
@@ -4516,8 +5795,17 @@
       <c r="L65" s="1">
         <v>46105</v>
       </c>
-    </row>
-    <row r="66" spans="2:12">
+      <c r="M65" t="s">
+        <v>8</v>
+      </c>
+      <c r="N65" t="s">
+        <v>12</v>
+      </c>
+      <c r="O65" s="1">
+        <v>46109</v>
+      </c>
+    </row>
+    <row r="66" spans="2:15">
       <c r="B66">
         <v>6</v>
       </c>
@@ -4552,7 +5840,7 @@
         <v>46105</v>
       </c>
     </row>
-    <row r="67" spans="2:12">
+    <row r="67" spans="2:15">
       <c r="C67">
         <v>2</v>
       </c>
@@ -4563,7 +5851,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="68" spans="2:12">
+    <row r="68" spans="2:15">
       <c r="B68">
         <v>7</v>
       </c>
@@ -4580,7 +5868,7 @@
         <v>46089</v>
       </c>
     </row>
-    <row r="69" spans="2:12">
+    <row r="69" spans="2:15">
       <c r="C69">
         <v>2</v>
       </c>
@@ -4591,7 +5879,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="70" spans="2:12">
+    <row r="70" spans="2:15">
       <c r="C70">
         <v>3</v>
       </c>
@@ -4602,7 +5890,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="71" spans="2:12">
+    <row r="71" spans="2:15">
       <c r="C71">
         <v>4</v>
       </c>
@@ -4613,7 +5901,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="72" spans="2:12">
+    <row r="72" spans="2:15">
       <c r="C72">
         <v>5</v>
       </c>
@@ -4624,7 +5912,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="73" spans="2:12">
+    <row r="73" spans="2:15">
       <c r="C73">
         <v>6</v>
       </c>
@@ -4635,7 +5923,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="74" spans="2:12">
+    <row r="74" spans="2:15">
       <c r="C74">
         <v>7</v>
       </c>
@@ -4646,7 +5934,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="75" spans="2:12">
+    <row r="75" spans="2:15">
       <c r="C75">
         <v>8</v>
       </c>
@@ -4657,7 +5945,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="76" spans="2:12">
+    <row r="76" spans="2:15">
       <c r="C76">
         <v>9</v>
       </c>
@@ -4668,7 +5956,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="77" spans="2:12">
+    <row r="77" spans="2:15">
       <c r="C77">
         <v>10</v>
       </c>
@@ -4688,7 +5976,7 @@
         <v>46097</v>
       </c>
     </row>
-    <row r="78" spans="2:12">
+    <row r="78" spans="2:15">
       <c r="C78">
         <v>11</v>
       </c>
@@ -4702,7 +5990,7 @@
         <v>46090</v>
       </c>
     </row>
-    <row r="79" spans="2:12">
+    <row r="79" spans="2:15">
       <c r="C79">
         <v>12</v>
       </c>
@@ -4713,7 +6001,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="80" spans="2:12">
+    <row r="80" spans="2:15">
       <c r="C80">
         <v>13</v>
       </c>
@@ -4733,7 +6021,7 @@
         <v>46097</v>
       </c>
     </row>
-    <row r="81" spans="3:12">
+    <row r="81" spans="3:15">
       <c r="C81">
         <v>14</v>
       </c>
@@ -4744,7 +6032,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="82" spans="3:12">
+    <row r="82" spans="3:15">
       <c r="C82">
         <v>15</v>
       </c>
@@ -4767,7 +6055,7 @@
         <v>46104</v>
       </c>
     </row>
-    <row r="83" spans="3:12">
+    <row r="83" spans="3:15">
       <c r="C83">
         <v>16</v>
       </c>
@@ -4778,7 +6066,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="84" spans="3:12">
+    <row r="84" spans="3:15">
       <c r="C84">
         <v>17</v>
       </c>
@@ -4798,7 +6086,7 @@
         <v>46104</v>
       </c>
     </row>
-    <row r="85" spans="3:12">
+    <row r="85" spans="3:15">
       <c r="C85">
         <v>18</v>
       </c>
@@ -4809,7 +6097,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="86" spans="3:12">
+    <row r="86" spans="3:15">
       <c r="C86">
         <v>19</v>
       </c>
@@ -4820,7 +6108,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="87" spans="3:12">
+    <row r="87" spans="3:15">
       <c r="C87">
         <v>20</v>
       </c>
@@ -4831,7 +6119,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="88" spans="3:12">
+    <row r="88" spans="3:15">
       <c r="C88">
         <v>21</v>
       </c>
@@ -4842,7 +6130,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="89" spans="3:12">
+    <row r="89" spans="3:15">
       <c r="C89">
         <v>22</v>
       </c>
@@ -4853,7 +6141,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="90" spans="3:12">
+    <row r="90" spans="3:15">
       <c r="C90">
         <v>23</v>
       </c>
@@ -4864,7 +6152,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="91" spans="3:12">
+    <row r="91" spans="3:15">
       <c r="C91">
         <v>24</v>
       </c>
@@ -4892,8 +6180,17 @@
       <c r="L91" s="1">
         <v>46105</v>
       </c>
-    </row>
-    <row r="92" spans="3:12">
+      <c r="M91" t="s">
+        <v>255</v>
+      </c>
+      <c r="N91" t="s">
+        <v>12</v>
+      </c>
+      <c r="O91" s="1">
+        <v>46109</v>
+      </c>
+    </row>
+    <row r="92" spans="3:15">
       <c r="C92">
         <v>25</v>
       </c>
@@ -4904,7 +6201,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="93" spans="3:12">
+    <row r="93" spans="3:15">
       <c r="C93">
         <v>26</v>
       </c>
@@ -4924,7 +6221,7 @@
         <v>46104</v>
       </c>
     </row>
-    <row r="94" spans="3:12">
+    <row r="94" spans="3:15">
       <c r="C94">
         <v>27</v>
       </c>
@@ -4952,8 +6249,17 @@
       <c r="L94" s="1">
         <v>46105</v>
       </c>
-    </row>
-    <row r="95" spans="3:12">
+      <c r="M94" t="s">
+        <v>255</v>
+      </c>
+      <c r="N94" t="s">
+        <v>12</v>
+      </c>
+      <c r="O94" s="1">
+        <v>46109</v>
+      </c>
+    </row>
+    <row r="95" spans="3:15">
       <c r="C95">
         <v>28</v>
       </c>
@@ -4981,8 +6287,17 @@
       <c r="L95" s="1">
         <v>46105</v>
       </c>
-    </row>
-    <row r="96" spans="3:12">
+      <c r="M95" t="s">
+        <v>255</v>
+      </c>
+      <c r="N95" t="s">
+        <v>12</v>
+      </c>
+      <c r="O95" s="1">
+        <v>46109</v>
+      </c>
+    </row>
+    <row r="96" spans="3:15">
       <c r="C96">
         <v>29</v>
       </c>
@@ -4993,7 +6308,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="97" spans="3:12">
+    <row r="97" spans="3:16">
       <c r="C97">
         <v>30</v>
       </c>
@@ -5004,7 +6319,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="98" spans="3:12">
+    <row r="98" spans="3:16">
       <c r="C98">
         <v>31</v>
       </c>
@@ -5015,7 +6330,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="99" spans="3:12">
+    <row r="99" spans="3:16">
       <c r="C99">
         <v>32</v>
       </c>
@@ -5043,8 +6358,17 @@
       <c r="L99" s="1">
         <v>46105</v>
       </c>
-    </row>
-    <row r="100" spans="3:12">
+      <c r="M99" t="s">
+        <v>255</v>
+      </c>
+      <c r="N99" t="s">
+        <v>10</v>
+      </c>
+      <c r="O99" s="1">
+        <v>46109</v>
+      </c>
+    </row>
+    <row r="100" spans="3:16">
       <c r="C100">
         <v>33</v>
       </c>
@@ -5055,7 +6379,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="101" spans="3:12">
+    <row r="101" spans="3:16">
       <c r="C101">
         <v>34</v>
       </c>
@@ -5075,7 +6399,7 @@
         <v>46104</v>
       </c>
     </row>
-    <row r="102" spans="3:12">
+    <row r="102" spans="3:16">
       <c r="C102">
         <v>35</v>
       </c>
@@ -5103,8 +6427,17 @@
       <c r="L102" s="1">
         <v>46105</v>
       </c>
-    </row>
-    <row r="103" spans="3:12">
+      <c r="M102" t="s">
+        <v>255</v>
+      </c>
+      <c r="N102" t="s">
+        <v>9</v>
+      </c>
+      <c r="O102" s="1">
+        <v>46109</v>
+      </c>
+    </row>
+    <row r="103" spans="3:16">
       <c r="C103">
         <v>36</v>
       </c>
@@ -5115,7 +6448,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="104" spans="3:12">
+    <row r="104" spans="3:16">
       <c r="C104">
         <v>37</v>
       </c>
@@ -5143,8 +6476,17 @@
       <c r="L104" s="1">
         <v>46105</v>
       </c>
-    </row>
-    <row r="105" spans="3:12">
+      <c r="M104" t="s">
+        <v>255</v>
+      </c>
+      <c r="N104" t="s">
+        <v>11</v>
+      </c>
+      <c r="O104" s="1">
+        <v>46109</v>
+      </c>
+    </row>
+    <row r="105" spans="3:16">
       <c r="C105">
         <v>38</v>
       </c>
@@ -5155,7 +6497,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="106" spans="3:12">
+    <row r="106" spans="3:16">
       <c r="C106">
         <v>39</v>
       </c>
@@ -5183,8 +6525,17 @@
       <c r="L106" s="1">
         <v>46105</v>
       </c>
-    </row>
-    <row r="107" spans="3:12">
+      <c r="M106" t="s">
+        <v>255</v>
+      </c>
+      <c r="N106" t="s">
+        <v>12</v>
+      </c>
+      <c r="O106" s="1">
+        <v>46109</v>
+      </c>
+    </row>
+    <row r="107" spans="3:16">
       <c r="C107">
         <v>40</v>
       </c>
@@ -5195,7 +6546,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="108" spans="3:12">
+    <row r="108" spans="3:16">
       <c r="D108" s="3">
         <f>COUNTIF(D2:D107,"○")/COUNTA(D2:D107)</f>
         <v>0.59433962264150941</v>
@@ -5215,6 +6566,14 @@
       <c r="J108" s="3">
         <f>COUNTIF(J2:J107,"○")/COUNTA(J2:J107)</f>
         <v>0.61538461538461542</v>
+      </c>
+      <c r="M108" s="3">
+        <f>COUNTIF(M2:M107,"○")/COUNTA(M2:M107)</f>
+        <v>0.65217391304347827</v>
+      </c>
+      <c r="P108" s="3">
+        <f>COUNTIF(P2:P107,"○")/COUNTA(P2:P107)</f>
+        <v>0.875</v>
       </c>
     </row>
   </sheetData>
@@ -5222,4 +6581,226 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D31F101-46C1-44B2-8ACA-D9FBA0843003}">
+  <dimension ref="B2:D15"/>
+  <sheetFormatPr defaultRowHeight="18"/>
+  <sheetData>
+    <row r="2" spans="2:4">
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="3" spans="2:4">
+      <c r="C3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="4" spans="2:4">
+      <c r="C4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="5" spans="2:4">
+      <c r="C5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D5" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="6" spans="2:4">
+      <c r="C6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D6" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="7" spans="2:4">
+      <c r="C7" t="s">
+        <v>257</v>
+      </c>
+      <c r="D7" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="8" spans="2:4">
+      <c r="C8" t="s">
+        <v>258</v>
+      </c>
+      <c r="D8" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="9" spans="2:4">
+      <c r="B9">
+        <v>2</v>
+      </c>
+      <c r="C9" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="10" spans="2:4">
+      <c r="C10" t="s">
+        <v>10</v>
+      </c>
+      <c r="D10" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="11" spans="2:4">
+      <c r="C11" t="s">
+        <v>9</v>
+      </c>
+      <c r="D11" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="12" spans="2:4">
+      <c r="C12" t="s">
+        <v>11</v>
+      </c>
+      <c r="D12" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="13" spans="2:4">
+      <c r="C13" t="s">
+        <v>12</v>
+      </c>
+      <c r="D13" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="14" spans="2:4">
+      <c r="C14" t="s">
+        <v>257</v>
+      </c>
+      <c r="D14" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="15" spans="2:4">
+      <c r="C15" t="s">
+        <v>258</v>
+      </c>
+      <c r="D15" t="s">
+        <v>271</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4F9E86CE-0C54-4910-857C-CE213AABC91E}">
+  <dimension ref="B2:C4"/>
+  <sheetFormatPr defaultRowHeight="18"/>
+  <sheetData>
+    <row r="2" spans="2:3">
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="2:3">
+      <c r="C3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="2:3">
+      <c r="C4" t="s">
+        <v>257</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3484731F-D563-4573-BC0F-79D78D330990}">
+  <dimension ref="B2:D6"/>
+  <sheetFormatPr defaultRowHeight="18"/>
+  <sheetData>
+    <row r="2" spans="2:4">
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="3" spans="2:4">
+      <c r="C3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="4" spans="2:4">
+      <c r="C4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="5" spans="2:4">
+      <c r="C5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D5" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="6" spans="2:4">
+      <c r="C6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D6" t="s">
+        <v>276</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{620A70BD-F03C-4EB8-A732-46147BB70A88}">
+  <dimension ref="B2:C2"/>
+  <sheetFormatPr defaultRowHeight="18"/>
+  <sheetData>
+    <row r="2" spans="2:3">
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/JSTQB_Foundation.xlsx
+++ b/JSTQB_Foundation.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27932"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29530"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ドキュメント\勉強\資格(取得)\JSTQB\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ドキュメント\その他\eラーニング\JSTQB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6DE5720-C978-48D6-B118-8D207D0CDC33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C42EF7AF-6B86-4C56-85B5-3C0E4535DC75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="43095" yWindow="0" windowWidth="14610" windowHeight="16305" firstSheet="7" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="テス友" sheetId="1" r:id="rId1"/>
@@ -39,15 +39,12 @@
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1027" uniqueCount="277">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1441" uniqueCount="470">
   <si>
     <t>典型的なテストの目的として、誤っているものはどれか。次の選択肢の中から1つ選びなさい。</t>
     <phoneticPr fontId="1"/>
@@ -1194,6 +1191,2202 @@
     </rPh>
     <rPh sb="10" eb="12">
       <t>カクチョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>妥当性確認の例として正しいものをすべて選びなさい。</t>
+    <rPh sb="0" eb="3">
+      <t>ダトウセイ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>カクニン</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>レイ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>タダ</t>
+    </rPh>
+    <rPh sb="19" eb="20">
+      <t>エラ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ソフトウェアの処理速度を測る</t>
+    <rPh sb="7" eb="9">
+      <t>ショリ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ソクド</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>ハカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ソフトウェアのバグ件数を数える</t>
+    <rPh sb="9" eb="11">
+      <t>ケンスウ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>カゾ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>高齢者向けアプリで操作が簡単か確認する</t>
+    <rPh sb="0" eb="3">
+      <t>コウレイシャ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ム</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ソウサ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>カンタン</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>カクニン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ソースコードの文法をチェックする</t>
+    <rPh sb="7" eb="9">
+      <t>ブンポウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アプリの文字が見やすいか確認する</t>
+    <rPh sb="4" eb="6">
+      <t>モジ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>ミ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>カクニン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>プログラマーの作業時間を管理する</t>
+    <rPh sb="7" eb="9">
+      <t>サギョウ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ジカン</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>カンリ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ソフトウェアテストで求められるスキルや活動として正しいものをすべて選びなさい</t>
+    <rPh sb="10" eb="11">
+      <t>モト</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>カツドウ</t>
+    </rPh>
+    <rPh sb="24" eb="25">
+      <t>タダ</t>
+    </rPh>
+    <rPh sb="33" eb="34">
+      <t>エラ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>新しい言語を開発する能力</t>
+    <rPh sb="0" eb="1">
+      <t>アタラ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ゲンゴ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>カイハツ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ノウリョク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>分析力</t>
+    <rPh sb="0" eb="3">
+      <t>ブンセキリョク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ソフトウェアを販売する能力</t>
+    <rPh sb="7" eb="9">
+      <t>ハンバイ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ノウリョク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>批判的思考</t>
+    <rPh sb="0" eb="3">
+      <t>ヒハンテキ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>シコウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ネットワークを組む能力</t>
+    <rPh sb="7" eb="8">
+      <t>ク</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ノウリョク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ツールを活用する能力</t>
+    <rPh sb="4" eb="6">
+      <t>カツヨウ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ノウリョク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>作業成果物の評価に含まれるものはどれですか？</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>要件</t>
+    <rPh sb="0" eb="2">
+      <t>ヨウケン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ユーザーストーリー</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>利用者の口コミ</t>
+    <rPh sb="0" eb="3">
+      <t>リヨウシャ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>クチ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ソースコード</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>広告ポスター</t>
+    <rPh sb="0" eb="2">
+      <t>コウコク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>会社のロゴ</t>
+    <rPh sb="0" eb="2">
+      <t>カイシャ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>欠陥の例として当てはまるものをすべて選んでください</t>
+    <rPh sb="0" eb="2">
+      <t>ケッカン</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>レイ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>エラ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ログインが速くなる</t>
+    <rPh sb="5" eb="6">
+      <t>ハヤ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>電卓アプリが0で割るとクラッシュする</t>
+    <rPh sb="0" eb="2">
+      <t>デンタク</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>ワ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>デザインが綺麗になる</t>
+    <rPh sb="5" eb="7">
+      <t>キレイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>新しい家電が電源を入れても動かない</t>
+    <rPh sb="0" eb="1">
+      <t>アタラ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>カデン</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>デンゲン</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>イ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>ウゴ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ユーザーが増える</t>
+    <rPh sb="5" eb="6">
+      <t>フ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ソフトが安く買える</t>
+    <rPh sb="4" eb="5">
+      <t>ヤス</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>カ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>カバレッジ確保の具体例に当てはまるものを選んでください。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ウェブサイトの全ページを確認する</t>
+    <rPh sb="7" eb="8">
+      <t>ゼン</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>カクニン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>新しい機能を作る</t>
+    <rPh sb="0" eb="1">
+      <t>アタラ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>キノウ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>ツク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>リンク切れをチェックする</t>
+    <rPh sb="3" eb="4">
+      <t>ギ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>広告を作成する</t>
+    <rPh sb="0" eb="2">
+      <t>コウコク</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>サクセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>異なるブラウザでの表示を確認する</t>
+    <rPh sb="0" eb="1">
+      <t>コト</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>カクニン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>社員の人数を増やす</t>
+    <rPh sb="0" eb="2">
+      <t>シャイン</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ニンズウ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>フ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>以下の選択肢の中で、ソフトウェアテストの主要な目的として最も適切なものを選んでください</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>欠陥を発見すること</t>
+    <rPh sb="0" eb="2">
+      <t>ケッカン</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ハッケン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ソフトウェアのドキュメントを作成すること</t>
+    <rPh sb="14" eb="16">
+      <t>サクセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>開発プロセスを簡略化すること</t>
+    <rPh sb="0" eb="2">
+      <t>カイハツ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>カンリャク</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>カ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>開発者のスキルを向上させること</t>
+    <rPh sb="0" eb="3">
+      <t>カイハツシャ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>コウジョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>次のうち、典型的なソフトウェアテストの目的として最も適切なものを選んでください</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ソフトウェアのパフォーマンスを最適化するため</t>
+    <rPh sb="15" eb="18">
+      <t>サイテキカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ソフトウェアの新機能を提案するため</t>
+    <rPh sb="7" eb="10">
+      <t>シンキノウ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>テイアン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ソフトウェアの設計品質を評価するため</t>
+    <rPh sb="7" eb="9">
+      <t>セッケイ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ヒンシツ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ヒョウカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ソフトウェアのメンテナンスを容易にするため</t>
+    <rPh sb="14" eb="16">
+      <t>ヨウイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>次の記述のうち、デバッグのプロセスに該当するものとして最も適切なものを選んでください</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>欠陥の原因を特定し、修正する</t>
+    <rPh sb="0" eb="2">
+      <t>ケッカン</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ゲンイン</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>トクテイ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>シュウセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ソフトウェアの欠陥を発見する</t>
+    <rPh sb="7" eb="9">
+      <t>ケッカン</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ハッケン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>システム全体の機能を確認する</t>
+    <rPh sb="4" eb="6">
+      <t>ゼンタイ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>キノウ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>カクニン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>要件に対する適合性を評価する</t>
+    <rPh sb="0" eb="2">
+      <t>ヨウケン</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>タイ</t>
+    </rPh>
+    <rPh sb="6" eb="9">
+      <t>テキゴウセイ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ヒョウカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>デバッグとテストの違いとして、最も適切なものを選んでください</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>テストは故障の原因を解析し、デバッグはその原因を取り除く</t>
+    <rPh sb="4" eb="6">
+      <t>コショウ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ゲンイン</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>カイセキ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>ゲンイン</t>
+    </rPh>
+    <rPh sb="24" eb="25">
+      <t>ト</t>
+    </rPh>
+    <rPh sb="26" eb="27">
+      <t>ノゾ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>テストは欠陥を発見し、デバッグは故障を引き起こす</t>
+    <rPh sb="4" eb="6">
+      <t>ケッカン</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ハッケン</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>コショウ</t>
+    </rPh>
+    <rPh sb="19" eb="20">
+      <t>ヒ</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>オ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>テストは欠陥を発見し、デバッグはその原因を解析し取り除く</t>
+    <rPh sb="4" eb="6">
+      <t>ケッカン</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ハッケン</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>ゲンイン</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>カイセキ</t>
+    </rPh>
+    <rPh sb="24" eb="25">
+      <t>ト</t>
+    </rPh>
+    <rPh sb="26" eb="27">
+      <t>ノゾ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>テストとデバッグは同じプロセスであり、両方とも欠陥を発見する</t>
+    <rPh sb="9" eb="10">
+      <t>オナ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>リョウホウ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>ケッカン</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>ハッケン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>次のうち、テストとデバッグの典型的な流れの組み合わせとして、最も適切なものを選んでください</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>テスト：故障の再現→デバッグ：診断→修正</t>
+    <rPh sb="4" eb="6">
+      <t>コショウ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>サイゲン</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>シンダン</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>シュウセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>テスト：欠陥の発見→デバッグ：原因の解析→修正</t>
+    <rPh sb="4" eb="6">
+      <t>ケッカン</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ハッケン</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>ゲンイン</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>カイセキ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>シュウセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>テスト：故障の原因の解析→デバッグ：欠陥の除去→リグレッションテスト</t>
+    <rPh sb="4" eb="6">
+      <t>コショウ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ゲンイン</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>カイセキ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>ケッカン</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>ジョキョ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>テスト：欠陥の発見→デバッグ：故障の再現→リグレッションテスト</t>
+    <rPh sb="4" eb="6">
+      <t>ケッカン</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ハッケン</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>コショウ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>サイゲン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ソフトウェアテストが必要な理由として最も適切なものを選んでください</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ソフトウェアの品質を評価し、運用環境での故障リスクを低減するため</t>
+    <rPh sb="7" eb="9">
+      <t>ヒンシツ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ヒョウカ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>ウンヨウ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>カンキョウ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>コショウ</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>テイゲン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>開発者がコーディングを早く終わらせるのを助けるため</t>
+    <rPh sb="0" eb="3">
+      <t>カイハツシャ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>ハヤ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>オ</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>タス</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ソフトウェアの機能追加を行うため</t>
+    <rPh sb="7" eb="9">
+      <t>キノウ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ツイカ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>オコナ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ユーザーの要件を正確に理解するため</t>
+    <rPh sb="5" eb="7">
+      <t>ヨウケン</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>セイカク</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>リカイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>テストがソフトウェア開発において重要である理由として、最も適切なものを選んでください</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>テストはすべてのバグを取り除くために必要である</t>
+    <rPh sb="11" eb="12">
+      <t>ト</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>ノゾ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>ヒツヨウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>テストはソフトウェアの欠陥を早期に発見し、修正コストを削減するために必要である</t>
+    <rPh sb="11" eb="13">
+      <t>ケッカン</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>ソウキ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>ハッケン</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>シュウセイ</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>サクゲン</t>
+    </rPh>
+    <rPh sb="34" eb="36">
+      <t>ヒツヨウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>テストはソフトウェアの開発期間を短縮するために必要である</t>
+    <rPh sb="11" eb="13">
+      <t>カイハツ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>キカン</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>タンシュク</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>ヒツヨウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>テストは開発者の仕事を評価するために必要である</t>
+    <rPh sb="4" eb="6">
+      <t>カイハツ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>シャ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>シゴト</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ヒョウカ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>ヒツヨウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ソフトウェアのすべての問題を解決するため</t>
+    <rPh sb="11" eb="13">
+      <t>モンダイ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>カイケツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ソフトウェアの欠陥を修正し、品質向上に直接的に貢献するため</t>
+    <rPh sb="7" eb="9">
+      <t>ケッカン</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>シュウセイ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>ヒンシツ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>コウジョウ</t>
+    </rPh>
+    <rPh sb="19" eb="22">
+      <t>チョクセツテキ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>コウケン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ソフトウェアのデザインの一貫性を保つため</t>
+    <rPh sb="12" eb="15">
+      <t>イッカンセイ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>タモ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ソフトウェアが契約上または法律上の要件を満たすため</t>
+    <rPh sb="7" eb="9">
+      <t>ケイヤク</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>ジョウ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>ホウリツ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>ジョウ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>ヨウケン</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>ミ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ソフトウェアテストが品質保証（QA）にどのように関連しているかを説明するものとして、最も適切なものを選んでください</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>テストは品質コントロール（QC）の形式の一つであり、品質保証（QA）はプロセスの実装と改善に焦点を当てる</t>
+    <rPh sb="4" eb="6">
+      <t>ヒンシツ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>ケイシキ</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>ヒト</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>ヒンシツ</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>ホショウ</t>
+    </rPh>
+    <rPh sb="40" eb="42">
+      <t>ジッソウ</t>
+    </rPh>
+    <rPh sb="43" eb="45">
+      <t>カイゼン</t>
+    </rPh>
+    <rPh sb="46" eb="48">
+      <t>ショウテン</t>
+    </rPh>
+    <rPh sb="49" eb="50">
+      <t>ア</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>テストは品質保証（QA）の一部であり、ソフトウェアの機能を確認する</t>
+    <rPh sb="4" eb="6">
+      <t>ヒンシツ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ホショウ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>イチブ</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>キノウ</t>
+    </rPh>
+    <rPh sb="29" eb="31">
+      <t>カクニン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>テストと品質保証（QA）は同じものであり、両方ともソフトウェアの欠陥を発見する</t>
+    <rPh sb="4" eb="6">
+      <t>ヒンシツ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ホショウ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>オナ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>リョウホウ</t>
+    </rPh>
+    <rPh sb="32" eb="34">
+      <t>ケッカン</t>
+    </rPh>
+    <rPh sb="35" eb="37">
+      <t>ハッケン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>テストは品質コントロール（QC）の形式の一つであり、品質保証（QA）はソフトウェアの最適化に焦点を当てる</t>
+    <rPh sb="4" eb="6">
+      <t>ヒンシツ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>ケイシキ</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>ヒト</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>ヒンシツ</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>ホショウ</t>
+    </rPh>
+    <rPh sb="42" eb="45">
+      <t>サイテキカ</t>
+    </rPh>
+    <rPh sb="46" eb="48">
+      <t>ショウテン</t>
+    </rPh>
+    <rPh sb="49" eb="50">
+      <t>ア</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>品質保証（QA）と品質コントロール（QC）の違いを示す説明として最も適切なものを選んでください</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>QAはプロダクト指向であり、QCはプロセス指向である</t>
+    <rPh sb="8" eb="10">
+      <t>シコウ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>シコウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>QAとQCはどちらも同じ活動を指す</t>
+    <rPh sb="10" eb="11">
+      <t>オナ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>カツドウ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>サ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>QAは欠陥を修正する活動であり、QCはプロセスの改善に焦点を当てる</t>
+    <rPh sb="3" eb="5">
+      <t>ケッカン</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>シュウセイ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>カツドウ</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>カイゼン</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>ショウテン</t>
+    </rPh>
+    <rPh sb="30" eb="31">
+      <t>ア</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>QAはプロセス指向であり、QCはプロダクト指向である</t>
+    <rPh sb="7" eb="9">
+      <t>シコウ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>シコウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>次のうち、品質保証（QA）の役割に該当するものとして最も適切なものを選んでください</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>プロダクトの欠陥を見つけて修正すること</t>
+    <rPh sb="6" eb="8">
+      <t>ケッカン</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>ミ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>シュウセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>開発とテストプロセスが正しく行われているかを監視し改善すること</t>
+    <rPh sb="0" eb="2">
+      <t>カイハツ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>タダ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>オコナ</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>カンシ</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>カイゼン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>開発者が書いたコードの品質を評価すること</t>
+    <rPh sb="0" eb="3">
+      <t>カイハツシャ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ヒンシツ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>ヒョウカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ソフトウェアのパフォーマンスをテストすること</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>次のうち、エラー（誤り）に該当するものを選んでください</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>間違った認識で要件仕様書を作成する</t>
+    <rPh sb="0" eb="2">
+      <t>マチガ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ニンシキ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ヨウケン</t>
+    </rPh>
+    <rPh sb="9" eb="12">
+      <t>シヨウショ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>サクセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ソフトウェアが予期しない動作をする</t>
+    <rPh sb="7" eb="9">
+      <t>ヨキ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ドウサ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>コードのバグが実行される</t>
+    <rPh sb="7" eb="9">
+      <t>ジッコウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ソフトウェアの設計にミスがある</t>
+    <rPh sb="7" eb="9">
+      <t>セッケイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>次のうち、欠陥（フォールト、バグ）に該当するものを選んでください</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>プログラマが誤った認識でコードを書く</t>
+    <rPh sb="6" eb="7">
+      <t>アヤマ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ニンシキ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>カ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ソフトウェアがクラッシュする</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ユーザーが操作を誤る</t>
+    <rPh sb="5" eb="7">
+      <t>ソウサ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>アヤマ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ソースコードに存在する不具合</t>
+    <rPh sb="7" eb="9">
+      <t>ソンザイ</t>
+    </rPh>
+    <rPh sb="11" eb="14">
+      <t>フグアイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>次のうち、ソフトウェアの故障の定義として最も適切なものを選んでください</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ソフトウェアの実装が計画通りに進んでいない状態を指す</t>
+    <rPh sb="7" eb="9">
+      <t>ジッソウ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ケイカク</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>ドオ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>スス</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>ジョウタイ</t>
+    </rPh>
+    <rPh sb="24" eb="25">
+      <t>サ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ソースコードに潜在的な問題がある状態を指す</t>
+    <rPh sb="7" eb="10">
+      <t>センザイテキ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>モンダイ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>ジョウタイ</t>
+    </rPh>
+    <rPh sb="19" eb="20">
+      <t>サ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>欠陥が実行され、システムが期待された動作をしない状態を指す</t>
+    <rPh sb="0" eb="2">
+      <t>ケッカン</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ジッコウ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>キタイ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>ドウサ</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>ジョウタイ</t>
+    </rPh>
+    <rPh sb="27" eb="28">
+      <t>サ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>システムのハードウェアが物理的に破損している状態を指す</t>
+    <rPh sb="12" eb="15">
+      <t>ブツリテキ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>ハソン</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>ジョウタイ</t>
+    </rPh>
+    <rPh sb="25" eb="26">
+      <t>サ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>次のうち、根本原因分析が必要とされる理由として最も適切なものを選んでください</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>根本原因を特定することで、同様の欠陥や故障を未然に防ぐことができる</t>
+    <rPh sb="0" eb="2">
+      <t>コンポン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ゲンイン</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>トクテイ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>ドウヨウ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>ケッカン</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>コショウ</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>ミゼン</t>
+    </rPh>
+    <rPh sb="25" eb="26">
+      <t>フセ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>問題が発生した場合、すぐにシステムを再起動するため</t>
+    <rPh sb="0" eb="2">
+      <t>モンダイ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ハッセイ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="18" eb="21">
+      <t>サイキドウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ソフトウェアの設計を全面的に見直すため</t>
+    <rPh sb="7" eb="9">
+      <t>セッケイ</t>
+    </rPh>
+    <rPh sb="10" eb="13">
+      <t>ゼンメンテキ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>ミナオ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>システムが正常に動作しているかどうかを確認するため</t>
+    <rPh sb="5" eb="7">
+      <t>セイジョウ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ドウサ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>カクニン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ソフトウェアのすべての要件を徹底的にテストし、すべての欠陥を修正したにもかかわらず、ユーザーからの不満が絶えません</t>
+  </si>
+  <si>
+    <t>この現象を説明しているテストの原則について、最も適切なものを選んでください</t>
+  </si>
+  <si>
+    <t>テストの弱化</t>
+    <rPh sb="4" eb="6">
+      <t>ジャッカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>欠陥の偏在</t>
+    <rPh sb="0" eb="2">
+      <t>ケッカン</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ヘンザイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>「欠陥ゼロ」の落とし穴</t>
+    <rPh sb="1" eb="3">
+      <t>ケッカン</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>オ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>アナ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>テストはコンテキスト次第</t>
+    <rPh sb="10" eb="12">
+      <t>シダイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>「全数テストは不可能」という原則の意味として最も適切なものを選んでください</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>すべてのテストケースを実行することは現実的ではない</t>
+    <rPh sb="11" eb="13">
+      <t>ジッコウ</t>
+    </rPh>
+    <rPh sb="18" eb="21">
+      <t>ゲンジツテキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>テストはすべての入力値を試す必要がある</t>
+    <rPh sb="8" eb="11">
+      <t>ニュウリョクチ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>タメ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>ヒツヨウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>すべてのテストを1日で完了することは困難</t>
+    <rPh sb="9" eb="10">
+      <t>ニチ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>カンリョウ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>コンナン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>すべてのテストケースを自動化することは不可能</t>
+    <rPh sb="11" eb="14">
+      <t>ジドウカ</t>
+    </rPh>
+    <rPh sb="19" eb="22">
+      <t>フカノウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>「欠陥の偏在」という原則の意味として最も適切なものを選んでください</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>すべてをテストし、すべての欠陥を取り除くことは不可能</t>
+    <rPh sb="13" eb="15">
+      <t>ケッカン</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>ト</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>ノゾ</t>
+    </rPh>
+    <rPh sb="23" eb="26">
+      <t>フカノウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>欠陥は少数のモジュールやコンポーネントに集中して存在する</t>
+    <rPh sb="0" eb="2">
+      <t>ケッカン</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ショウスウ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>シュウチュウ</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>ソンザイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>同じテストを繰り返すと新たな欠陥が発見しづらくなる</t>
+    <rPh sb="0" eb="1">
+      <t>オナ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>ク</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>カエ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>アラ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>ケッカン</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>ハッケン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>欠陥をすべて修正してもユーザーのニーズを満たすとは限らない</t>
+    <rPh sb="0" eb="2">
+      <t>ケッカン</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>シュウセイ</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>ミ</t>
+    </rPh>
+    <rPh sb="25" eb="26">
+      <t>カギ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>「早期テストで時間とコストを節約」という原則に従うとき、テストのタイミングとして最も適切なものを選んでください</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>テストはすべての機能が実装された後に開始する</t>
+    <rPh sb="8" eb="10">
+      <t>キノウ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ジッソウ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>アト</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>カイシ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>テストは要件定義や設計の段階から開始する</t>
+    <rPh sb="4" eb="6">
+      <t>ヨウケン</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>テイギ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>セッケイ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ダンカイ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>カイシ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>テストは開発の完了直前に開始する</t>
+    <rPh sb="4" eb="6">
+      <t>カイハツ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>カンリョウ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>チョクゼン</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>カイシ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>テストはリリース後にユーザーからのフィードバックを受けてから開始する</t>
+    <rPh sb="8" eb="9">
+      <t>アト</t>
+    </rPh>
+    <rPh sb="25" eb="26">
+      <t>ウ</t>
+    </rPh>
+    <rPh sb="30" eb="32">
+      <t>カイシ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>新しいアプリケーションのテストで、あるプロジェクトチームはセキュリティに重点を置き、 別のチームはユーザーインターフェースに重点を置いています</t>
+  </si>
+  <si>
+    <t>異なるチームが異なる焦点を持つ理由を最もよく説明するテストの原則を選んでください</t>
+  </si>
+  <si>
+    <t>「テストの弱化」という原則の意味として最も適切なものを選んでください</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>全数テストは不可能</t>
+    <rPh sb="0" eb="2">
+      <t>ゼンスウ</t>
+    </rPh>
+    <rPh sb="6" eb="9">
+      <t>フカノウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>同じテストを繰り返すと、新しい欠陥を見つける可能性が高くなる</t>
+    <rPh sb="0" eb="1">
+      <t>オナ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>ク</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>カエ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>アタラ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>ケッカン</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>ミ</t>
+    </rPh>
+    <rPh sb="22" eb="25">
+      <t>カノウセイ</t>
+    </rPh>
+    <rPh sb="26" eb="27">
+      <t>タカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>テストケースを増やすことで、欠陥の発見確立が下がる</t>
+    <rPh sb="7" eb="8">
+      <t>フ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>ケッカン</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>ハッケン</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>カクリツ</t>
+    </rPh>
+    <rPh sb="22" eb="23">
+      <t>サ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>同じテストを繰り返すと、新しい欠陥を見つける可能性が低くなる</t>
+    <rPh sb="0" eb="1">
+      <t>オナ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>ク</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>カエ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>アタラ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>ケッカン</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>ミ</t>
+    </rPh>
+    <rPh sb="22" eb="25">
+      <t>カノウセイ</t>
+    </rPh>
+    <rPh sb="26" eb="27">
+      <t>ヒク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>テストケースを減らすことで、欠陥の発見確立が下がる</t>
+    <rPh sb="7" eb="8">
+      <t>ヘ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>ケッカン</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>ハッケン</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>カクリツ</t>
+    </rPh>
+    <rPh sb="22" eb="23">
+      <t>サ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>テスト計画の主な目的として最も適切なものを選んでください</t>
+  </si>
+  <si>
+    <t>テストの目的を定義し、最も効果的なアプローチを選択すること</t>
+    <rPh sb="4" eb="6">
+      <t>モクテキ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>テイギ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>モット</t>
+    </rPh>
+    <rPh sb="13" eb="16">
+      <t>コウカテキ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>センタク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>テストの進捗を監視し、必要に応じて調整すること</t>
+    <rPh sb="4" eb="6">
+      <t>シンチョク</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>カンシ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ヒツヨウ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>オウ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>チョウセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>テストの実行結果を記録すること</t>
+    <rPh sb="4" eb="6">
+      <t>ジッコウ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ケッカ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>キロク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>テストケースを作成すること</t>
+    <rPh sb="7" eb="9">
+      <t>サクセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>テスト実行の主なタスクとして最も適切なものを選んでください</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>テストケースの優先順位を決める</t>
+    <rPh sb="7" eb="9">
+      <t>ユウセン</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ジュンイ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>キ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>テストケースを作成する</t>
+    <rPh sb="7" eb="9">
+      <t>サクセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>テスト実行スケジュールに従ってテストを実施し、結果を記録する</t>
+    <rPh sb="3" eb="5">
+      <t>ジッコウ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>シタガ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>ジッシ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>ケッカ</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>キロク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>テスト対象の評価とリスク分析</t>
+    <rPh sb="3" eb="5">
+      <t>タイショウ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ヒョウカ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ブンセキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ソフトウェアのリリースが承認される前に、テストチームはすべてのテスト結果をレビューし、未解決の問題やリスクを関係者に報告しました</t>
+  </si>
+  <si>
+    <t>この活動として最も適切なものを選んでください</t>
+  </si>
+  <si>
+    <t>テスト設計</t>
+    <rPh sb="3" eb="5">
+      <t>セッケイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>テストのモニタリングとコントロール</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>テスト分析</t>
+    <rPh sb="3" eb="5">
+      <t>ブンセキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>テスト完了</t>
+    <rPh sb="3" eb="5">
+      <t>カンリョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ソフトウェア開発ライフサイクル（SDLC）がテストプロセスに与える影響として最も適切なものを選んでください</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>SDLCの選択により、テスト戦略やテストのタイミングが決定される</t>
+    <rPh sb="5" eb="7">
+      <t>センタク</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>センリャク</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>ケッテイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>SDLCはテストプロセスに影響を与えない</t>
+    <rPh sb="13" eb="15">
+      <t>エイキョウ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>アタ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>SDLCの選択により、テストケースの数が決まる</t>
+    <rPh sb="5" eb="7">
+      <t>センタク</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>カズ</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>キ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>SDLCはテストの実施方法に関係しない</t>
+    <rPh sb="9" eb="11">
+      <t>ジッシ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ホウホウ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>カンケイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ビジネスドメインがテストプロセスに与える影響として最も適切なものを選んでください</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ビジネスドメインにより、使用するプログラミング言語が決定される</t>
+    <rPh sb="12" eb="14">
+      <t>シヨウ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>ゲンゴ</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>ケッテイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ビジネスドメインにより、テストの重要性やリスク評価が変わる</t>
+    <rPh sb="16" eb="19">
+      <t>ジュウヨウセイ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>ヒョウカ</t>
+    </rPh>
+    <rPh sb="26" eb="27">
+      <t>カ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ビジネスドメインはテストプロセスに影響を与えない</t>
+    <rPh sb="17" eb="19">
+      <t>エイキョウ</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>アタ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ビジネスドメインにより、テスト環境の設定が決まる</t>
+    <rPh sb="15" eb="17">
+      <t>カンキョウ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>セッテイ</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>キ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>以下のうち、テストプロセスに顕著な影響を与える要因として、最も適切なものを選んでください</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ドキュメントのフォーマット</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>テストケースの数</t>
+    <rPh sb="7" eb="8">
+      <t>カズ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>テストに割り当てられる予算</t>
+    <rPh sb="4" eb="5">
+      <t>ワ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ヨサン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>テスト実行の時間帯</t>
+    <rPh sb="3" eb="5">
+      <t>ジッコウ</t>
+    </rPh>
+    <rPh sb="6" eb="9">
+      <t>ジカンタイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>テスト設計の過程で作成される作業成果物として最も適切なものを選んでください</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>テストケース</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>欠陥レポート</t>
+    <rPh sb="0" eb="2">
+      <t>ケッカン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>テスト完了レポート</t>
+    <rPh sb="3" eb="5">
+      <t>カンリョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>テスト計画フェーズで作成される成果物として最も適切なものを選んでください</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>テストスクリプト</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>リスクレジスター</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>成果物として「優先順位を付けたテスト条件」が生成されるテストプロセスは次のうちどれか、最も適切なものを選んでください</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>テスト計画</t>
+    <rPh sb="3" eb="5">
+      <t>ケイカク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>トレーサビリティを維持することによる利点として最も適切なものを選んでください</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>新しいバージョンのリリース時にテスト計画が不要になる</t>
+    <rPh sb="0" eb="1">
+      <t>アタラ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>ジ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>ケイカク</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>フヨウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>要件がすべてテストされていることを確認できる</t>
+    <rPh sb="0" eb="2">
+      <t>ヨウケン</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>カクニン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>テストの実行速度が向上する</t>
+    <rPh sb="4" eb="6">
+      <t>ジッコウ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ソクド</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>コウジョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>テスト環境のセットアップが簡単になる</t>
+    <rPh sb="3" eb="5">
+      <t>カンキョウ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>カンタン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>トレーサビリティを維持することの価値として、最も適切なものを選んでください</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>要件変更による影響範囲を迅速に把握できるようになる</t>
+    <rPh sb="0" eb="2">
+      <t>ヨウケン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ヘンコウ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>エイキョウ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ハンイ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ジンソク</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>ハアク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>プロジェクトの進捗を迅速に確認できるようになる</t>
+    <rPh sb="7" eb="9">
+      <t>シンチョク</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ジンソク</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>カクニン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>欠陥レポートの作成プロセスを簡素化する</t>
+    <rPh sb="0" eb="2">
+      <t>ケッカン</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>サクセイ</t>
+    </rPh>
+    <rPh sb="14" eb="17">
+      <t>カンソカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>開発者がコード最適化を行うためのガイドラインを提供する</t>
+    <rPh sb="0" eb="3">
+      <t>カイハツシャ</t>
+    </rPh>
+    <rPh sb="7" eb="10">
+      <t>サイテキカ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>オコナ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>テイキョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>トレーサビリティがテストプロセス全体に与える影響として最も適切なものを選んでください</t>
+    <rPh sb="16" eb="18">
+      <t>ゼンタイ</t>
+    </rPh>
+    <rPh sb="19" eb="20">
+      <t>アタ</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>エイキョウ</t>
+    </rPh>
+    <rPh sb="27" eb="28">
+      <t>モット</t>
+    </rPh>
+    <rPh sb="29" eb="31">
+      <t>テキセツ</t>
+    </rPh>
+    <rPh sb="35" eb="36">
+      <t>エラ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>テストケースの作成を簡素化する</t>
+    <rPh sb="7" eb="9">
+      <t>サクセイ</t>
+    </rPh>
+    <rPh sb="10" eb="13">
+      <t>カンソカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>テストの実行を迅速にする</t>
+    <rPh sb="4" eb="6">
+      <t>ジッコウ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ジンソク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>テストデータの生成を自動化する</t>
+    <rPh sb="7" eb="9">
+      <t>セイセイ</t>
+    </rPh>
+    <rPh sb="10" eb="13">
+      <t>ジドウカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>テストのカバレッジを評価しやすくする</t>
+    <rPh sb="10" eb="12">
+      <t>ヒョウカ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -1610,9 +3803,9 @@
   <dimension ref="B2:J244"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
-    <col min="2" max="3" width="3.296875" customWidth="1"/>
-    <col min="4" max="4" width="85.3984375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.19921875" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="3.33203125" customWidth="1"/>
+    <col min="4" max="4" width="85.4140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:10">
@@ -3939,9 +6132,9 @@
   <dimension ref="B2:L68"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
-    <col min="2" max="3" width="3.296875" customWidth="1"/>
-    <col min="4" max="4" width="85.3984375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="10.19921875" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="3.33203125" customWidth="1"/>
+    <col min="4" max="4" width="85.4140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:12">
@@ -4419,17 +6612,17 @@
   <dimension ref="B2:R108"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
-    <col min="5" max="5" width="8.69921875" hidden="1" customWidth="1"/>
-    <col min="6" max="6" width="10.19921875" hidden="1" customWidth="1"/>
-    <col min="7" max="7" width="8.69921875" customWidth="1"/>
+    <col min="5" max="5" width="8.6640625" hidden="1" customWidth="1"/>
+    <col min="6" max="6" width="10.1640625" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="8.6640625" customWidth="1"/>
     <col min="8" max="8" width="0" hidden="1" customWidth="1"/>
-    <col min="9" max="9" width="10.19921875" hidden="1" customWidth="1"/>
+    <col min="9" max="9" width="10.1640625" hidden="1" customWidth="1"/>
     <col min="10" max="10" width="0" hidden="1" customWidth="1"/>
-    <col min="11" max="11" width="8.796875" hidden="1" customWidth="1"/>
-    <col min="12" max="12" width="10.19921875" hidden="1" customWidth="1"/>
-    <col min="14" max="14" width="8.796875" hidden="1" customWidth="1"/>
-    <col min="15" max="15" width="10.19921875" hidden="1" customWidth="1"/>
-    <col min="18" max="18" width="10.19921875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="8.83203125" hidden="1" customWidth="1"/>
+    <col min="12" max="12" width="10.1640625" hidden="1" customWidth="1"/>
+    <col min="14" max="14" width="8.83203125" hidden="1" customWidth="1"/>
+    <col min="15" max="15" width="10.1640625" hidden="1" customWidth="1"/>
+    <col min="18" max="18" width="10.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:18">
@@ -6585,7 +8778,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D31F101-46C1-44B2-8ACA-D9FBA0843003}">
-  <dimension ref="B2:D15"/>
+  <dimension ref="B2:D50"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <sheetData>
     <row r="2" spans="2:4">
@@ -6698,6 +8891,286 @@
       </c>
       <c r="D15" t="s">
         <v>271</v>
+      </c>
+    </row>
+    <row r="16" spans="2:4">
+      <c r="B16">
+        <v>3</v>
+      </c>
+      <c r="C16" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="17" spans="2:4">
+      <c r="C17" t="s">
+        <v>10</v>
+      </c>
+      <c r="D17" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="18" spans="2:4">
+      <c r="C18" t="s">
+        <v>9</v>
+      </c>
+      <c r="D18" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="19" spans="2:4">
+      <c r="C19" t="s">
+        <v>11</v>
+      </c>
+      <c r="D19" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="20" spans="2:4">
+      <c r="C20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D20" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="21" spans="2:4">
+      <c r="C21" t="s">
+        <v>257</v>
+      </c>
+      <c r="D21" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="22" spans="2:4">
+      <c r="C22" t="s">
+        <v>258</v>
+      </c>
+      <c r="D22" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="23" spans="2:4">
+      <c r="B23">
+        <v>4</v>
+      </c>
+      <c r="C23" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="24" spans="2:4">
+      <c r="C24" t="s">
+        <v>10</v>
+      </c>
+      <c r="D24" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="25" spans="2:4">
+      <c r="C25" t="s">
+        <v>9</v>
+      </c>
+      <c r="D25" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="26" spans="2:4">
+      <c r="C26" t="s">
+        <v>11</v>
+      </c>
+      <c r="D26" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="27" spans="2:4">
+      <c r="C27" t="s">
+        <v>12</v>
+      </c>
+      <c r="D27" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="28" spans="2:4">
+      <c r="C28" t="s">
+        <v>257</v>
+      </c>
+      <c r="D28" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="29" spans="2:4">
+      <c r="C29" t="s">
+        <v>258</v>
+      </c>
+      <c r="D29" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="30" spans="2:4">
+      <c r="B30">
+        <v>5</v>
+      </c>
+      <c r="C30" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="31" spans="2:4">
+      <c r="C31" t="s">
+        <v>10</v>
+      </c>
+      <c r="D31" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="32" spans="2:4">
+      <c r="C32" t="s">
+        <v>9</v>
+      </c>
+      <c r="D32" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="33" spans="2:4">
+      <c r="C33" t="s">
+        <v>11</v>
+      </c>
+      <c r="D33" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="34" spans="2:4">
+      <c r="C34" t="s">
+        <v>12</v>
+      </c>
+      <c r="D34" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="35" spans="2:4">
+      <c r="C35" t="s">
+        <v>257</v>
+      </c>
+      <c r="D35" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="36" spans="2:4">
+      <c r="C36" t="s">
+        <v>258</v>
+      </c>
+      <c r="D36" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="37" spans="2:4">
+      <c r="B37">
+        <v>6</v>
+      </c>
+      <c r="C37" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="38" spans="2:4">
+      <c r="C38" t="s">
+        <v>10</v>
+      </c>
+      <c r="D38" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="39" spans="2:4">
+      <c r="C39" t="s">
+        <v>9</v>
+      </c>
+      <c r="D39" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="40" spans="2:4">
+      <c r="C40" t="s">
+        <v>11</v>
+      </c>
+      <c r="D40" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="41" spans="2:4">
+      <c r="C41" t="s">
+        <v>12</v>
+      </c>
+      <c r="D41" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="42" spans="2:4">
+      <c r="C42" t="s">
+        <v>257</v>
+      </c>
+      <c r="D42" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="43" spans="2:4">
+      <c r="C43" t="s">
+        <v>258</v>
+      </c>
+      <c r="D43" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="44" spans="2:4">
+      <c r="B44">
+        <v>7</v>
+      </c>
+      <c r="C44" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="45" spans="2:4">
+      <c r="C45" t="s">
+        <v>10</v>
+      </c>
+      <c r="D45" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="46" spans="2:4">
+      <c r="C46" t="s">
+        <v>9</v>
+      </c>
+      <c r="D46" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="47" spans="2:4">
+      <c r="C47" t="s">
+        <v>11</v>
+      </c>
+      <c r="D47" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="48" spans="2:4">
+      <c r="C48" t="s">
+        <v>12</v>
+      </c>
+      <c r="D48" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="49" spans="3:4">
+      <c r="C49" t="s">
+        <v>257</v>
+      </c>
+      <c r="D49" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="50" spans="3:4">
+      <c r="C50" t="s">
+        <v>258</v>
+      </c>
+      <c r="D50" t="s">
+        <v>311</v>
       </c>
     </row>
   </sheetData>
@@ -6708,7 +9181,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4F9E86CE-0C54-4910-857C-CE213AABC91E}">
-  <dimension ref="B2:C4"/>
+  <dimension ref="B2:C20"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <sheetData>
     <row r="2" spans="2:3">
@@ -6726,6 +9199,104 @@
     </row>
     <row r="4" spans="2:3">
       <c r="C4" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="5" spans="2:3">
+      <c r="B5">
+        <v>2</v>
+      </c>
+      <c r="C5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="2:3">
+      <c r="C6" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" spans="2:3">
+      <c r="C7" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="8" spans="2:3">
+      <c r="B8">
+        <v>3</v>
+      </c>
+      <c r="C8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9" spans="2:3">
+      <c r="C9" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="10" spans="2:3">
+      <c r="B10">
+        <v>4</v>
+      </c>
+      <c r="C10" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="2:3">
+      <c r="C11" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="12" spans="2:3">
+      <c r="C12" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="13" spans="2:3">
+      <c r="B13">
+        <v>5</v>
+      </c>
+      <c r="C13" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14" spans="2:3">
+      <c r="C14" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="15" spans="2:3">
+      <c r="C15" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="16" spans="2:3">
+      <c r="B16">
+        <v>6</v>
+      </c>
+      <c r="C16" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="17" spans="2:3">
+      <c r="C17" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="18" spans="2:3">
+      <c r="B18">
+        <v>7</v>
+      </c>
+      <c r="C18" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="19" spans="2:3">
+      <c r="C19" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="20" spans="2:3">
+      <c r="C20" t="s">
         <v>257</v>
       </c>
     </row>
@@ -6737,7 +9308,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3484731F-D563-4573-BC0F-79D78D330990}">
-  <dimension ref="B2:D6"/>
+  <dimension ref="B2:D174"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <sheetData>
     <row r="2" spans="2:4">
@@ -6778,6 +9349,1341 @@
       </c>
       <c r="D6" t="s">
         <v>276</v>
+      </c>
+    </row>
+    <row r="7" spans="2:4">
+      <c r="B7">
+        <v>2</v>
+      </c>
+      <c r="C7" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="8" spans="2:4">
+      <c r="C8" t="s">
+        <v>10</v>
+      </c>
+      <c r="D8" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="9" spans="2:4">
+      <c r="C9" t="s">
+        <v>9</v>
+      </c>
+      <c r="D9" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="10" spans="2:4">
+      <c r="C10" t="s">
+        <v>11</v>
+      </c>
+      <c r="D10" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="11" spans="2:4">
+      <c r="C11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D11" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="12" spans="2:4">
+      <c r="B12">
+        <v>3</v>
+      </c>
+      <c r="C12" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="13" spans="2:4">
+      <c r="C13" t="s">
+        <v>10</v>
+      </c>
+      <c r="D13" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="14" spans="2:4">
+      <c r="C14" t="s">
+        <v>9</v>
+      </c>
+      <c r="D14" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="15" spans="2:4">
+      <c r="C15" t="s">
+        <v>11</v>
+      </c>
+      <c r="D15" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="16" spans="2:4">
+      <c r="C16" t="s">
+        <v>12</v>
+      </c>
+      <c r="D16" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="17" spans="2:4">
+      <c r="B17">
+        <v>4</v>
+      </c>
+      <c r="C17" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="18" spans="2:4">
+      <c r="C18" t="s">
+        <v>10</v>
+      </c>
+      <c r="D18" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="19" spans="2:4">
+      <c r="C19" t="s">
+        <v>9</v>
+      </c>
+      <c r="D19" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="20" spans="2:4">
+      <c r="C20" t="s">
+        <v>11</v>
+      </c>
+      <c r="D20" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="21" spans="2:4">
+      <c r="C21" t="s">
+        <v>12</v>
+      </c>
+      <c r="D21" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="22" spans="2:4">
+      <c r="B22">
+        <v>5</v>
+      </c>
+      <c r="C22" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="23" spans="2:4">
+      <c r="C23" t="s">
+        <v>10</v>
+      </c>
+      <c r="D23" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="24" spans="2:4">
+      <c r="C24" t="s">
+        <v>9</v>
+      </c>
+      <c r="D24" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="25" spans="2:4">
+      <c r="C25" t="s">
+        <v>11</v>
+      </c>
+      <c r="D25" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="26" spans="2:4">
+      <c r="C26" t="s">
+        <v>12</v>
+      </c>
+      <c r="D26" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="27" spans="2:4">
+      <c r="B27">
+        <v>6</v>
+      </c>
+      <c r="C27" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="28" spans="2:4">
+      <c r="C28" t="s">
+        <v>10</v>
+      </c>
+      <c r="D28" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="29" spans="2:4">
+      <c r="C29" t="s">
+        <v>9</v>
+      </c>
+      <c r="D29" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="30" spans="2:4">
+      <c r="C30" t="s">
+        <v>11</v>
+      </c>
+      <c r="D30" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="31" spans="2:4">
+      <c r="C31" t="s">
+        <v>12</v>
+      </c>
+      <c r="D31" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="32" spans="2:4">
+      <c r="B32">
+        <v>7</v>
+      </c>
+      <c r="C32" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="33" spans="2:4">
+      <c r="C33" t="s">
+        <v>10</v>
+      </c>
+      <c r="D33" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="34" spans="2:4">
+      <c r="C34" t="s">
+        <v>9</v>
+      </c>
+      <c r="D34" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="35" spans="2:4">
+      <c r="C35" t="s">
+        <v>11</v>
+      </c>
+      <c r="D35" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="36" spans="2:4">
+      <c r="C36" t="s">
+        <v>12</v>
+      </c>
+      <c r="D36" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="37" spans="2:4">
+      <c r="B37">
+        <v>8</v>
+      </c>
+      <c r="C37" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="38" spans="2:4">
+      <c r="C38" t="s">
+        <v>10</v>
+      </c>
+      <c r="D38" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="39" spans="2:4">
+      <c r="C39" t="s">
+        <v>9</v>
+      </c>
+      <c r="D39" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="40" spans="2:4">
+      <c r="C40" t="s">
+        <v>11</v>
+      </c>
+      <c r="D40" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="41" spans="2:4">
+      <c r="C41" t="s">
+        <v>12</v>
+      </c>
+      <c r="D41" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="42" spans="2:4">
+      <c r="B42">
+        <v>9</v>
+      </c>
+      <c r="C42" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="43" spans="2:4">
+      <c r="C43" t="s">
+        <v>10</v>
+      </c>
+      <c r="D43" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="44" spans="2:4">
+      <c r="C44" t="s">
+        <v>9</v>
+      </c>
+      <c r="D44" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="45" spans="2:4">
+      <c r="C45" t="s">
+        <v>11</v>
+      </c>
+      <c r="D45" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="46" spans="2:4">
+      <c r="C46" t="s">
+        <v>12</v>
+      </c>
+      <c r="D46" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="47" spans="2:4">
+      <c r="B47">
+        <v>10</v>
+      </c>
+      <c r="C47" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="48" spans="2:4">
+      <c r="C48" t="s">
+        <v>10</v>
+      </c>
+      <c r="D48" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="49" spans="2:4">
+      <c r="C49" t="s">
+        <v>9</v>
+      </c>
+      <c r="D49" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="50" spans="2:4">
+      <c r="C50" t="s">
+        <v>11</v>
+      </c>
+      <c r="D50" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="51" spans="2:4">
+      <c r="C51" t="s">
+        <v>12</v>
+      </c>
+      <c r="D51" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="52" spans="2:4">
+      <c r="B52">
+        <v>11</v>
+      </c>
+      <c r="C52" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="53" spans="2:4">
+      <c r="C53" t="s">
+        <v>10</v>
+      </c>
+      <c r="D53" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="54" spans="2:4">
+      <c r="C54" t="s">
+        <v>9</v>
+      </c>
+      <c r="D54" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="55" spans="2:4">
+      <c r="C55" t="s">
+        <v>11</v>
+      </c>
+      <c r="D55" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="56" spans="2:4">
+      <c r="C56" t="s">
+        <v>12</v>
+      </c>
+      <c r="D56" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="57" spans="2:4">
+      <c r="B57">
+        <v>12</v>
+      </c>
+      <c r="C57" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="58" spans="2:4">
+      <c r="C58" t="s">
+        <v>10</v>
+      </c>
+      <c r="D58" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="59" spans="2:4">
+      <c r="C59" t="s">
+        <v>9</v>
+      </c>
+      <c r="D59" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="60" spans="2:4">
+      <c r="C60" t="s">
+        <v>11</v>
+      </c>
+      <c r="D60" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="61" spans="2:4">
+      <c r="C61" t="s">
+        <v>12</v>
+      </c>
+      <c r="D61" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="62" spans="2:4">
+      <c r="B62">
+        <v>13</v>
+      </c>
+      <c r="C62" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="63" spans="2:4">
+      <c r="C63" t="s">
+        <v>10</v>
+      </c>
+      <c r="D63" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="64" spans="2:4">
+      <c r="C64" t="s">
+        <v>9</v>
+      </c>
+      <c r="D64" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="65" spans="2:4">
+      <c r="C65" t="s">
+        <v>11</v>
+      </c>
+      <c r="D65" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="66" spans="2:4">
+      <c r="C66" t="s">
+        <v>12</v>
+      </c>
+      <c r="D66" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="67" spans="2:4">
+      <c r="B67">
+        <v>14</v>
+      </c>
+      <c r="C67" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="68" spans="2:4">
+      <c r="C68" t="s">
+        <v>10</v>
+      </c>
+      <c r="D68" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="69" spans="2:4">
+      <c r="C69" t="s">
+        <v>9</v>
+      </c>
+      <c r="D69" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="70" spans="2:4">
+      <c r="C70" t="s">
+        <v>11</v>
+      </c>
+      <c r="D70" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="71" spans="2:4">
+      <c r="C71" t="s">
+        <v>12</v>
+      </c>
+      <c r="D71" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="72" spans="2:4">
+      <c r="B72">
+        <v>15</v>
+      </c>
+      <c r="C72" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="73" spans="2:4">
+      <c r="C73" t="s">
+        <v>10</v>
+      </c>
+      <c r="D73" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="74" spans="2:4">
+      <c r="C74" t="s">
+        <v>9</v>
+      </c>
+      <c r="D74" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="75" spans="2:4">
+      <c r="C75" t="s">
+        <v>11</v>
+      </c>
+      <c r="D75" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="76" spans="2:4">
+      <c r="C76" t="s">
+        <v>12</v>
+      </c>
+      <c r="D76" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="77" spans="2:4">
+      <c r="B77">
+        <v>16</v>
+      </c>
+      <c r="C77" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="78" spans="2:4">
+      <c r="C78" t="s">
+        <v>10</v>
+      </c>
+      <c r="D78" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="79" spans="2:4">
+      <c r="C79" t="s">
+        <v>9</v>
+      </c>
+      <c r="D79" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="80" spans="2:4">
+      <c r="C80" t="s">
+        <v>11</v>
+      </c>
+      <c r="D80" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="81" spans="2:4">
+      <c r="C81" t="s">
+        <v>12</v>
+      </c>
+      <c r="D81" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="82" spans="2:4">
+      <c r="B82">
+        <v>17</v>
+      </c>
+      <c r="C82" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="83" spans="2:4">
+      <c r="C83" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="84" spans="2:4">
+      <c r="C84" t="s">
+        <v>10</v>
+      </c>
+      <c r="D84" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="85" spans="2:4">
+      <c r="C85" t="s">
+        <v>9</v>
+      </c>
+      <c r="D85" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="86" spans="2:4">
+      <c r="C86" t="s">
+        <v>11</v>
+      </c>
+      <c r="D86" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="87" spans="2:4">
+      <c r="C87" t="s">
+        <v>12</v>
+      </c>
+      <c r="D87" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="88" spans="2:4">
+      <c r="B88">
+        <v>18</v>
+      </c>
+      <c r="C88" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="89" spans="2:4">
+      <c r="C89" t="s">
+        <v>10</v>
+      </c>
+      <c r="D89" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="90" spans="2:4">
+      <c r="C90" t="s">
+        <v>9</v>
+      </c>
+      <c r="D90" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="91" spans="2:4">
+      <c r="C91" t="s">
+        <v>11</v>
+      </c>
+      <c r="D91" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="92" spans="2:4">
+      <c r="C92" t="s">
+        <v>12</v>
+      </c>
+      <c r="D92" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="93" spans="2:4">
+      <c r="B93">
+        <v>19</v>
+      </c>
+      <c r="C93" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="94" spans="2:4">
+      <c r="C94" t="s">
+        <v>10</v>
+      </c>
+      <c r="D94" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="95" spans="2:4">
+      <c r="C95" t="s">
+        <v>9</v>
+      </c>
+      <c r="D95" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="96" spans="2:4">
+      <c r="C96" t="s">
+        <v>11</v>
+      </c>
+      <c r="D96" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="97" spans="2:4">
+      <c r="C97" t="s">
+        <v>12</v>
+      </c>
+      <c r="D97" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="98" spans="2:4">
+      <c r="B98">
+        <v>20</v>
+      </c>
+      <c r="C98" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="99" spans="2:4">
+      <c r="C99" t="s">
+        <v>10</v>
+      </c>
+      <c r="D99" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="100" spans="2:4">
+      <c r="C100" t="s">
+        <v>9</v>
+      </c>
+      <c r="D100" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="101" spans="2:4">
+      <c r="C101" t="s">
+        <v>11</v>
+      </c>
+      <c r="D101" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="102" spans="2:4">
+      <c r="C102" t="s">
+        <v>12</v>
+      </c>
+      <c r="D102" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="103" spans="2:4">
+      <c r="B103">
+        <v>21</v>
+      </c>
+      <c r="C103" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="104" spans="2:4">
+      <c r="C104" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="105" spans="2:4">
+      <c r="C105" t="s">
+        <v>10</v>
+      </c>
+      <c r="D105" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="106" spans="2:4">
+      <c r="C106" t="s">
+        <v>9</v>
+      </c>
+      <c r="D106" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="107" spans="2:4">
+      <c r="C107" t="s">
+        <v>11</v>
+      </c>
+      <c r="D107" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="108" spans="2:4">
+      <c r="C108" t="s">
+        <v>12</v>
+      </c>
+      <c r="D108" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="109" spans="2:4">
+      <c r="B109">
+        <v>22</v>
+      </c>
+      <c r="C109" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="110" spans="2:4">
+      <c r="C110" t="s">
+        <v>10</v>
+      </c>
+      <c r="D110" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="111" spans="2:4">
+      <c r="C111" t="s">
+        <v>9</v>
+      </c>
+      <c r="D111" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="112" spans="2:4">
+      <c r="C112" t="s">
+        <v>11</v>
+      </c>
+      <c r="D112" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="113" spans="2:4">
+      <c r="C113" t="s">
+        <v>12</v>
+      </c>
+      <c r="D113" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="114" spans="2:4">
+      <c r="B114">
+        <v>23</v>
+      </c>
+      <c r="C114" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="115" spans="2:4">
+      <c r="C115" t="s">
+        <v>10</v>
+      </c>
+      <c r="D115" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="116" spans="2:4">
+      <c r="C116" t="s">
+        <v>9</v>
+      </c>
+      <c r="D116" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="117" spans="2:4">
+      <c r="C117" t="s">
+        <v>11</v>
+      </c>
+      <c r="D117" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="118" spans="2:4">
+      <c r="C118" t="s">
+        <v>12</v>
+      </c>
+      <c r="D118" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="119" spans="2:4">
+      <c r="B119">
+        <v>24</v>
+      </c>
+      <c r="C119" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="120" spans="2:4">
+      <c r="C120" t="s">
+        <v>10</v>
+      </c>
+      <c r="D120" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="121" spans="2:4">
+      <c r="C121" t="s">
+        <v>9</v>
+      </c>
+      <c r="D121" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="122" spans="2:4">
+      <c r="C122" t="s">
+        <v>11</v>
+      </c>
+      <c r="D122" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="123" spans="2:4">
+      <c r="C123" t="s">
+        <v>12</v>
+      </c>
+      <c r="D123" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="124" spans="2:4">
+      <c r="B124">
+        <v>25</v>
+      </c>
+      <c r="C124" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="125" spans="2:4">
+      <c r="C125" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="126" spans="2:4">
+      <c r="C126" t="s">
+        <v>10</v>
+      </c>
+      <c r="D126" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="127" spans="2:4">
+      <c r="C127" t="s">
+        <v>9</v>
+      </c>
+      <c r="D127" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="128" spans="2:4">
+      <c r="C128" t="s">
+        <v>11</v>
+      </c>
+      <c r="D128" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="129" spans="2:4">
+      <c r="C129" t="s">
+        <v>12</v>
+      </c>
+      <c r="D129" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="130" spans="2:4">
+      <c r="B130">
+        <v>26</v>
+      </c>
+      <c r="C130" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="131" spans="2:4">
+      <c r="C131" t="s">
+        <v>10</v>
+      </c>
+      <c r="D131" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="132" spans="2:4">
+      <c r="C132" t="s">
+        <v>9</v>
+      </c>
+      <c r="D132" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="133" spans="2:4">
+      <c r="C133" t="s">
+        <v>11</v>
+      </c>
+      <c r="D133" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="134" spans="2:4">
+      <c r="C134" t="s">
+        <v>12</v>
+      </c>
+      <c r="D134" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="135" spans="2:4">
+      <c r="B135">
+        <v>27</v>
+      </c>
+      <c r="C135" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="136" spans="2:4">
+      <c r="C136" t="s">
+        <v>10</v>
+      </c>
+      <c r="D136" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="137" spans="2:4">
+      <c r="C137" t="s">
+        <v>9</v>
+      </c>
+      <c r="D137" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="138" spans="2:4">
+      <c r="C138" t="s">
+        <v>11</v>
+      </c>
+      <c r="D138" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="139" spans="2:4">
+      <c r="C139" t="s">
+        <v>12</v>
+      </c>
+      <c r="D139" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="140" spans="2:4">
+      <c r="B140">
+        <v>28</v>
+      </c>
+      <c r="C140" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="141" spans="2:4">
+      <c r="C141" t="s">
+        <v>10</v>
+      </c>
+      <c r="D141" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="142" spans="2:4">
+      <c r="C142" t="s">
+        <v>9</v>
+      </c>
+      <c r="D142" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="143" spans="2:4">
+      <c r="C143" t="s">
+        <v>11</v>
+      </c>
+      <c r="D143" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="144" spans="2:4">
+      <c r="C144" t="s">
+        <v>12</v>
+      </c>
+      <c r="D144" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="145" spans="2:4">
+      <c r="B145">
+        <v>29</v>
+      </c>
+      <c r="C145" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="146" spans="2:4">
+      <c r="C146" t="s">
+        <v>10</v>
+      </c>
+      <c r="D146" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="147" spans="2:4">
+      <c r="C147" t="s">
+        <v>9</v>
+      </c>
+      <c r="D147" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="148" spans="2:4">
+      <c r="C148" t="s">
+        <v>11</v>
+      </c>
+      <c r="D148" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="149" spans="2:4">
+      <c r="C149" t="s">
+        <v>12</v>
+      </c>
+      <c r="D149" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="150" spans="2:4">
+      <c r="B150">
+        <v>30</v>
+      </c>
+      <c r="C150" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="151" spans="2:4">
+      <c r="C151" t="s">
+        <v>10</v>
+      </c>
+      <c r="D151" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="152" spans="2:4">
+      <c r="C152" t="s">
+        <v>9</v>
+      </c>
+      <c r="D152" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="153" spans="2:4">
+      <c r="C153" t="s">
+        <v>11</v>
+      </c>
+      <c r="D153" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="154" spans="2:4">
+      <c r="C154" t="s">
+        <v>12</v>
+      </c>
+      <c r="D154" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="155" spans="2:4">
+      <c r="B155">
+        <v>31</v>
+      </c>
+      <c r="C155" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="156" spans="2:4">
+      <c r="C156" t="s">
+        <v>10</v>
+      </c>
+      <c r="D156" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="157" spans="2:4">
+      <c r="C157" t="s">
+        <v>9</v>
+      </c>
+      <c r="D157" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="158" spans="2:4">
+      <c r="C158" t="s">
+        <v>11</v>
+      </c>
+      <c r="D158" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="159" spans="2:4">
+      <c r="C159" t="s">
+        <v>12</v>
+      </c>
+      <c r="D159" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="160" spans="2:4">
+      <c r="B160">
+        <v>32</v>
+      </c>
+      <c r="C160" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="161" spans="2:4">
+      <c r="C161" t="s">
+        <v>10</v>
+      </c>
+      <c r="D161" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="162" spans="2:4">
+      <c r="C162" t="s">
+        <v>9</v>
+      </c>
+      <c r="D162" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="163" spans="2:4">
+      <c r="C163" t="s">
+        <v>11</v>
+      </c>
+      <c r="D163" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="164" spans="2:4">
+      <c r="C164" t="s">
+        <v>12</v>
+      </c>
+      <c r="D164" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="165" spans="2:4">
+      <c r="B165">
+        <v>33</v>
+      </c>
+      <c r="C165" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="166" spans="2:4">
+      <c r="C166" t="s">
+        <v>10</v>
+      </c>
+      <c r="D166" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="167" spans="2:4">
+      <c r="C167" t="s">
+        <v>9</v>
+      </c>
+      <c r="D167" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="168" spans="2:4">
+      <c r="C168" t="s">
+        <v>11</v>
+      </c>
+      <c r="D168" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="169" spans="2:4">
+      <c r="C169" t="s">
+        <v>12</v>
+      </c>
+      <c r="D169" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="170" spans="2:4">
+      <c r="B170">
+        <v>34</v>
+      </c>
+      <c r="C170" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="171" spans="2:4">
+      <c r="C171" t="s">
+        <v>10</v>
+      </c>
+      <c r="D171" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="172" spans="2:4">
+      <c r="C172" t="s">
+        <v>9</v>
+      </c>
+      <c r="D172" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="173" spans="2:4">
+      <c r="C173" t="s">
+        <v>11</v>
+      </c>
+      <c r="D173" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="174" spans="2:4">
+      <c r="C174" t="s">
+        <v>12</v>
+      </c>
+      <c r="D174" t="s">
+        <v>469</v>
       </c>
     </row>
   </sheetData>
@@ -6788,7 +10694,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{620A70BD-F03C-4EB8-A732-46147BB70A88}">
-  <dimension ref="B2:C2"/>
+  <dimension ref="B2:C104"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <sheetData>
     <row r="2" spans="2:3">
@@ -6799,8 +10705,618 @@
         <v>9</v>
       </c>
     </row>
+    <row r="3" spans="2:3">
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="2:3">
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="2:3">
+      <c r="B5">
+        <v>4</v>
+      </c>
+      <c r="C5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="2:3">
+      <c r="B6">
+        <v>5</v>
+      </c>
+      <c r="C6" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" spans="2:3">
+      <c r="B7">
+        <v>6</v>
+      </c>
+      <c r="C7" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" spans="2:3">
+      <c r="B8">
+        <v>7</v>
+      </c>
+      <c r="C8" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="2:3">
+      <c r="B9">
+        <v>8</v>
+      </c>
+      <c r="C9" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" spans="2:3">
+      <c r="B10">
+        <v>9</v>
+      </c>
+      <c r="C10" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="2:3">
+      <c r="B11">
+        <v>10</v>
+      </c>
+      <c r="C11" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="2:3">
+      <c r="B12">
+        <v>11</v>
+      </c>
+      <c r="C12" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="13" spans="2:3">
+      <c r="B13">
+        <v>12</v>
+      </c>
+      <c r="C13" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="14" spans="2:3">
+      <c r="B14">
+        <v>13</v>
+      </c>
+      <c r="C14" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="15" spans="2:3">
+      <c r="B15">
+        <v>14</v>
+      </c>
+      <c r="C15" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16" spans="2:3">
+      <c r="B16">
+        <v>15</v>
+      </c>
+      <c r="C16" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="17" spans="2:3">
+      <c r="B17">
+        <v>16</v>
+      </c>
+      <c r="C17" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="18" spans="2:3">
+      <c r="B18">
+        <v>17</v>
+      </c>
+      <c r="C18" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="19" spans="2:3">
+      <c r="B19">
+        <v>18</v>
+      </c>
+      <c r="C19" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="20" spans="2:3">
+      <c r="B20">
+        <v>19</v>
+      </c>
+      <c r="C20" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="21" spans="2:3">
+      <c r="B21">
+        <v>20</v>
+      </c>
+      <c r="C21" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="22" spans="2:3">
+      <c r="B22">
+        <v>21</v>
+      </c>
+      <c r="C22" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="23" spans="2:3">
+      <c r="B23">
+        <v>22</v>
+      </c>
+      <c r="C23" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="24" spans="2:3">
+      <c r="B24">
+        <v>23</v>
+      </c>
+      <c r="C24" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="25" spans="2:3">
+      <c r="B25">
+        <v>24</v>
+      </c>
+      <c r="C25" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="26" spans="2:3">
+      <c r="B26">
+        <v>25</v>
+      </c>
+      <c r="C26" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="27" spans="2:3">
+      <c r="B27">
+        <v>26</v>
+      </c>
+      <c r="C27" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="28" spans="2:3">
+      <c r="B28">
+        <v>27</v>
+      </c>
+      <c r="C28" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="29" spans="2:3">
+      <c r="B29">
+        <v>28</v>
+      </c>
+      <c r="C29" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="30" spans="2:3">
+      <c r="B30">
+        <v>29</v>
+      </c>
+      <c r="C30" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="31" spans="2:3">
+      <c r="B31">
+        <v>30</v>
+      </c>
+      <c r="C31" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="32" spans="2:3">
+      <c r="B32">
+        <v>31</v>
+      </c>
+      <c r="C32" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="33" spans="2:3">
+      <c r="B33">
+        <v>32</v>
+      </c>
+      <c r="C33" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="34" spans="2:3">
+      <c r="B34">
+        <v>33</v>
+      </c>
+      <c r="C34" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="35" spans="2:3">
+      <c r="B35">
+        <v>34</v>
+      </c>
+      <c r="C35" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="36" spans="2:3">
+      <c r="B36">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="37" spans="2:3">
+      <c r="B37">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="38" spans="2:3">
+      <c r="B38">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="39" spans="2:3">
+      <c r="B39">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="40" spans="2:3">
+      <c r="B40">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="41" spans="2:3">
+      <c r="B41">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="42" spans="2:3">
+      <c r="B42">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="43" spans="2:3">
+      <c r="B43">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="44" spans="2:3">
+      <c r="B44">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="45" spans="2:3">
+      <c r="B45">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="46" spans="2:3">
+      <c r="B46">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="47" spans="2:3">
+      <c r="B47">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="48" spans="2:3">
+      <c r="B48">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="49" spans="2:2">
+      <c r="B49">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="50" spans="2:2">
+      <c r="B50">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="51" spans="2:2">
+      <c r="B51">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="52" spans="2:2">
+      <c r="B52">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="53" spans="2:2">
+      <c r="B53">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="54" spans="2:2">
+      <c r="B54">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="55" spans="2:2">
+      <c r="B55">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="56" spans="2:2">
+      <c r="B56">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="57" spans="2:2">
+      <c r="B57">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="58" spans="2:2">
+      <c r="B58">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="59" spans="2:2">
+      <c r="B59">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="60" spans="2:2">
+      <c r="B60">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="61" spans="2:2">
+      <c r="B61">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="62" spans="2:2">
+      <c r="B62">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="63" spans="2:2">
+      <c r="B63">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="64" spans="2:2">
+      <c r="B64">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="65" spans="2:2">
+      <c r="B65">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="66" spans="2:2">
+      <c r="B66">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="67" spans="2:2">
+      <c r="B67">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="68" spans="2:2">
+      <c r="B68">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="69" spans="2:2">
+      <c r="B69">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="70" spans="2:2">
+      <c r="B70">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="71" spans="2:2">
+      <c r="B71">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="72" spans="2:2">
+      <c r="B72">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="73" spans="2:2">
+      <c r="B73">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="74" spans="2:2">
+      <c r="B74">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="75" spans="2:2">
+      <c r="B75">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="76" spans="2:2">
+      <c r="B76">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="77" spans="2:2">
+      <c r="B77">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="78" spans="2:2">
+      <c r="B78">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="79" spans="2:2">
+      <c r="B79">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="80" spans="2:2">
+      <c r="B80">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="81" spans="2:2">
+      <c r="B81">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="82" spans="2:2">
+      <c r="B82">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="83" spans="2:2">
+      <c r="B83">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="84" spans="2:2">
+      <c r="B84">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="85" spans="2:2">
+      <c r="B85">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="86" spans="2:2">
+      <c r="B86">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="87" spans="2:2">
+      <c r="B87">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="88" spans="2:2">
+      <c r="B88">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="89" spans="2:2">
+      <c r="B89">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="90" spans="2:2">
+      <c r="B90">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="91" spans="2:2">
+      <c r="B91">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="92" spans="2:2">
+      <c r="B92">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="93" spans="2:2">
+      <c r="B93">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="94" spans="2:2">
+      <c r="B94">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="95" spans="2:2">
+      <c r="B95">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="96" spans="2:2">
+      <c r="B96">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="97" spans="2:2">
+      <c r="B97">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="98" spans="2:2">
+      <c r="B98">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="99" spans="2:2">
+      <c r="B99">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="100" spans="2:2">
+      <c r="B100">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="101" spans="2:2">
+      <c r="B101">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="102" spans="2:2">
+      <c r="B102">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="103" spans="2:2">
+      <c r="B103">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="104" spans="2:2">
+      <c r="B104">
+        <v>103</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>